--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -2585,10 +2585,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117992046</v>
+        <v>117991518</v>
       </c>
       <c r="B18" t="n">
-        <v>97836</v>
+        <v>78514</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2597,31 +2597,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2629,13 +2636,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478295</v>
+        <v>478267</v>
       </c>
       <c r="R18" t="n">
-        <v>6770726</v>
+        <v>6770344</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2659,12 +2666,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,10 +2699,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117991518</v>
+        <v>117992046</v>
       </c>
       <c r="B19" t="n">
-        <v>78514</v>
+        <v>97836</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2704,38 +2711,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2743,13 +2743,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478267</v>
+        <v>478295</v>
       </c>
       <c r="R19" t="n">
-        <v>6770344</v>
+        <v>6770726</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2773,12 +2773,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -1684,7 +1684,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117991994</v>
+        <v>117992046</v>
       </c>
       <c r="B10" t="n">
         <v>97836</v>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478332</v>
+        <v>478295</v>
       </c>
       <c r="R10" t="n">
-        <v>6770702</v>
+        <v>6770726</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1791,10 +1791,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117991486</v>
+        <v>117987499</v>
       </c>
       <c r="B11" t="n">
-        <v>97836</v>
+        <v>57721</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1803,53 +1803,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>102999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Löva strand, Dlr</t>
+          <t>Lisselheds badplats (Lisselheds badplats), Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478287</v>
+        <v>478305</v>
       </c>
       <c r="R11" t="n">
-        <v>6770389</v>
+        <v>6771072</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1876,18 +1873,27 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1899,17 +1905,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117992031</v>
+        <v>117987719</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>57930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1918,45 +1924,60 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103042</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Löva strand, Dlr</t>
+          <t>Lisselheds badplats (Lisselheds badplats), Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478332</v>
+        <v>478256</v>
       </c>
       <c r="R12" t="n">
-        <v>6770710</v>
+        <v>6771182</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1980,12 +2001,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1994,7 +2025,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2006,17 +2036,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117991390</v>
+        <v>117991161</v>
       </c>
       <c r="B13" t="n">
-        <v>97836</v>
+        <v>91772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2025,39 +2055,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2065,13 +2094,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478310</v>
+        <v>478342</v>
       </c>
       <c r="R13" t="n">
-        <v>6770390</v>
+        <v>6770431</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2128,7 +2157,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117991424</v>
+        <v>117991376</v>
       </c>
       <c r="B14" t="n">
         <v>97836</v>
@@ -2163,7 +2192,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2180,10 +2209,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478302</v>
+        <v>478377</v>
       </c>
       <c r="R14" t="n">
-        <v>6770371</v>
+        <v>6770482</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2243,7 +2272,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117991494</v>
+        <v>117991506</v>
       </c>
       <c r="B15" t="n">
         <v>97836</v>
@@ -2278,7 +2307,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2295,10 +2324,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478291</v>
+        <v>478284</v>
       </c>
       <c r="R15" t="n">
-        <v>6770386</v>
+        <v>6770387</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2358,7 +2387,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117991376</v>
+        <v>117992067</v>
       </c>
       <c r="B16" t="n">
         <v>97836</v>
@@ -2391,16 +2420,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2410,13 +2431,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478377</v>
+        <v>478284</v>
       </c>
       <c r="R16" t="n">
-        <v>6770482</v>
+        <v>6770684</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2440,12 +2461,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2473,10 +2494,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117991128</v>
+        <v>117991141</v>
       </c>
       <c r="B17" t="n">
-        <v>8416</v>
+        <v>78514</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2485,36 +2506,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2522,10 +2545,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478389</v>
+        <v>478323</v>
       </c>
       <c r="R17" t="n">
-        <v>6770568</v>
+        <v>6770453</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2585,10 +2608,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117991518</v>
+        <v>117992010</v>
       </c>
       <c r="B18" t="n">
-        <v>78514</v>
+        <v>97836</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2597,38 +2620,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2636,13 +2652,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478267</v>
+        <v>478333</v>
       </c>
       <c r="R18" t="n">
-        <v>6770344</v>
+        <v>6770705</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2666,12 +2682,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2699,10 +2715,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117992046</v>
+        <v>117991173</v>
       </c>
       <c r="B19" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2711,31 +2727,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2743,13 +2766,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478295</v>
+        <v>478256</v>
       </c>
       <c r="R19" t="n">
-        <v>6770726</v>
+        <v>6770345</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2773,12 +2796,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>10-15 cm</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2806,7 +2834,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117992067</v>
+        <v>117991390</v>
       </c>
       <c r="B20" t="n">
         <v>97836</v>
@@ -2839,8 +2867,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2850,13 +2886,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478284</v>
+        <v>478310</v>
       </c>
       <c r="R20" t="n">
-        <v>6770684</v>
+        <v>6770390</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2880,12 +2916,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2913,7 +2949,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117991442</v>
+        <v>117991424</v>
       </c>
       <c r="B21" t="n">
         <v>97836</v>
@@ -2948,7 +2984,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2965,10 +3001,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478300</v>
+        <v>478302</v>
       </c>
       <c r="R21" t="n">
-        <v>6770395</v>
+        <v>6770371</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -3028,10 +3064,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117991141</v>
+        <v>117991238</v>
       </c>
       <c r="B22" t="n">
-        <v>78514</v>
+        <v>97836</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3040,38 +3076,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3079,13 +3116,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478323</v>
+        <v>478393</v>
       </c>
       <c r="R22" t="n">
-        <v>6770453</v>
+        <v>6770495</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3142,10 +3179,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117987499</v>
+        <v>117991494</v>
       </c>
       <c r="B23" t="n">
-        <v>57721</v>
+        <v>97836</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3154,50 +3191,53 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102999</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lisselheds badplats (Lisselheds badplats), Dlr</t>
+          <t>Löva strand, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478305</v>
+        <v>478291</v>
       </c>
       <c r="R23" t="n">
-        <v>6771072</v>
+        <v>6770386</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3224,27 +3264,18 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3256,17 +3287,17 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117991238</v>
+        <v>117991518</v>
       </c>
       <c r="B24" t="n">
-        <v>97836</v>
+        <v>78514</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3275,39 +3306,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3315,13 +3345,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478393</v>
+        <v>478267</v>
       </c>
       <c r="R24" t="n">
-        <v>6770495</v>
+        <v>6770344</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3378,10 +3408,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117991967</v>
+        <v>117991994</v>
       </c>
       <c r="B25" t="n">
-        <v>97740</v>
+        <v>97836</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3390,25 +3420,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3422,10 +3452,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478279</v>
+        <v>478332</v>
       </c>
       <c r="R25" t="n">
-        <v>6770619</v>
+        <v>6770702</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3485,10 +3515,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117991173</v>
+        <v>117991939</v>
       </c>
       <c r="B26" t="n">
-        <v>78480</v>
+        <v>97870</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3497,38 +3527,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3536,13 +3559,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478256</v>
+        <v>478272</v>
       </c>
       <c r="R26" t="n">
-        <v>6770345</v>
+        <v>6770612</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3566,17 +3589,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>10-15 cm</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3604,7 +3622,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117992010</v>
+        <v>117992041</v>
       </c>
       <c r="B27" t="n">
         <v>97836</v>
@@ -3648,10 +3666,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478333</v>
+        <v>478332</v>
       </c>
       <c r="R27" t="n">
-        <v>6770705</v>
+        <v>6770725</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3711,10 +3729,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117991506</v>
+        <v>117991967</v>
       </c>
       <c r="B28" t="n">
-        <v>97836</v>
+        <v>97740</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3723,37 +3741,29 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -3763,13 +3773,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478284</v>
+        <v>478279</v>
       </c>
       <c r="R28" t="n">
-        <v>6770387</v>
+        <v>6770619</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3793,12 +3803,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3826,10 +3836,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117987719</v>
+        <v>117992031</v>
       </c>
       <c r="B29" t="n">
-        <v>57930</v>
+        <v>97836</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3838,60 +3848,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103042</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lisselheds badplats (Lisselheds badplats), Dlr</t>
+          <t>Löva strand, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478256</v>
+        <v>478332</v>
       </c>
       <c r="R29" t="n">
-        <v>6771182</v>
+        <v>6770710</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3915,22 +3910,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3939,6 +3924,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3950,17 +3936,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117991161</v>
+        <v>117991309</v>
       </c>
       <c r="B30" t="n">
-        <v>91772</v>
+        <v>97836</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3969,38 +3955,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4008,13 +3999,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478342</v>
+        <v>478373</v>
       </c>
       <c r="R30" t="n">
-        <v>6770431</v>
+        <v>6770484</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4044,6 +4035,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4071,7 +4067,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117992041</v>
+        <v>117991442</v>
       </c>
       <c r="B31" t="n">
         <v>97836</v>
@@ -4104,8 +4100,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -4115,13 +4119,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478332</v>
+        <v>478300</v>
       </c>
       <c r="R31" t="n">
-        <v>6770725</v>
+        <v>6770395</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4145,12 +4149,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4178,10 +4182,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117991939</v>
+        <v>117991462</v>
       </c>
       <c r="B32" t="n">
-        <v>97870</v>
+        <v>97836</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4190,29 +4194,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
@@ -4222,13 +4234,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478272</v>
+        <v>478297</v>
       </c>
       <c r="R32" t="n">
-        <v>6770612</v>
+        <v>6770390</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4252,12 +4264,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4285,10 +4297,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117991309</v>
+        <v>117991128</v>
       </c>
       <c r="B33" t="n">
-        <v>97836</v>
+        <v>8416</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4297,43 +4309,36 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4341,13 +4346,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478373</v>
+        <v>478389</v>
       </c>
       <c r="R33" t="n">
-        <v>6770484</v>
+        <v>6770568</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4377,11 +4382,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4409,7 +4409,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117991462</v>
+        <v>117991486</v>
       </c>
       <c r="B34" t="n">
         <v>97836</v>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478297</v>
+        <v>478287</v>
       </c>
       <c r="R34" t="n">
-        <v>6770390</v>
+        <v>6770389</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4524,10 +4524,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118005992</v>
+        <v>118012435</v>
       </c>
       <c r="B35" t="n">
-        <v>90782</v>
+        <v>57287</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4540,46 +4540,45 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Löva strand (Löva strand), Dlr</t>
+          <t>Löva strand, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478317</v>
+        <v>478273</v>
       </c>
       <c r="R35" t="n">
-        <v>6770881</v>
+        <v>6770752</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4606,19 +4605,9 @@
           <t>2024-06-25</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>09:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4638,17 +4627,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118012604</v>
+        <v>118012495</v>
       </c>
       <c r="B36" t="n">
-        <v>57303</v>
+        <v>57287</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4661,16 +4650,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4693,10 +4682,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478425</v>
+        <v>478316</v>
       </c>
       <c r="R36" t="n">
-        <v>6770887</v>
+        <v>6770684</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4755,10 +4744,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118012563</v>
+        <v>118012356</v>
       </c>
       <c r="B37" t="n">
-        <v>57287</v>
+        <v>78514</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4771,31 +4760,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4803,10 +4791,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478429</v>
+        <v>478271</v>
       </c>
       <c r="R37" t="n">
-        <v>6770806</v>
+        <v>6770777</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4847,6 +4835,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4865,10 +4854,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118012097</v>
+        <v>118012524</v>
       </c>
       <c r="B38" t="n">
-        <v>90782</v>
+        <v>57287</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4881,30 +4870,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4912,10 +4902,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478340</v>
+        <v>478360</v>
       </c>
       <c r="R38" t="n">
-        <v>6770883</v>
+        <v>6770637</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4956,7 +4946,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4975,10 +4964,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118012066</v>
+        <v>118012532</v>
       </c>
       <c r="B39" t="n">
-        <v>90499</v>
+        <v>57287</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4991,26 +4980,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5018,10 +5012,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478346</v>
+        <v>478379</v>
       </c>
       <c r="R39" t="n">
-        <v>6770893</v>
+        <v>6770707</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5062,7 +5056,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5081,7 +5074,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118012626</v>
+        <v>118012341</v>
       </c>
       <c r="B40" t="n">
         <v>57287</v>
@@ -5129,10 +5122,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478361</v>
+        <v>478313</v>
       </c>
       <c r="R40" t="n">
-        <v>6770994</v>
+        <v>6770775</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5191,10 +5184,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118012524</v>
+        <v>118012475</v>
       </c>
       <c r="B41" t="n">
-        <v>57287</v>
+        <v>97836</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5203,35 +5196,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5239,10 +5236,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478360</v>
+        <v>478323</v>
       </c>
       <c r="R41" t="n">
-        <v>6770637</v>
+        <v>6770678</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5277,12 +5274,18 @@
           <t>2024-06-25</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>4 stjälkar med knopp</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5301,10 +5304,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118012347</v>
+        <v>118012604</v>
       </c>
       <c r="B42" t="n">
-        <v>57287</v>
+        <v>57303</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5317,16 +5320,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5349,10 +5352,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478280</v>
+        <v>478425</v>
       </c>
       <c r="R42" t="n">
-        <v>6770778</v>
+        <v>6770887</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5411,7 +5414,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118012475</v>
+        <v>118012170</v>
       </c>
       <c r="B43" t="n">
         <v>97836</v>
@@ -5446,7 +5449,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5463,10 +5466,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478323</v>
+        <v>478322</v>
       </c>
       <c r="R43" t="n">
-        <v>6770678</v>
+        <v>6770862</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5499,11 +5502,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>4 stjälkar med knopp</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5531,10 +5529,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118012224</v>
+        <v>118012615</v>
       </c>
       <c r="B44" t="n">
-        <v>5166</v>
+        <v>57287</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5543,32 +5541,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5576,10 +5577,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478286</v>
+        <v>478353</v>
       </c>
       <c r="R44" t="n">
-        <v>6770841</v>
+        <v>6770981</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5620,7 +5621,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5639,10 +5639,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118012210</v>
+        <v>118012310</v>
       </c>
       <c r="B45" t="n">
-        <v>90782</v>
+        <v>57287</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5655,26 +5655,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5682,10 +5687,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478289</v>
+        <v>478313</v>
       </c>
       <c r="R45" t="n">
-        <v>6770849</v>
+        <v>6770778</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5726,7 +5731,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5745,10 +5749,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118012486</v>
+        <v>118012520</v>
       </c>
       <c r="B46" t="n">
-        <v>97836</v>
+        <v>57287</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5757,39 +5761,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5797,10 +5797,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478326</v>
+        <v>478353</v>
       </c>
       <c r="R46" t="n">
-        <v>6770688</v>
+        <v>6770628</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5841,7 +5841,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5860,7 +5859,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118012333</v>
+        <v>118012371</v>
       </c>
       <c r="B47" t="n">
         <v>57287</v>
@@ -5908,10 +5907,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478303</v>
+        <v>478270</v>
       </c>
       <c r="R47" t="n">
-        <v>6770765</v>
+        <v>6770776</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5970,7 +5969,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118012590</v>
+        <v>118012488</v>
       </c>
       <c r="B48" t="n">
         <v>57287</v>
@@ -6018,10 +6017,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478412</v>
+        <v>478332</v>
       </c>
       <c r="R48" t="n">
-        <v>6770832</v>
+        <v>6770689</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6080,7 +6079,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118012520</v>
+        <v>118012541</v>
       </c>
       <c r="B49" t="n">
         <v>57287</v>
@@ -6128,10 +6127,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478353</v>
+        <v>478395</v>
       </c>
       <c r="R49" t="n">
-        <v>6770628</v>
+        <v>6770706</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6190,7 +6189,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118012371</v>
+        <v>118012327</v>
       </c>
       <c r="B50" t="n">
         <v>57287</v>
@@ -6238,10 +6237,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478270</v>
+        <v>478307</v>
       </c>
       <c r="R50" t="n">
-        <v>6770776</v>
+        <v>6770778</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6300,10 +6299,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118012179</v>
+        <v>118012580</v>
       </c>
       <c r="B51" t="n">
-        <v>90782</v>
+        <v>57287</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6316,34 +6315,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6351,10 +6347,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478312</v>
+        <v>478418</v>
       </c>
       <c r="R51" t="n">
-        <v>6770833</v>
+        <v>6770813</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6395,7 +6391,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6414,10 +6409,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118012242</v>
+        <v>118012179</v>
       </c>
       <c r="B52" t="n">
-        <v>95131</v>
+        <v>90782</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6426,39 +6421,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6466,10 +6460,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478347</v>
+        <v>478312</v>
       </c>
       <c r="R52" t="n">
-        <v>6770839</v>
+        <v>6770833</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6529,10 +6523,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118012418</v>
+        <v>118012590</v>
       </c>
       <c r="B53" t="n">
-        <v>5166</v>
+        <v>57287</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6541,34 +6535,33 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6578,10 +6571,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478280</v>
+        <v>478412</v>
       </c>
       <c r="R53" t="n">
-        <v>6770778</v>
+        <v>6770832</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6622,7 +6615,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6641,7 +6633,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118012197</v>
+        <v>118012626</v>
       </c>
       <c r="B54" t="n">
         <v>57287</v>
@@ -6689,10 +6681,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478270</v>
+        <v>478361</v>
       </c>
       <c r="R54" t="n">
-        <v>6770837</v>
+        <v>6770994</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6751,7 +6743,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118012615</v>
+        <v>118012252</v>
       </c>
       <c r="B55" t="n">
         <v>57287</v>
@@ -6799,10 +6791,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478353</v>
+        <v>478351</v>
       </c>
       <c r="R55" t="n">
-        <v>6770981</v>
+        <v>6770848</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6861,10 +6853,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118012532</v>
+        <v>118012283</v>
       </c>
       <c r="B56" t="n">
-        <v>57287</v>
+        <v>97836</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6873,35 +6865,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6909,10 +6901,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478379</v>
+        <v>478311</v>
       </c>
       <c r="R56" t="n">
-        <v>6770707</v>
+        <v>6770775</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -6953,6 +6945,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6971,10 +6964,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118012512</v>
+        <v>118012418</v>
       </c>
       <c r="B57" t="n">
-        <v>57287</v>
+        <v>5166</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6983,33 +6976,34 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7019,10 +7013,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478343</v>
+        <v>478280</v>
       </c>
       <c r="R57" t="n">
-        <v>6770636</v>
+        <v>6770778</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -7063,6 +7057,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7081,10 +7076,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118012130</v>
+        <v>118012563</v>
       </c>
       <c r="B58" t="n">
-        <v>5166</v>
+        <v>57287</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7093,34 +7088,33 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7130,10 +7124,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478336</v>
+        <v>478429</v>
       </c>
       <c r="R58" t="n">
-        <v>6770864</v>
+        <v>6770806</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7174,7 +7168,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7193,7 +7186,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118012507</v>
+        <v>118012262</v>
       </c>
       <c r="B59" t="n">
         <v>57287</v>
@@ -7241,10 +7234,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>478322</v>
+        <v>478347</v>
       </c>
       <c r="R59" t="n">
-        <v>6770683</v>
+        <v>6770859</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -7303,10 +7296,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118012541</v>
+        <v>118012130</v>
       </c>
       <c r="B60" t="n">
-        <v>57287</v>
+        <v>5166</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7315,33 +7308,34 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7351,10 +7345,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478395</v>
+        <v>478336</v>
       </c>
       <c r="R60" t="n">
-        <v>6770706</v>
+        <v>6770864</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -7395,6 +7389,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7413,10 +7408,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118012262</v>
+        <v>118012066</v>
       </c>
       <c r="B61" t="n">
-        <v>57287</v>
+        <v>90499</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7429,31 +7424,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7461,10 +7451,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478347</v>
+        <v>478346</v>
       </c>
       <c r="R61" t="n">
-        <v>6770859</v>
+        <v>6770893</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7505,6 +7495,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7523,10 +7514,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118012356</v>
+        <v>118012500</v>
       </c>
       <c r="B62" t="n">
-        <v>78514</v>
+        <v>57287</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7539,30 +7530,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7570,10 +7562,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>478271</v>
+        <v>478322</v>
       </c>
       <c r="R62" t="n">
-        <v>6770777</v>
+        <v>6770683</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7614,7 +7606,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7743,10 +7734,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118012283</v>
+        <v>118012197</v>
       </c>
       <c r="B64" t="n">
-        <v>97836</v>
+        <v>57287</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7755,35 +7746,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7791,10 +7782,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>478311</v>
+        <v>478270</v>
       </c>
       <c r="R64" t="n">
-        <v>6770775</v>
+        <v>6770837</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7835,7 +7826,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7854,7 +7844,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118012327</v>
+        <v>118012515</v>
       </c>
       <c r="B65" t="n">
         <v>57287</v>
@@ -7902,10 +7892,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>478307</v>
+        <v>478341</v>
       </c>
       <c r="R65" t="n">
-        <v>6770778</v>
+        <v>6770628</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7964,10 +7954,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118012310</v>
+        <v>118012242</v>
       </c>
       <c r="B66" t="n">
-        <v>57287</v>
+        <v>95131</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7976,35 +7966,39 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8012,10 +8006,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478313</v>
+        <v>478347</v>
       </c>
       <c r="R66" t="n">
-        <v>6770778</v>
+        <v>6770839</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8056,6 +8050,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8074,7 +8069,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118012515</v>
+        <v>118012384</v>
       </c>
       <c r="B67" t="n">
         <v>57287</v>
@@ -8122,10 +8117,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478341</v>
+        <v>478275</v>
       </c>
       <c r="R67" t="n">
-        <v>6770628</v>
+        <v>6770755</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -8184,10 +8179,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118012495</v>
+        <v>118012224</v>
       </c>
       <c r="B68" t="n">
-        <v>57287</v>
+        <v>5166</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8196,35 +8191,32 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8232,10 +8224,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>478316</v>
+        <v>478286</v>
       </c>
       <c r="R68" t="n">
-        <v>6770684</v>
+        <v>6770841</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -8276,6 +8268,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8294,10 +8287,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118012488</v>
+        <v>118012097</v>
       </c>
       <c r="B69" t="n">
-        <v>57287</v>
+        <v>90782</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8310,31 +8303,30 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8342,10 +8334,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>478332</v>
+        <v>478340</v>
       </c>
       <c r="R69" t="n">
-        <v>6770689</v>
+        <v>6770883</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -8386,6 +8378,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8404,10 +8397,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118012252</v>
+        <v>118005992</v>
       </c>
       <c r="B70" t="n">
-        <v>57287</v>
+        <v>90782</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8420,45 +8413,46 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Löva strand, Dlr</t>
+          <t>Löva strand (Löva strand), Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>478351</v>
+        <v>478317</v>
       </c>
       <c r="R70" t="n">
-        <v>6770848</v>
+        <v>6770881</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8485,9 +8479,19 @@
           <t>2024-06-25</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8507,17 +8511,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118012170</v>
+        <v>118012347</v>
       </c>
       <c r="B71" t="n">
-        <v>97836</v>
+        <v>57287</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8526,39 +8530,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8566,10 +8566,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>478322</v>
+        <v>478280</v>
       </c>
       <c r="R71" t="n">
-        <v>6770862</v>
+        <v>6770778</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -8610,7 +8610,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8629,10 +8628,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118012435</v>
+        <v>118012210</v>
       </c>
       <c r="B72" t="n">
-        <v>57287</v>
+        <v>90782</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8645,31 +8644,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8677,10 +8671,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>478273</v>
+        <v>478289</v>
       </c>
       <c r="R72" t="n">
-        <v>6770752</v>
+        <v>6770849</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8721,6 +8715,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8739,10 +8734,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118012580</v>
+        <v>118012486</v>
       </c>
       <c r="B73" t="n">
-        <v>57287</v>
+        <v>97836</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8751,35 +8746,39 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8787,10 +8786,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>478418</v>
+        <v>478326</v>
       </c>
       <c r="R73" t="n">
-        <v>6770813</v>
+        <v>6770688</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8831,6 +8830,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8849,7 +8849,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118012341</v>
+        <v>118012157</v>
       </c>
       <c r="B74" t="n">
         <v>57287</v>
@@ -8897,10 +8897,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>478313</v>
+        <v>478319</v>
       </c>
       <c r="R74" t="n">
-        <v>6770775</v>
+        <v>6770865</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8959,7 +8959,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118012157</v>
+        <v>118012333</v>
       </c>
       <c r="B75" t="n">
         <v>57287</v>
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>478319</v>
+        <v>478303</v>
       </c>
       <c r="R75" t="n">
-        <v>6770865</v>
+        <v>6770765</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -9069,7 +9069,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118012384</v>
+        <v>118012512</v>
       </c>
       <c r="B76" t="n">
         <v>57287</v>
@@ -9117,10 +9117,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>478275</v>
+        <v>478343</v>
       </c>
       <c r="R76" t="n">
-        <v>6770755</v>
+        <v>6770636</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>

--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -1684,10 +1684,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117992046</v>
+        <v>117991486</v>
       </c>
       <c r="B10" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1717,8 +1717,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -1728,13 +1736,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478295</v>
+        <v>478287</v>
       </c>
       <c r="R10" t="n">
-        <v>6770726</v>
+        <v>6770389</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1758,12 +1766,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1791,10 +1799,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117987499</v>
+        <v>117991994</v>
       </c>
       <c r="B11" t="n">
-        <v>57721</v>
+        <v>97838</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1803,50 +1811,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102999</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lisselheds badplats (Lisselheds badplats), Dlr</t>
+          <t>Löva strand, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478305</v>
+        <v>478332</v>
       </c>
       <c r="R11" t="n">
-        <v>6771072</v>
+        <v>6770702</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1870,22 +1873,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1894,6 +1887,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1905,17 +1899,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117987719</v>
+        <v>117991141</v>
       </c>
       <c r="B12" t="n">
-        <v>57930</v>
+        <v>78516</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1924,25 +1918,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103042</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1950,34 +1944,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lisselheds badplats (Lisselheds badplats), Dlr</t>
+          <t>Löva strand, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478256</v>
+        <v>478323</v>
       </c>
       <c r="R12" t="n">
-        <v>6771182</v>
+        <v>6770453</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2004,27 +1990,18 @@
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-06-24</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2036,17 +2013,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117991161</v>
+        <v>117991128</v>
       </c>
       <c r="B13" t="n">
-        <v>91772</v>
+        <v>8416</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2059,34 +2036,32 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2094,10 +2069,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478342</v>
+        <v>478389</v>
       </c>
       <c r="R13" t="n">
-        <v>6770431</v>
+        <v>6770568</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2157,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117991376</v>
+        <v>117991462</v>
       </c>
       <c r="B14" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2192,12 +2167,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2209,10 +2184,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478377</v>
+        <v>478297</v>
       </c>
       <c r="R14" t="n">
-        <v>6770482</v>
+        <v>6770390</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2272,10 +2247,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117991506</v>
+        <v>117991424</v>
       </c>
       <c r="B15" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2307,7 +2282,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2324,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478284</v>
+        <v>478302</v>
       </c>
       <c r="R15" t="n">
-        <v>6770387</v>
+        <v>6770371</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2387,10 +2362,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117992067</v>
+        <v>117991390</v>
       </c>
       <c r="B16" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2420,8 +2395,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2431,13 +2414,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478284</v>
+        <v>478310</v>
       </c>
       <c r="R16" t="n">
-        <v>6770684</v>
+        <v>6770390</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2461,12 +2444,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2494,10 +2477,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117991141</v>
+        <v>117992046</v>
       </c>
       <c r="B17" t="n">
-        <v>78514</v>
+        <v>97838</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2506,38 +2489,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2545,13 +2521,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478323</v>
+        <v>478295</v>
       </c>
       <c r="R17" t="n">
-        <v>6770453</v>
+        <v>6770726</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2575,12 +2551,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2608,10 +2584,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117992010</v>
+        <v>117991238</v>
       </c>
       <c r="B18" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2641,8 +2617,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2652,13 +2636,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478333</v>
+        <v>478393</v>
       </c>
       <c r="R18" t="n">
-        <v>6770705</v>
+        <v>6770495</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2682,12 +2666,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2715,10 +2699,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117991173</v>
+        <v>117991309</v>
       </c>
       <c r="B19" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2727,38 +2711,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2766,13 +2755,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478256</v>
+        <v>478373</v>
       </c>
       <c r="R19" t="n">
-        <v>6770345</v>
+        <v>6770484</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2806,7 +2795,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>10-15 cm</t>
+          <t>5 blomstjälkar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2834,10 +2823,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117991390</v>
+        <v>117987719</v>
       </c>
       <c r="B20" t="n">
-        <v>97836</v>
+        <v>57931</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2846,53 +2835,60 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103042</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Löva strand, Dlr</t>
+          <t>Lisselheds badplats (Lisselheds badplats), Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478310</v>
+        <v>478256</v>
       </c>
       <c r="R20" t="n">
-        <v>6770390</v>
+        <v>6771182</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2919,18 +2915,27 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2942,17 +2947,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117991424</v>
+        <v>117992041</v>
       </c>
       <c r="B21" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2982,16 +2987,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3001,13 +2998,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478302</v>
+        <v>478332</v>
       </c>
       <c r="R21" t="n">
-        <v>6770371</v>
+        <v>6770725</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3031,12 +3028,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3064,10 +3061,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117991238</v>
+        <v>117991518</v>
       </c>
       <c r="B22" t="n">
-        <v>97836</v>
+        <v>78516</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3076,39 +3073,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3116,13 +3112,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478393</v>
+        <v>478267</v>
       </c>
       <c r="R22" t="n">
-        <v>6770495</v>
+        <v>6770344</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3179,10 +3175,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117991494</v>
+        <v>117992067</v>
       </c>
       <c r="B23" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3212,16 +3208,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3231,13 +3219,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478291</v>
+        <v>478284</v>
       </c>
       <c r="R23" t="n">
-        <v>6770386</v>
+        <v>6770684</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3261,12 +3249,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3294,10 +3282,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117991518</v>
+        <v>117992031</v>
       </c>
       <c r="B24" t="n">
-        <v>78514</v>
+        <v>97838</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3306,38 +3294,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3345,13 +3326,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478267</v>
+        <v>478332</v>
       </c>
       <c r="R24" t="n">
-        <v>6770344</v>
+        <v>6770710</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3375,12 +3356,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3408,10 +3389,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117991994</v>
+        <v>117991376</v>
       </c>
       <c r="B25" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3441,8 +3422,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3452,13 +3441,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478332</v>
+        <v>478377</v>
       </c>
       <c r="R25" t="n">
-        <v>6770702</v>
+        <v>6770482</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3482,12 +3471,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3518,7 +3507,7 @@
         <v>117991939</v>
       </c>
       <c r="B26" t="n">
-        <v>97870</v>
+        <v>97872</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3622,10 +3611,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117992041</v>
+        <v>117991173</v>
       </c>
       <c r="B27" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3634,31 +3623,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3666,13 +3662,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478332</v>
+        <v>478256</v>
       </c>
       <c r="R27" t="n">
-        <v>6770725</v>
+        <v>6770345</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3696,12 +3692,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>10-15 cm</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3729,10 +3730,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117991967</v>
+        <v>117991161</v>
       </c>
       <c r="B28" t="n">
-        <v>97740</v>
+        <v>91774</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3745,27 +3746,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220093</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3773,13 +3781,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478279</v>
+        <v>478342</v>
       </c>
       <c r="R28" t="n">
-        <v>6770619</v>
+        <v>6770431</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3803,12 +3811,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3836,10 +3844,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117992031</v>
+        <v>117991494</v>
       </c>
       <c r="B29" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3869,8 +3877,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3880,13 +3896,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478332</v>
+        <v>478291</v>
       </c>
       <c r="R29" t="n">
-        <v>6770710</v>
+        <v>6770386</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3910,12 +3926,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3943,10 +3959,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117991309</v>
+        <v>117991967</v>
       </c>
       <c r="B30" t="n">
-        <v>97836</v>
+        <v>97742</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3955,42 +3971,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
@@ -3999,13 +4003,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478373</v>
+        <v>478279</v>
       </c>
       <c r="R30" t="n">
-        <v>6770484</v>
+        <v>6770619</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4029,17 +4033,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>5 blomstjälkar</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4070,7 +4069,7 @@
         <v>117991442</v>
       </c>
       <c r="B31" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4182,10 +4181,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117991462</v>
+        <v>117987499</v>
       </c>
       <c r="B32" t="n">
-        <v>97836</v>
+        <v>57722</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4194,53 +4193,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>102999</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Löva strand, Dlr</t>
+          <t>Lisselheds badplats (Lisselheds badplats), Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478297</v>
+        <v>478305</v>
       </c>
       <c r="R32" t="n">
-        <v>6770390</v>
+        <v>6771072</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4267,18 +4263,27 @@
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-06-24</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4290,17 +4295,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117991128</v>
+        <v>117992010</v>
       </c>
       <c r="B33" t="n">
-        <v>8416</v>
+        <v>97838</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4309,36 +4314,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4346,13 +4346,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478389</v>
+        <v>478333</v>
       </c>
       <c r="R33" t="n">
-        <v>6770568</v>
+        <v>6770705</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4376,12 +4376,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4409,10 +4409,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117991486</v>
+        <v>117991506</v>
       </c>
       <c r="B34" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>478287</v>
+        <v>478284</v>
       </c>
       <c r="R34" t="n">
-        <v>6770389</v>
+        <v>6770387</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4524,10 +4524,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118012435</v>
+        <v>118012066</v>
       </c>
       <c r="B35" t="n">
-        <v>57287</v>
+        <v>90501</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4540,31 +4540,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4572,10 +4567,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>478273</v>
+        <v>478346</v>
       </c>
       <c r="R35" t="n">
-        <v>6770752</v>
+        <v>6770893</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4616,6 +4611,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4634,10 +4630,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118012495</v>
+        <v>118012512</v>
       </c>
       <c r="B36" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4682,10 +4678,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>478316</v>
+        <v>478343</v>
       </c>
       <c r="R36" t="n">
-        <v>6770684</v>
+        <v>6770636</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4744,10 +4740,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118012356</v>
+        <v>118012486</v>
       </c>
       <c r="B37" t="n">
-        <v>78514</v>
+        <v>97838</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4756,34 +4752,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4791,10 +4792,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>478271</v>
+        <v>478326</v>
       </c>
       <c r="R37" t="n">
-        <v>6770777</v>
+        <v>6770688</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4854,10 +4855,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118012524</v>
+        <v>118012170</v>
       </c>
       <c r="B38" t="n">
-        <v>57287</v>
+        <v>97838</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4866,35 +4867,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4902,10 +4907,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>478360</v>
+        <v>478322</v>
       </c>
       <c r="R38" t="n">
-        <v>6770637</v>
+        <v>6770862</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4946,6 +4951,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4964,10 +4970,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118012532</v>
+        <v>118012252</v>
       </c>
       <c r="B39" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5012,10 +5018,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>478379</v>
+        <v>478351</v>
       </c>
       <c r="R39" t="n">
-        <v>6770707</v>
+        <v>6770848</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5074,10 +5080,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118012341</v>
+        <v>118012495</v>
       </c>
       <c r="B40" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5122,10 +5128,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>478313</v>
+        <v>478316</v>
       </c>
       <c r="R40" t="n">
-        <v>6770775</v>
+        <v>6770684</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5184,10 +5190,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118012475</v>
+        <v>118012488</v>
       </c>
       <c r="B41" t="n">
-        <v>97836</v>
+        <v>57288</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5196,39 +5202,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5236,10 +5238,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>478323</v>
+        <v>478332</v>
       </c>
       <c r="R41" t="n">
-        <v>6770678</v>
+        <v>6770689</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5274,18 +5276,12 @@
           <t>2024-06-25</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>4 stjälkar med knopp</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5304,10 +5300,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118012604</v>
+        <v>118012224</v>
       </c>
       <c r="B42" t="n">
-        <v>57303</v>
+        <v>5166</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5316,35 +5312,32 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5352,10 +5345,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>478425</v>
+        <v>478286</v>
       </c>
       <c r="R42" t="n">
-        <v>6770887</v>
+        <v>6770841</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5396,6 +5389,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5414,10 +5408,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118012170</v>
+        <v>118012179</v>
       </c>
       <c r="B43" t="n">
-        <v>97836</v>
+        <v>90784</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5426,39 +5420,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5466,10 +5459,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>478322</v>
+        <v>478312</v>
       </c>
       <c r="R43" t="n">
-        <v>6770862</v>
+        <v>6770833</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5529,10 +5522,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118012615</v>
+        <v>118012327</v>
       </c>
       <c r="B44" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5577,10 +5570,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>478353</v>
+        <v>478307</v>
       </c>
       <c r="R44" t="n">
-        <v>6770981</v>
+        <v>6770778</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5639,10 +5632,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118012310</v>
+        <v>118012347</v>
       </c>
       <c r="B45" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5687,7 +5680,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>478313</v>
+        <v>478280</v>
       </c>
       <c r="R45" t="n">
         <v>6770778</v>
@@ -5749,10 +5742,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118012520</v>
+        <v>118012356</v>
       </c>
       <c r="B46" t="n">
-        <v>57287</v>
+        <v>78516</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5765,31 +5758,30 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5797,10 +5789,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>478353</v>
+        <v>478271</v>
       </c>
       <c r="R46" t="n">
-        <v>6770628</v>
+        <v>6770777</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5841,6 +5833,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5859,10 +5852,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118012371</v>
+        <v>118012507</v>
       </c>
       <c r="B47" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5907,10 +5900,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>478270</v>
+        <v>478322</v>
       </c>
       <c r="R47" t="n">
-        <v>6770776</v>
+        <v>6770683</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5969,10 +5962,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118012488</v>
+        <v>118012563</v>
       </c>
       <c r="B48" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6017,10 +6010,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>478332</v>
+        <v>478429</v>
       </c>
       <c r="R48" t="n">
-        <v>6770689</v>
+        <v>6770806</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6079,10 +6072,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118012541</v>
+        <v>118012590</v>
       </c>
       <c r="B49" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6127,10 +6120,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>478395</v>
+        <v>478412</v>
       </c>
       <c r="R49" t="n">
-        <v>6770706</v>
+        <v>6770832</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6189,10 +6182,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118012327</v>
+        <v>118012130</v>
       </c>
       <c r="B50" t="n">
-        <v>57287</v>
+        <v>5166</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6201,33 +6194,34 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6237,10 +6231,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>478307</v>
+        <v>478336</v>
       </c>
       <c r="R50" t="n">
-        <v>6770778</v>
+        <v>6770864</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6281,6 +6275,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6299,10 +6294,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118012580</v>
+        <v>118012475</v>
       </c>
       <c r="B51" t="n">
-        <v>57287</v>
+        <v>97838</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6311,35 +6306,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6347,10 +6346,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>478418</v>
+        <v>478323</v>
       </c>
       <c r="R51" t="n">
-        <v>6770813</v>
+        <v>6770678</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -6385,12 +6384,18 @@
           <t>2024-06-25</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>4 stjälkar med knopp</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6409,10 +6414,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118012179</v>
+        <v>118012197</v>
       </c>
       <c r="B52" t="n">
-        <v>90782</v>
+        <v>57288</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6425,34 +6430,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6460,10 +6462,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>478312</v>
+        <v>478270</v>
       </c>
       <c r="R52" t="n">
-        <v>6770833</v>
+        <v>6770837</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -6504,7 +6506,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6523,10 +6524,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118012590</v>
+        <v>118012333</v>
       </c>
       <c r="B53" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6571,10 +6572,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>478412</v>
+        <v>478303</v>
       </c>
       <c r="R53" t="n">
-        <v>6770832</v>
+        <v>6770765</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -6633,10 +6634,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118012626</v>
+        <v>118012283</v>
       </c>
       <c r="B54" t="n">
-        <v>57287</v>
+        <v>97838</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6645,35 +6646,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6681,10 +6682,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>478361</v>
+        <v>478311</v>
       </c>
       <c r="R54" t="n">
-        <v>6770994</v>
+        <v>6770775</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6725,6 +6726,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6743,10 +6745,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118012252</v>
+        <v>118012515</v>
       </c>
       <c r="B55" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6791,10 +6793,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>478351</v>
+        <v>478341</v>
       </c>
       <c r="R55" t="n">
-        <v>6770848</v>
+        <v>6770628</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -6853,10 +6855,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118012283</v>
+        <v>118012524</v>
       </c>
       <c r="B56" t="n">
-        <v>97836</v>
+        <v>57288</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6865,35 +6867,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6901,10 +6903,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>478311</v>
+        <v>478360</v>
       </c>
       <c r="R56" t="n">
-        <v>6770775</v>
+        <v>6770637</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -6945,7 +6947,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6964,10 +6965,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118012418</v>
+        <v>118005992</v>
       </c>
       <c r="B57" t="n">
-        <v>5166</v>
+        <v>90784</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6976,50 +6977,50 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Löva strand, Dlr</t>
+          <t>Löva strand (Löva strand), Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>478280</v>
+        <v>478317</v>
       </c>
       <c r="R57" t="n">
-        <v>6770778</v>
+        <v>6770881</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7046,18 +7047,27 @@
           <t>2024-06-25</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-06-25</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7069,17 +7079,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118012563</v>
+        <v>118012157</v>
       </c>
       <c r="B58" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7124,10 +7134,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>478429</v>
+        <v>478319</v>
       </c>
       <c r="R58" t="n">
-        <v>6770806</v>
+        <v>6770865</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -7186,10 +7196,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118012262</v>
+        <v>118012626</v>
       </c>
       <c r="B59" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7234,10 +7244,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>478347</v>
+        <v>478361</v>
       </c>
       <c r="R59" t="n">
-        <v>6770859</v>
+        <v>6770994</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -7296,10 +7306,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118012130</v>
+        <v>118012520</v>
       </c>
       <c r="B60" t="n">
-        <v>5166</v>
+        <v>57288</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7308,34 +7318,33 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7345,10 +7354,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>478336</v>
+        <v>478353</v>
       </c>
       <c r="R60" t="n">
-        <v>6770864</v>
+        <v>6770628</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -7389,7 +7398,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7408,10 +7416,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118012066</v>
+        <v>118012371</v>
       </c>
       <c r="B61" t="n">
-        <v>90499</v>
+        <v>57288</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7424,26 +7432,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7451,10 +7464,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>478346</v>
+        <v>478270</v>
       </c>
       <c r="R61" t="n">
-        <v>6770893</v>
+        <v>6770776</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -7495,7 +7508,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7514,10 +7526,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118012500</v>
+        <v>118012541</v>
       </c>
       <c r="B62" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7562,10 +7574,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>478322</v>
+        <v>478395</v>
       </c>
       <c r="R62" t="n">
-        <v>6770683</v>
+        <v>6770706</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7624,10 +7636,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118012651</v>
+        <v>118012097</v>
       </c>
       <c r="B63" t="n">
-        <v>57287</v>
+        <v>90784</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7640,31 +7652,30 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7672,10 +7683,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>478346</v>
+        <v>478340</v>
       </c>
       <c r="R63" t="n">
-        <v>6771016</v>
+        <v>6770883</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7716,6 +7727,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7734,10 +7746,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118012197</v>
+        <v>118012435</v>
       </c>
       <c r="B64" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7782,10 +7794,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>478270</v>
+        <v>478273</v>
       </c>
       <c r="R64" t="n">
-        <v>6770837</v>
+        <v>6770752</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7844,10 +7856,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118012515</v>
+        <v>118012615</v>
       </c>
       <c r="B65" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7892,10 +7904,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>478341</v>
+        <v>478353</v>
       </c>
       <c r="R65" t="n">
-        <v>6770628</v>
+        <v>6770981</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7954,10 +7966,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118012242</v>
+        <v>118012210</v>
       </c>
       <c r="B66" t="n">
-        <v>95131</v>
+        <v>90784</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7966,39 +7978,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8006,10 +8009,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>478347</v>
+        <v>478289</v>
       </c>
       <c r="R66" t="n">
-        <v>6770839</v>
+        <v>6770849</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -8069,10 +8072,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118012384</v>
+        <v>118012310</v>
       </c>
       <c r="B67" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8117,10 +8120,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>478275</v>
+        <v>478313</v>
       </c>
       <c r="R67" t="n">
-        <v>6770755</v>
+        <v>6770778</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -8179,10 +8182,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118012224</v>
+        <v>118012532</v>
       </c>
       <c r="B68" t="n">
-        <v>5166</v>
+        <v>57288</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8191,32 +8194,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8224,10 +8230,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>478286</v>
+        <v>478379</v>
       </c>
       <c r="R68" t="n">
-        <v>6770841</v>
+        <v>6770707</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -8268,7 +8274,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8287,10 +8292,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>118012097</v>
+        <v>118012242</v>
       </c>
       <c r="B69" t="n">
-        <v>90782</v>
+        <v>95133</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8299,34 +8304,39 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8334,10 +8344,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>478340</v>
+        <v>478347</v>
       </c>
       <c r="R69" t="n">
-        <v>6770883</v>
+        <v>6770839</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -8397,10 +8407,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118005992</v>
+        <v>118012580</v>
       </c>
       <c r="B70" t="n">
-        <v>90782</v>
+        <v>57288</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8413,46 +8423,45 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Löva strand (Löva strand), Dlr</t>
+          <t>Löva strand, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>478317</v>
+        <v>478418</v>
       </c>
       <c r="R70" t="n">
-        <v>6770881</v>
+        <v>6770813</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8479,19 +8488,9 @@
           <t>2024-06-25</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>09:49</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-06-25</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>09:49</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8511,17 +8510,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118012347</v>
+        <v>118012262</v>
       </c>
       <c r="B71" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8566,10 +8565,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>478280</v>
+        <v>478347</v>
       </c>
       <c r="R71" t="n">
-        <v>6770778</v>
+        <v>6770859</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -8628,10 +8627,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118012210</v>
+        <v>118012418</v>
       </c>
       <c r="B72" t="n">
-        <v>90782</v>
+        <v>5166</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8640,30 +8639,36 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8671,10 +8676,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>478289</v>
+        <v>478280</v>
       </c>
       <c r="R72" t="n">
-        <v>6770849</v>
+        <v>6770778</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8734,10 +8739,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118012486</v>
+        <v>118012651</v>
       </c>
       <c r="B73" t="n">
-        <v>97836</v>
+        <v>57288</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8746,39 +8751,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -8786,10 +8787,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>478326</v>
+        <v>478346</v>
       </c>
       <c r="R73" t="n">
-        <v>6770688</v>
+        <v>6771016</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8830,7 +8831,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8849,10 +8849,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118012157</v>
+        <v>118012341</v>
       </c>
       <c r="B74" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8897,10 +8897,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>478319</v>
+        <v>478313</v>
       </c>
       <c r="R74" t="n">
-        <v>6770865</v>
+        <v>6770775</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8959,10 +8959,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118012333</v>
+        <v>118012384</v>
       </c>
       <c r="B75" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>478303</v>
+        <v>478275</v>
       </c>
       <c r="R75" t="n">
-        <v>6770765</v>
+        <v>6770755</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -9069,10 +9069,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118012512</v>
+        <v>118012604</v>
       </c>
       <c r="B76" t="n">
-        <v>57287</v>
+        <v>57304</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9085,16 +9085,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9117,10 +9117,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>478343</v>
+        <v>478425</v>
       </c>
       <c r="R76" t="n">
-        <v>6770636</v>
+        <v>6770887</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>

--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -2823,10 +2823,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117987719</v>
+        <v>117992041</v>
       </c>
       <c r="B20" t="n">
-        <v>57931</v>
+        <v>97838</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2835,60 +2835,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103042</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lisselheds badplats (Lisselheds badplats), Dlr</t>
+          <t>Löva strand, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478256</v>
+        <v>478332</v>
       </c>
       <c r="R20" t="n">
-        <v>6771182</v>
+        <v>6770725</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2912,22 +2897,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2936,6 +2911,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2947,17 +2923,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117992041</v>
+        <v>117987719</v>
       </c>
       <c r="B21" t="n">
-        <v>97838</v>
+        <v>57931</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2966,45 +2942,60 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103042</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Löva strand, Dlr</t>
+          <t>Lisselheds badplats (Lisselheds badplats), Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478332</v>
+        <v>478256</v>
       </c>
       <c r="R21" t="n">
-        <v>6770725</v>
+        <v>6771182</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3028,12 +3019,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3042,7 +3043,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3389,10 +3389,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117991376</v>
+        <v>117991939</v>
       </c>
       <c r="B25" t="n">
-        <v>97838</v>
+        <v>97872</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3401,37 +3401,29 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3441,13 +3433,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478377</v>
+        <v>478272</v>
       </c>
       <c r="R25" t="n">
-        <v>6770482</v>
+        <v>6770612</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3471,12 +3463,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3504,10 +3496,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117991939</v>
+        <v>117991376</v>
       </c>
       <c r="B26" t="n">
-        <v>97872</v>
+        <v>97838</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3516,29 +3508,37 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3548,13 +3548,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478272</v>
+        <v>478377</v>
       </c>
       <c r="R26" t="n">
-        <v>6770612</v>
+        <v>6770482</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3730,10 +3730,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117991161</v>
+        <v>117991494</v>
       </c>
       <c r="B28" t="n">
-        <v>91774</v>
+        <v>97838</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3742,38 +3742,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3781,13 +3782,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478342</v>
+        <v>478291</v>
       </c>
       <c r="R28" t="n">
-        <v>6770431</v>
+        <v>6770386</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3844,10 +3845,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117991494</v>
+        <v>117991161</v>
       </c>
       <c r="B29" t="n">
-        <v>97838</v>
+        <v>91774</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3856,39 +3857,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3896,13 +3896,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>478291</v>
+        <v>478342</v>
       </c>
       <c r="R29" t="n">
-        <v>6770386</v>
+        <v>6770431</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117991967</v>
+        <v>117991442</v>
       </c>
       <c r="B30" t="n">
-        <v>97742</v>
+        <v>97838</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3971,29 +3971,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -4003,13 +4011,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>478279</v>
+        <v>478300</v>
       </c>
       <c r="R30" t="n">
-        <v>6770619</v>
+        <v>6770395</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4033,12 +4041,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4066,10 +4074,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117991442</v>
+        <v>117991967</v>
       </c>
       <c r="B31" t="n">
-        <v>97838</v>
+        <v>97742</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4078,37 +4086,29 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -4118,13 +4118,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>478300</v>
+        <v>478279</v>
       </c>
       <c r="R31" t="n">
-        <v>6770395</v>
+        <v>6770619</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4181,10 +4181,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117987499</v>
+        <v>117992010</v>
       </c>
       <c r="B32" t="n">
-        <v>57722</v>
+        <v>97838</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4193,50 +4193,45 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102999</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lisselheds badplats (Lisselheds badplats), Dlr</t>
+          <t>Löva strand, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>478305</v>
+        <v>478333</v>
       </c>
       <c r="R32" t="n">
-        <v>6771072</v>
+        <v>6770705</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4260,22 +4255,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2010-06-24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4284,6 +4269,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4295,17 +4281,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117992010</v>
+        <v>117987499</v>
       </c>
       <c r="B33" t="n">
-        <v>97838</v>
+        <v>57722</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4314,45 +4300,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>102999</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Löva strand, Dlr</t>
+          <t>Lisselheds badplats (Lisselheds badplats), Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>478333</v>
+        <v>478305</v>
       </c>
       <c r="R33" t="n">
-        <v>6770705</v>
+        <v>6771072</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4376,12 +4367,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2010-06-24</t>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4390,7 +4391,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118012651</v>
+        <v>118012604</v>
       </c>
       <c r="B73" t="n">
-        <v>57288</v>
+        <v>57304</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8755,16 +8755,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -8787,10 +8787,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>478346</v>
+        <v>478425</v>
       </c>
       <c r="R73" t="n">
-        <v>6771016</v>
+        <v>6770887</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8849,7 +8849,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118012341</v>
+        <v>118012651</v>
       </c>
       <c r="B74" t="n">
         <v>57288</v>
@@ -8897,10 +8897,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>478313</v>
+        <v>478346</v>
       </c>
       <c r="R74" t="n">
-        <v>6770775</v>
+        <v>6771016</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8959,7 +8959,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118012384</v>
+        <v>118012341</v>
       </c>
       <c r="B75" t="n">
         <v>57288</v>
@@ -9007,10 +9007,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>478275</v>
+        <v>478313</v>
       </c>
       <c r="R75" t="n">
-        <v>6770755</v>
+        <v>6770775</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -9069,10 +9069,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118012604</v>
+        <v>118012384</v>
       </c>
       <c r="B76" t="n">
-        <v>57304</v>
+        <v>57288</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9085,16 +9085,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9117,10 +9117,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>478425</v>
+        <v>478275</v>
       </c>
       <c r="R76" t="n">
-        <v>6770887</v>
+        <v>6770755</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>

--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -9758,10 +9758,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118462616</v>
+        <v>118462737</v>
       </c>
       <c r="B82" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9774,34 +9774,31 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -9809,10 +9806,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>478368</v>
+        <v>478337</v>
       </c>
       <c r="R82" t="n">
-        <v>6770403</v>
+        <v>6770347</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9853,7 +9850,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9872,10 +9868,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118462737</v>
+        <v>118462681</v>
       </c>
       <c r="B83" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9884,35 +9880,39 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9920,10 +9920,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>478337</v>
+        <v>478325</v>
       </c>
       <c r="R83" t="n">
-        <v>6770347</v>
+        <v>6770397</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -9964,6 +9964,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9982,10 +9983,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118463054</v>
+        <v>118462616</v>
       </c>
       <c r="B84" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9994,39 +9995,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>478291</v>
+        <v>478368</v>
       </c>
       <c r="R84" t="n">
-        <v>6770307</v>
+        <v>6770403</v>
       </c>
       <c r="S84" t="n">
         <v>1</v>
@@ -10097,10 +10097,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118462962</v>
+        <v>118463054</v>
       </c>
       <c r="B85" t="n">
-        <v>78518</v>
+        <v>97846</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10109,25 +10109,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -10135,12 +10135,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10148,10 +10149,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>478237</v>
+        <v>478291</v>
       </c>
       <c r="R85" t="n">
-        <v>6770384</v>
+        <v>6770307</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -10211,10 +10212,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118462681</v>
+        <v>118462962</v>
       </c>
       <c r="B86" t="n">
-        <v>97846</v>
+        <v>78518</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10223,25 +10224,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -10249,13 +10250,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10263,10 +10263,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>478325</v>
+        <v>478237</v>
       </c>
       <c r="R86" t="n">
-        <v>6770397</v>
+        <v>6770384</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
@@ -10441,7 +10441,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118463152</v>
+        <v>118462935</v>
       </c>
       <c r="B88" t="n">
         <v>97846</v>
@@ -10493,10 +10493,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>478290</v>
+        <v>478273</v>
       </c>
       <c r="R88" t="n">
-        <v>6770342</v>
+        <v>6770391</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
@@ -10556,7 +10556,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118462935</v>
+        <v>118463012</v>
       </c>
       <c r="B89" t="n">
         <v>97846</v>
@@ -10608,10 +10608,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>478273</v>
+        <v>478293</v>
       </c>
       <c r="R89" t="n">
-        <v>6770391</v>
+        <v>6770323</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
@@ -10671,7 +10671,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118463012</v>
+        <v>118463152</v>
       </c>
       <c r="B90" t="n">
         <v>97846</v>
@@ -10723,10 +10723,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>478293</v>
+        <v>478290</v>
       </c>
       <c r="R90" t="n">
-        <v>6770323</v>
+        <v>6770342</v>
       </c>
       <c r="S90" t="n">
         <v>1</v>
@@ -13106,7 +13106,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>118462168</v>
+        <v>118462083</v>
       </c>
       <c r="B111" t="n">
         <v>97846</v>
@@ -13141,7 +13141,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J111" t="inlineStr"/>
@@ -13158,10 +13158,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>478355</v>
+        <v>478364</v>
       </c>
       <c r="R111" t="n">
-        <v>6770479</v>
+        <v>6770476</v>
       </c>
       <c r="S111" t="n">
         <v>1</v>
@@ -13221,7 +13221,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118462083</v>
+        <v>118462970</v>
       </c>
       <c r="B112" t="n">
         <v>97846</v>
@@ -13273,10 +13273,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>478364</v>
+        <v>478274</v>
       </c>
       <c r="R112" t="n">
-        <v>6770476</v>
+        <v>6770335</v>
       </c>
       <c r="S112" t="n">
         <v>1</v>
@@ -13336,7 +13336,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>118462970</v>
+        <v>118462168</v>
       </c>
       <c r="B113" t="n">
         <v>97846</v>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
@@ -13388,10 +13388,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>478274</v>
+        <v>478355</v>
       </c>
       <c r="R113" t="n">
-        <v>6770335</v>
+        <v>6770479</v>
       </c>
       <c r="S113" t="n">
         <v>1</v>
@@ -14140,7 +14140,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>118462240</v>
+        <v>118462778</v>
       </c>
       <c r="B120" t="n">
         <v>97846</v>
@@ -14175,14 +14175,10 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -14196,10 +14192,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>478367</v>
+        <v>478284</v>
       </c>
       <c r="R120" t="n">
-        <v>6770508</v>
+        <v>6770403</v>
       </c>
       <c r="S120" t="n">
         <v>1</v>
@@ -14259,7 +14255,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>118462365</v>
+        <v>118462794</v>
       </c>
       <c r="B121" t="n">
         <v>97846</v>
@@ -14311,10 +14307,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>478405</v>
+        <v>478284</v>
       </c>
       <c r="R121" t="n">
-        <v>6770539</v>
+        <v>6770396</v>
       </c>
       <c r="S121" t="n">
         <v>1</v>
@@ -14374,7 +14370,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>118462763</v>
+        <v>118462240</v>
       </c>
       <c r="B122" t="n">
         <v>97846</v>
@@ -14409,10 +14405,14 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K122" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -14426,10 +14426,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>478290</v>
+        <v>478367</v>
       </c>
       <c r="R122" t="n">
-        <v>6770394</v>
+        <v>6770508</v>
       </c>
       <c r="S122" t="n">
         <v>1</v>
@@ -14489,7 +14489,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118462117</v>
+        <v>118462365</v>
       </c>
       <c r="B123" t="n">
         <v>97846</v>
@@ -14524,7 +14524,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J123" t="inlineStr"/>
@@ -14541,10 +14541,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>478362</v>
+        <v>478405</v>
       </c>
       <c r="R123" t="n">
-        <v>6770492</v>
+        <v>6770539</v>
       </c>
       <c r="S123" t="n">
         <v>1</v>
@@ -14604,7 +14604,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118462778</v>
+        <v>118462763</v>
       </c>
       <c r="B124" t="n">
         <v>97846</v>
@@ -14656,10 +14656,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>478284</v>
+        <v>478290</v>
       </c>
       <c r="R124" t="n">
-        <v>6770403</v>
+        <v>6770394</v>
       </c>
       <c r="S124" t="n">
         <v>1</v>
@@ -14719,7 +14719,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118462794</v>
+        <v>118462117</v>
       </c>
       <c r="B125" t="n">
         <v>97846</v>
@@ -14754,7 +14754,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
@@ -14771,10 +14771,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>478284</v>
+        <v>478362</v>
       </c>
       <c r="R125" t="n">
-        <v>6770396</v>
+        <v>6770492</v>
       </c>
       <c r="S125" t="n">
         <v>1</v>
@@ -17592,7 +17592,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118462505</v>
+        <v>118463125</v>
       </c>
       <c r="B150" t="n">
         <v>97846</v>
@@ -17644,10 +17644,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>478361</v>
+        <v>478288</v>
       </c>
       <c r="R150" t="n">
-        <v>6770471</v>
+        <v>6770338</v>
       </c>
       <c r="S150" t="n">
         <v>1</v>
@@ -17707,7 +17707,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118463125</v>
+        <v>118462230</v>
       </c>
       <c r="B151" t="n">
         <v>97846</v>
@@ -17745,7 +17745,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K151" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -17759,10 +17763,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>478288</v>
+        <v>478352</v>
       </c>
       <c r="R151" t="n">
-        <v>6770338</v>
+        <v>6770494</v>
       </c>
       <c r="S151" t="n">
         <v>1</v>
@@ -17822,7 +17826,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118462230</v>
+        <v>118462227</v>
       </c>
       <c r="B152" t="n">
         <v>97846</v>
@@ -17878,10 +17882,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>478352</v>
+        <v>478351</v>
       </c>
       <c r="R152" t="n">
-        <v>6770494</v>
+        <v>6770493</v>
       </c>
       <c r="S152" t="n">
         <v>1</v>
@@ -17941,7 +17945,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>118462227</v>
+        <v>118462505</v>
       </c>
       <c r="B153" t="n">
         <v>97846</v>
@@ -17979,11 +17983,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -17997,10 +17997,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>478351</v>
+        <v>478361</v>
       </c>
       <c r="R153" t="n">
-        <v>6770493</v>
+        <v>6770471</v>
       </c>
       <c r="S153" t="n">
         <v>1</v>
@@ -19900,10 +19900,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>118496272</v>
+        <v>118493975</v>
       </c>
       <c r="B170" t="n">
-        <v>97880</v>
+        <v>90504</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -19912,43 +19912,30 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
@@ -19956,10 +19943,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>478288</v>
+        <v>478308</v>
       </c>
       <c r="R170" t="n">
-        <v>6770593</v>
+        <v>6770435</v>
       </c>
       <c r="S170" t="n">
         <v>1</v>
@@ -20019,10 +20006,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>118493975</v>
+        <v>118496272</v>
       </c>
       <c r="B171" t="n">
-        <v>90504</v>
+        <v>97880</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -20031,30 +20018,43 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
@@ -20062,10 +20062,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>478308</v>
+        <v>478288</v>
       </c>
       <c r="R171" t="n">
-        <v>6770435</v>
+        <v>6770593</v>
       </c>
       <c r="S171" t="n">
         <v>1</v>
@@ -22080,7 +22080,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>118495779</v>
+        <v>118495789</v>
       </c>
       <c r="B189" t="n">
         <v>97846</v>
@@ -22132,10 +22132,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>478274</v>
+        <v>478259</v>
       </c>
       <c r="R189" t="n">
-        <v>6770407</v>
+        <v>6770408</v>
       </c>
       <c r="S189" t="n">
         <v>1</v>
@@ -22195,7 +22195,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>118495789</v>
+        <v>118495779</v>
       </c>
       <c r="B190" t="n">
         <v>97846</v>
@@ -22247,10 +22247,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>478259</v>
+        <v>478274</v>
       </c>
       <c r="R190" t="n">
-        <v>6770408</v>
+        <v>6770407</v>
       </c>
       <c r="S190" t="n">
         <v>1</v>
@@ -22310,10 +22310,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>118496309</v>
+        <v>118494225</v>
       </c>
       <c r="B191" t="n">
-        <v>97869</v>
+        <v>97846</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22322,25 +22322,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -22351,7 +22351,7 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L191" t="inlineStr"/>
@@ -22362,10 +22362,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>478334</v>
+        <v>478304</v>
       </c>
       <c r="R191" t="n">
-        <v>6770571</v>
+        <v>6770422</v>
       </c>
       <c r="S191" t="n">
         <v>1</v>
@@ -22425,7 +22425,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>118494225</v>
+        <v>118496227</v>
       </c>
       <c r="B192" t="n">
         <v>97846</v>
@@ -22477,10 +22477,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>478304</v>
+        <v>478308</v>
       </c>
       <c r="R192" t="n">
-        <v>6770422</v>
+        <v>6770574</v>
       </c>
       <c r="S192" t="n">
         <v>1</v>
@@ -22540,10 +22540,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>118496227</v>
+        <v>118496309</v>
       </c>
       <c r="B193" t="n">
-        <v>97846</v>
+        <v>97869</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22552,25 +22552,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -22581,7 +22581,7 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L193" t="inlineStr"/>
@@ -22592,10 +22592,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>478308</v>
+        <v>478334</v>
       </c>
       <c r="R193" t="n">
-        <v>6770574</v>
+        <v>6770571</v>
       </c>
       <c r="S193" t="n">
         <v>1</v>
@@ -23352,10 +23352,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>118493987</v>
+        <v>118494239</v>
       </c>
       <c r="B200" t="n">
-        <v>97846</v>
+        <v>5166</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -23364,39 +23364,36 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
@@ -23404,10 +23401,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>478306</v>
+        <v>478296</v>
       </c>
       <c r="R200" t="n">
-        <v>6770444</v>
+        <v>6770423</v>
       </c>
       <c r="S200" t="n">
         <v>1</v>
@@ -23467,7 +23464,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>118495946</v>
+        <v>118493987</v>
       </c>
       <c r="B201" t="n">
         <v>97846</v>
@@ -23508,7 +23505,7 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L201" t="inlineStr"/>
@@ -23519,10 +23516,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>478291</v>
+        <v>478306</v>
       </c>
       <c r="R201" t="n">
-        <v>6770492</v>
+        <v>6770444</v>
       </c>
       <c r="S201" t="n">
         <v>1</v>
@@ -23582,10 +23579,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>118494239</v>
+        <v>118495946</v>
       </c>
       <c r="B202" t="n">
-        <v>5166</v>
+        <v>97846</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -23594,36 +23591,39 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
@@ -23631,10 +23631,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>478296</v>
+        <v>478291</v>
       </c>
       <c r="R202" t="n">
-        <v>6770423</v>
+        <v>6770492</v>
       </c>
       <c r="S202" t="n">
         <v>1</v>
@@ -24155,10 +24155,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>118494003</v>
+        <v>118494224</v>
       </c>
       <c r="B207" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -24167,35 +24167,39 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
@@ -24203,10 +24207,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>478303</v>
+        <v>478309</v>
       </c>
       <c r="R207" t="n">
-        <v>6770456</v>
+        <v>6770432</v>
       </c>
       <c r="S207" t="n">
         <v>1</v>
@@ -24247,6 +24251,7 @@
       <c r="AE207" t="b">
         <v>0</v>
       </c>
+      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
@@ -24265,10 +24270,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>118494224</v>
+        <v>118494003</v>
       </c>
       <c r="B208" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -24277,39 +24282,35 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
@@ -24317,10 +24318,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>478309</v>
+        <v>478303</v>
       </c>
       <c r="R208" t="n">
-        <v>6770432</v>
+        <v>6770456</v>
       </c>
       <c r="S208" t="n">
         <v>1</v>
@@ -24361,7 +24362,6 @@
       <c r="AE208" t="b">
         <v>0</v>
       </c>
-      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
@@ -26546,7 +26546,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>118552177</v>
+        <v>118551875</v>
       </c>
       <c r="B228" t="n">
         <v>97846</v>
@@ -26598,10 +26598,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>478368</v>
+        <v>478327</v>
       </c>
       <c r="R228" t="n">
-        <v>6770798</v>
+        <v>6770718</v>
       </c>
       <c r="S228" t="n">
         <v>1</v>
@@ -26642,6 +26642,7 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
+      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -26660,7 +26661,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>118551875</v>
+        <v>118551811</v>
       </c>
       <c r="B229" t="n">
         <v>97846</v>
@@ -26712,10 +26713,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>478327</v>
+        <v>478343</v>
       </c>
       <c r="R229" t="n">
-        <v>6770718</v>
+        <v>6770689</v>
       </c>
       <c r="S229" t="n">
         <v>1</v>
@@ -26756,7 +26757,6 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
-      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
       </c>
@@ -26775,7 +26775,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>118551811</v>
+        <v>118552203</v>
       </c>
       <c r="B230" t="n">
         <v>97846</v>
@@ -26827,10 +26827,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>478343</v>
+        <v>478351</v>
       </c>
       <c r="R230" t="n">
-        <v>6770689</v>
+        <v>6770795</v>
       </c>
       <c r="S230" t="n">
         <v>1</v>
@@ -26889,7 +26889,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>118551266</v>
+        <v>118552684</v>
       </c>
       <c r="B231" t="n">
         <v>97846</v>
@@ -26941,10 +26941,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>478361</v>
+        <v>478471</v>
       </c>
       <c r="R231" t="n">
-        <v>6770574</v>
+        <v>6770711</v>
       </c>
       <c r="S231" t="n">
         <v>1</v>
@@ -26997,14 +26997,14 @@
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>118551455</v>
+        <v>118552177</v>
       </c>
       <c r="B232" t="n">
         <v>97846</v>
@@ -27056,10 +27056,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>478332</v>
+        <v>478368</v>
       </c>
       <c r="R232" t="n">
-        <v>6770666</v>
+        <v>6770798</v>
       </c>
       <c r="S232" t="n">
         <v>1</v>
@@ -27118,7 +27118,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>118552162</v>
+        <v>118551266</v>
       </c>
       <c r="B233" t="n">
         <v>97846</v>
@@ -27153,7 +27153,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J233" t="inlineStr"/>
@@ -27170,10 +27170,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>478349</v>
+        <v>478361</v>
       </c>
       <c r="R233" t="n">
-        <v>6770751</v>
+        <v>6770574</v>
       </c>
       <c r="S233" t="n">
         <v>1</v>
@@ -27214,6 +27214,7 @@
       <c r="AE233" t="b">
         <v>0</v>
       </c>
+      <c r="AF233" t="inlineStr"/>
       <c r="AG233" t="b">
         <v>0</v>
       </c>
@@ -27225,14 +27226,14 @@
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>118552724</v>
+        <v>118551455</v>
       </c>
       <c r="B234" t="n">
         <v>97846</v>
@@ -27284,10 +27285,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>478468</v>
+        <v>478332</v>
       </c>
       <c r="R234" t="n">
-        <v>6770769</v>
+        <v>6770666</v>
       </c>
       <c r="S234" t="n">
         <v>1</v>
@@ -27328,7 +27329,6 @@
       <c r="AE234" t="b">
         <v>0</v>
       </c>
-      <c r="AF234" t="inlineStr"/>
       <c r="AG234" t="b">
         <v>0</v>
       </c>
@@ -27347,7 +27347,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>118552203</v>
+        <v>118552162</v>
       </c>
       <c r="B235" t="n">
         <v>97846</v>
@@ -27382,7 +27382,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J235" t="inlineStr"/>
@@ -27399,10 +27399,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>478351</v>
+        <v>478349</v>
       </c>
       <c r="R235" t="n">
-        <v>6770795</v>
+        <v>6770751</v>
       </c>
       <c r="S235" t="n">
         <v>1</v>
@@ -27461,7 +27461,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>118552684</v>
+        <v>118552724</v>
       </c>
       <c r="B236" t="n">
         <v>97846</v>
@@ -27513,10 +27513,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>478471</v>
+        <v>478468</v>
       </c>
       <c r="R236" t="n">
-        <v>6770711</v>
+        <v>6770769</v>
       </c>
       <c r="S236" t="n">
         <v>1</v>
@@ -28265,7 +28265,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>118553013</v>
+        <v>118551829</v>
       </c>
       <c r="B243" t="n">
         <v>97846</v>
@@ -28300,7 +28300,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J243" t="inlineStr"/>
@@ -28317,10 +28317,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>478467</v>
+        <v>478353</v>
       </c>
       <c r="R243" t="n">
-        <v>6770793</v>
+        <v>6770681</v>
       </c>
       <c r="S243" t="n">
         <v>1</v>
@@ -28380,7 +28380,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>118552038</v>
+        <v>118551541</v>
       </c>
       <c r="B244" t="n">
         <v>97846</v>
@@ -28415,7 +28415,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J244" t="inlineStr"/>
@@ -28432,10 +28432,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>478391</v>
+        <v>478311</v>
       </c>
       <c r="R244" t="n">
-        <v>6770726</v>
+        <v>6770690</v>
       </c>
       <c r="S244" t="n">
         <v>1</v>
@@ -28494,7 +28494,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>118551980</v>
+        <v>118552953</v>
       </c>
       <c r="B245" t="n">
         <v>97846</v>
@@ -28546,10 +28546,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>478352</v>
+        <v>478438</v>
       </c>
       <c r="R245" t="n">
-        <v>6770670</v>
+        <v>6770852</v>
       </c>
       <c r="S245" t="n">
         <v>1</v>
@@ -28609,7 +28609,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>118551829</v>
+        <v>118552046</v>
       </c>
       <c r="B246" t="n">
         <v>97846</v>
@@ -28661,10 +28661,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>478353</v>
+        <v>478407</v>
       </c>
       <c r="R246" t="n">
-        <v>6770681</v>
+        <v>6770699</v>
       </c>
       <c r="S246" t="n">
         <v>1</v>
@@ -28705,7 +28705,6 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
-      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
@@ -28724,7 +28723,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>118551541</v>
+        <v>118553013</v>
       </c>
       <c r="B247" t="n">
         <v>97846</v>
@@ -28776,10 +28775,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>478311</v>
+        <v>478467</v>
       </c>
       <c r="R247" t="n">
-        <v>6770690</v>
+        <v>6770793</v>
       </c>
       <c r="S247" t="n">
         <v>1</v>
@@ -28820,6 +28819,7 @@
       <c r="AE247" t="b">
         <v>0</v>
       </c>
+      <c r="AF247" t="inlineStr"/>
       <c r="AG247" t="b">
         <v>0</v>
       </c>
@@ -28838,7 +28838,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>118552953</v>
+        <v>118552038</v>
       </c>
       <c r="B248" t="n">
         <v>97846</v>
@@ -28873,7 +28873,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J248" t="inlineStr"/>
@@ -28890,10 +28890,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>478438</v>
+        <v>478391</v>
       </c>
       <c r="R248" t="n">
-        <v>6770852</v>
+        <v>6770726</v>
       </c>
       <c r="S248" t="n">
         <v>1</v>
@@ -28934,7 +28934,6 @@
       <c r="AE248" t="b">
         <v>0</v>
       </c>
-      <c r="AF248" t="inlineStr"/>
       <c r="AG248" t="b">
         <v>0</v>
       </c>
@@ -28953,7 +28952,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>118552046</v>
+        <v>118551980</v>
       </c>
       <c r="B249" t="n">
         <v>97846</v>
@@ -28988,7 +28987,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J249" t="inlineStr"/>
@@ -29005,10 +29004,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>478407</v>
+        <v>478352</v>
       </c>
       <c r="R249" t="n">
-        <v>6770699</v>
+        <v>6770670</v>
       </c>
       <c r="S249" t="n">
         <v>1</v>
@@ -29049,6 +29048,7 @@
       <c r="AE249" t="b">
         <v>0</v>
       </c>
+      <c r="AF249" t="inlineStr"/>
       <c r="AG249" t="b">
         <v>0</v>
       </c>
@@ -29067,10 +29067,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>118553085</v>
+        <v>118551450</v>
       </c>
       <c r="B250" t="n">
-        <v>57443</v>
+        <v>97846</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -29079,35 +29079,39 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr"/>
-      <c r="K250" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr"/>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
@@ -29115,13 +29119,13 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>478361</v>
+        <v>478331</v>
       </c>
       <c r="R250" t="n">
-        <v>6770534</v>
+        <v>6770654</v>
       </c>
       <c r="S250" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -29177,10 +29181,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>118551450</v>
+        <v>118553085</v>
       </c>
       <c r="B251" t="n">
-        <v>97846</v>
+        <v>57443</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -29189,39 +29193,35 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr"/>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
@@ -29229,13 +29229,13 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>478331</v>
+        <v>478361</v>
       </c>
       <c r="R251" t="n">
-        <v>6770654</v>
+        <v>6770534</v>
       </c>
       <c r="S251" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>118551889</v>
+        <v>118551379</v>
       </c>
       <c r="B319" t="n">
         <v>97846</v>
@@ -37017,10 +37017,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>478330</v>
+        <v>478326</v>
       </c>
       <c r="R319" t="n">
-        <v>6770712</v>
+        <v>6770611</v>
       </c>
       <c r="S319" t="n">
         <v>1</v>
@@ -37061,7 +37061,6 @@
       <c r="AE319" t="b">
         <v>0</v>
       </c>
-      <c r="AF319" t="inlineStr"/>
       <c r="AG319" t="b">
         <v>0</v>
       </c>
@@ -37080,7 +37079,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>118551379</v>
+        <v>118551889</v>
       </c>
       <c r="B320" t="n">
         <v>97846</v>
@@ -37132,10 +37131,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>478326</v>
+        <v>478330</v>
       </c>
       <c r="R320" t="n">
-        <v>6770611</v>
+        <v>6770712</v>
       </c>
       <c r="S320" t="n">
         <v>1</v>
@@ -37176,6 +37175,7 @@
       <c r="AE320" t="b">
         <v>0</v>
       </c>
+      <c r="AF320" t="inlineStr"/>
       <c r="AG320" t="b">
         <v>0</v>
       </c>
@@ -45331,10 +45331,10 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>118552054</v>
+        <v>118552221</v>
       </c>
       <c r="B392" t="n">
-        <v>78518</v>
+        <v>97846</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
@@ -45343,25 +45343,25 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -45369,12 +45369,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J392" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="J392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr"/>
       <c r="N392" t="inlineStr"/>
       <c r="P392" t="inlineStr">
         <is>
@@ -45382,10 +45383,10 @@
         </is>
       </c>
       <c r="Q392" t="n">
-        <v>478407</v>
+        <v>478277</v>
       </c>
       <c r="R392" t="n">
-        <v>6770699</v>
+        <v>6770726</v>
       </c>
       <c r="S392" t="n">
         <v>1</v>
@@ -45444,7 +45445,7 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>118552221</v>
+        <v>118552128</v>
       </c>
       <c r="B393" t="n">
         <v>97846</v>
@@ -45496,10 +45497,10 @@
         </is>
       </c>
       <c r="Q393" t="n">
-        <v>478277</v>
+        <v>478363</v>
       </c>
       <c r="R393" t="n">
-        <v>6770726</v>
+        <v>6770718</v>
       </c>
       <c r="S393" t="n">
         <v>1</v>
@@ -45558,7 +45559,7 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>118552128</v>
+        <v>118552217</v>
       </c>
       <c r="B394" t="n">
         <v>97846</v>
@@ -45610,10 +45611,10 @@
         </is>
       </c>
       <c r="Q394" t="n">
-        <v>478363</v>
+        <v>478288</v>
       </c>
       <c r="R394" t="n">
-        <v>6770718</v>
+        <v>6770773</v>
       </c>
       <c r="S394" t="n">
         <v>1</v>
@@ -45672,7 +45673,7 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>118552217</v>
+        <v>118551345</v>
       </c>
       <c r="B395" t="n">
         <v>97846</v>
@@ -45724,10 +45725,10 @@
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>478288</v>
+        <v>478317</v>
       </c>
       <c r="R395" t="n">
-        <v>6770773</v>
+        <v>6770651</v>
       </c>
       <c r="S395" t="n">
         <v>1</v>
@@ -45786,7 +45787,7 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>118551345</v>
+        <v>118552370</v>
       </c>
       <c r="B396" t="n">
         <v>97846</v>
@@ -45838,10 +45839,10 @@
         </is>
       </c>
       <c r="Q396" t="n">
-        <v>478317</v>
+        <v>478292</v>
       </c>
       <c r="R396" t="n">
-        <v>6770651</v>
+        <v>6770602</v>
       </c>
       <c r="S396" t="n">
         <v>1</v>
@@ -45882,6 +45883,7 @@
       <c r="AE396" t="b">
         <v>0</v>
       </c>
+      <c r="AF396" t="inlineStr"/>
       <c r="AG396" t="b">
         <v>0</v>
       </c>
@@ -45900,7 +45902,7 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>118552370</v>
+        <v>118552524</v>
       </c>
       <c r="B397" t="n">
         <v>97846</v>
@@ -45941,7 +45943,7 @@
       <c r="J397" t="inlineStr"/>
       <c r="K397" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L397" t="inlineStr"/>
@@ -45952,10 +45954,10 @@
         </is>
       </c>
       <c r="Q397" t="n">
-        <v>478292</v>
+        <v>478415</v>
       </c>
       <c r="R397" t="n">
-        <v>6770602</v>
+        <v>6770617</v>
       </c>
       <c r="S397" t="n">
         <v>1</v>
@@ -46015,10 +46017,10 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>118552524</v>
+        <v>118552054</v>
       </c>
       <c r="B398" t="n">
-        <v>97846</v>
+        <v>78518</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
@@ -46027,25 +46029,25 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E398" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -46053,13 +46055,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J398" t="inlineStr"/>
-      <c r="K398" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L398" t="inlineStr"/>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr"/>
       <c r="N398" t="inlineStr"/>
       <c r="P398" t="inlineStr">
         <is>
@@ -46067,10 +46068,10 @@
         </is>
       </c>
       <c r="Q398" t="n">
-        <v>478415</v>
+        <v>478407</v>
       </c>
       <c r="R398" t="n">
-        <v>6770617</v>
+        <v>6770699</v>
       </c>
       <c r="S398" t="n">
         <v>1</v>
@@ -46111,7 +46112,6 @@
       <c r="AE398" t="b">
         <v>0</v>
       </c>
-      <c r="AF398" t="inlineStr"/>
       <c r="AG398" t="b">
         <v>0</v>
       </c>
@@ -48538,7 +48538,7 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>118568275</v>
+        <v>118568655</v>
       </c>
       <c r="B420" t="n">
         <v>97846</v>
@@ -48573,7 +48573,7 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J420" t="inlineStr"/>
@@ -48590,10 +48590,10 @@
         </is>
       </c>
       <c r="Q420" t="n">
-        <v>478318</v>
+        <v>478296</v>
       </c>
       <c r="R420" t="n">
-        <v>6770987</v>
+        <v>6770864</v>
       </c>
       <c r="S420" t="n">
         <v>1</v>
@@ -48653,7 +48653,7 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>118568655</v>
+        <v>118568340</v>
       </c>
       <c r="B421" t="n">
         <v>97846</v>
@@ -48688,7 +48688,7 @@
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J421" t="inlineStr"/>
@@ -48705,10 +48705,10 @@
         </is>
       </c>
       <c r="Q421" t="n">
-        <v>478296</v>
+        <v>478318</v>
       </c>
       <c r="R421" t="n">
-        <v>6770864</v>
+        <v>6770982</v>
       </c>
       <c r="S421" t="n">
         <v>1</v>
@@ -48768,7 +48768,7 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>118568340</v>
+        <v>118568192</v>
       </c>
       <c r="B422" t="n">
         <v>97846</v>
@@ -48820,10 +48820,10 @@
         </is>
       </c>
       <c r="Q422" t="n">
-        <v>478318</v>
+        <v>478334</v>
       </c>
       <c r="R422" t="n">
-        <v>6770982</v>
+        <v>6770878</v>
       </c>
       <c r="S422" t="n">
         <v>1</v>
@@ -48883,7 +48883,7 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>118568192</v>
+        <v>118568342</v>
       </c>
       <c r="B423" t="n">
         <v>97846</v>
@@ -48935,10 +48935,10 @@
         </is>
       </c>
       <c r="Q423" t="n">
-        <v>478334</v>
+        <v>478320</v>
       </c>
       <c r="R423" t="n">
-        <v>6770878</v>
+        <v>6770982</v>
       </c>
       <c r="S423" t="n">
         <v>1</v>
@@ -48998,7 +48998,7 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>118568342</v>
+        <v>118568275</v>
       </c>
       <c r="B424" t="n">
         <v>97846</v>
@@ -49033,7 +49033,7 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J424" t="inlineStr"/>
@@ -49050,10 +49050,10 @@
         </is>
       </c>
       <c r="Q424" t="n">
-        <v>478320</v>
+        <v>478318</v>
       </c>
       <c r="R424" t="n">
-        <v>6770982</v>
+        <v>6770987</v>
       </c>
       <c r="S424" t="n">
         <v>1</v>

--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -10441,7 +10441,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>118462935</v>
+        <v>118463152</v>
       </c>
       <c r="B88" t="n">
         <v>97846</v>
@@ -10493,10 +10493,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>478273</v>
+        <v>478290</v>
       </c>
       <c r="R88" t="n">
-        <v>6770391</v>
+        <v>6770342</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
@@ -10556,7 +10556,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>118463012</v>
+        <v>118462935</v>
       </c>
       <c r="B89" t="n">
         <v>97846</v>
@@ -10608,10 +10608,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>478293</v>
+        <v>478273</v>
       </c>
       <c r="R89" t="n">
-        <v>6770323</v>
+        <v>6770391</v>
       </c>
       <c r="S89" t="n">
         <v>1</v>
@@ -10671,7 +10671,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>118463152</v>
+        <v>118463012</v>
       </c>
       <c r="B90" t="n">
         <v>97846</v>
@@ -10723,10 +10723,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>478290</v>
+        <v>478293</v>
       </c>
       <c r="R90" t="n">
-        <v>6770342</v>
+        <v>6770323</v>
       </c>
       <c r="S90" t="n">
         <v>1</v>
@@ -16222,7 +16222,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118462943</v>
+        <v>118462377</v>
       </c>
       <c r="B138" t="n">
         <v>97846</v>
@@ -16274,10 +16274,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>478245</v>
+        <v>478415</v>
       </c>
       <c r="R138" t="n">
-        <v>6770383</v>
+        <v>6770518</v>
       </c>
       <c r="S138" t="n">
         <v>1</v>
@@ -16337,7 +16337,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118462984</v>
+        <v>118462943</v>
       </c>
       <c r="B139" t="n">
         <v>97846</v>
@@ -16389,10 +16389,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>478285</v>
+        <v>478245</v>
       </c>
       <c r="R139" t="n">
-        <v>6770323</v>
+        <v>6770383</v>
       </c>
       <c r="S139" t="n">
         <v>1</v>
@@ -16452,7 +16452,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118462377</v>
+        <v>118462984</v>
       </c>
       <c r="B140" t="n">
         <v>97846</v>
@@ -16504,10 +16504,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>478415</v>
+        <v>478285</v>
       </c>
       <c r="R140" t="n">
-        <v>6770518</v>
+        <v>6770323</v>
       </c>
       <c r="S140" t="n">
         <v>1</v>
@@ -17592,7 +17592,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118463125</v>
+        <v>118462505</v>
       </c>
       <c r="B150" t="n">
         <v>97846</v>
@@ -17644,10 +17644,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>478288</v>
+        <v>478361</v>
       </c>
       <c r="R150" t="n">
-        <v>6770338</v>
+        <v>6770471</v>
       </c>
       <c r="S150" t="n">
         <v>1</v>
@@ -17707,7 +17707,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118462230</v>
+        <v>118463125</v>
       </c>
       <c r="B151" t="n">
         <v>97846</v>
@@ -17745,11 +17745,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -17763,10 +17759,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>478352</v>
+        <v>478288</v>
       </c>
       <c r="R151" t="n">
-        <v>6770494</v>
+        <v>6770338</v>
       </c>
       <c r="S151" t="n">
         <v>1</v>
@@ -17826,7 +17822,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118462227</v>
+        <v>118462230</v>
       </c>
       <c r="B152" t="n">
         <v>97846</v>
@@ -17882,10 +17878,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>478351</v>
+        <v>478352</v>
       </c>
       <c r="R152" t="n">
-        <v>6770493</v>
+        <v>6770494</v>
       </c>
       <c r="S152" t="n">
         <v>1</v>
@@ -17945,7 +17941,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>118462505</v>
+        <v>118462227</v>
       </c>
       <c r="B153" t="n">
         <v>97846</v>
@@ -17983,7 +17979,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr"/>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K153" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -17997,10 +17997,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>478361</v>
+        <v>478351</v>
       </c>
       <c r="R153" t="n">
-        <v>6770471</v>
+        <v>6770493</v>
       </c>
       <c r="S153" t="n">
         <v>1</v>
@@ -22080,7 +22080,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>118495789</v>
+        <v>118495779</v>
       </c>
       <c r="B189" t="n">
         <v>97846</v>
@@ -22132,10 +22132,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>478259</v>
+        <v>478274</v>
       </c>
       <c r="R189" t="n">
-        <v>6770408</v>
+        <v>6770407</v>
       </c>
       <c r="S189" t="n">
         <v>1</v>
@@ -22195,7 +22195,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>118495779</v>
+        <v>118495789</v>
       </c>
       <c r="B190" t="n">
         <v>97846</v>
@@ -22247,10 +22247,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>478274</v>
+        <v>478259</v>
       </c>
       <c r="R190" t="n">
-        <v>6770407</v>
+        <v>6770408</v>
       </c>
       <c r="S190" t="n">
         <v>1</v>
@@ -22310,10 +22310,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>118494225</v>
+        <v>118496309</v>
       </c>
       <c r="B191" t="n">
-        <v>97846</v>
+        <v>97869</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -22322,25 +22322,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -22351,7 +22351,7 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L191" t="inlineStr"/>
@@ -22362,10 +22362,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>478304</v>
+        <v>478334</v>
       </c>
       <c r="R191" t="n">
-        <v>6770422</v>
+        <v>6770571</v>
       </c>
       <c r="S191" t="n">
         <v>1</v>
@@ -22425,7 +22425,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>118496227</v>
+        <v>118494225</v>
       </c>
       <c r="B192" t="n">
         <v>97846</v>
@@ -22477,10 +22477,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>478308</v>
+        <v>478304</v>
       </c>
       <c r="R192" t="n">
-        <v>6770574</v>
+        <v>6770422</v>
       </c>
       <c r="S192" t="n">
         <v>1</v>
@@ -22540,10 +22540,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>118496309</v>
+        <v>118496227</v>
       </c>
       <c r="B193" t="n">
-        <v>97869</v>
+        <v>97846</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -22552,25 +22552,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -22581,7 +22581,7 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L193" t="inlineStr"/>
@@ -22592,10 +22592,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>478334</v>
+        <v>478308</v>
       </c>
       <c r="R193" t="n">
-        <v>6770571</v>
+        <v>6770574</v>
       </c>
       <c r="S193" t="n">
         <v>1</v>
@@ -23352,10 +23352,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>118494239</v>
+        <v>118493987</v>
       </c>
       <c r="B200" t="n">
-        <v>5166</v>
+        <v>97846</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -23364,36 +23364,39 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
@@ -23401,10 +23404,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>478296</v>
+        <v>478306</v>
       </c>
       <c r="R200" t="n">
-        <v>6770423</v>
+        <v>6770444</v>
       </c>
       <c r="S200" t="n">
         <v>1</v>
@@ -23464,7 +23467,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>118493987</v>
+        <v>118495946</v>
       </c>
       <c r="B201" t="n">
         <v>97846</v>
@@ -23505,7 +23508,7 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L201" t="inlineStr"/>
@@ -23516,10 +23519,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>478306</v>
+        <v>478291</v>
       </c>
       <c r="R201" t="n">
-        <v>6770444</v>
+        <v>6770492</v>
       </c>
       <c r="S201" t="n">
         <v>1</v>
@@ -23579,10 +23582,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>118495946</v>
+        <v>118494239</v>
       </c>
       <c r="B202" t="n">
-        <v>97846</v>
+        <v>5166</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -23591,39 +23594,36 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
@@ -23631,10 +23631,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>478291</v>
+        <v>478296</v>
       </c>
       <c r="R202" t="n">
-        <v>6770492</v>
+        <v>6770423</v>
       </c>
       <c r="S202" t="n">
         <v>1</v>
@@ -24155,10 +24155,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>118494224</v>
+        <v>118494003</v>
       </c>
       <c r="B207" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -24167,39 +24167,35 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
@@ -24207,10 +24203,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>478309</v>
+        <v>478303</v>
       </c>
       <c r="R207" t="n">
-        <v>6770432</v>
+        <v>6770456</v>
       </c>
       <c r="S207" t="n">
         <v>1</v>
@@ -24251,7 +24247,6 @@
       <c r="AE207" t="b">
         <v>0</v>
       </c>
-      <c r="AF207" t="inlineStr"/>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
@@ -24270,10 +24265,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>118494003</v>
+        <v>118494224</v>
       </c>
       <c r="B208" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -24282,35 +24277,39 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
@@ -24318,10 +24317,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>478303</v>
+        <v>478309</v>
       </c>
       <c r="R208" t="n">
-        <v>6770456</v>
+        <v>6770432</v>
       </c>
       <c r="S208" t="n">
         <v>1</v>
@@ -24362,6 +24361,7 @@
       <c r="AE208" t="b">
         <v>0</v>
       </c>
+      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
@@ -26546,7 +26546,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>118551875</v>
+        <v>118552177</v>
       </c>
       <c r="B228" t="n">
         <v>97846</v>
@@ -26598,10 +26598,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>478327</v>
+        <v>478368</v>
       </c>
       <c r="R228" t="n">
-        <v>6770718</v>
+        <v>6770798</v>
       </c>
       <c r="S228" t="n">
         <v>1</v>
@@ -26642,7 +26642,6 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -26661,7 +26660,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>118551811</v>
+        <v>118551875</v>
       </c>
       <c r="B229" t="n">
         <v>97846</v>
@@ -26713,10 +26712,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>478343</v>
+        <v>478327</v>
       </c>
       <c r="R229" t="n">
-        <v>6770689</v>
+        <v>6770718</v>
       </c>
       <c r="S229" t="n">
         <v>1</v>
@@ -26757,6 +26756,7 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
+      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
       </c>
@@ -26775,7 +26775,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>118552203</v>
+        <v>118551811</v>
       </c>
       <c r="B230" t="n">
         <v>97846</v>
@@ -26827,10 +26827,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>478351</v>
+        <v>478343</v>
       </c>
       <c r="R230" t="n">
-        <v>6770795</v>
+        <v>6770689</v>
       </c>
       <c r="S230" t="n">
         <v>1</v>
@@ -26889,7 +26889,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>118552684</v>
+        <v>118551266</v>
       </c>
       <c r="B231" t="n">
         <v>97846</v>
@@ -26941,10 +26941,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>478471</v>
+        <v>478361</v>
       </c>
       <c r="R231" t="n">
-        <v>6770711</v>
+        <v>6770574</v>
       </c>
       <c r="S231" t="n">
         <v>1</v>
@@ -26997,14 +26997,14 @@
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>118552177</v>
+        <v>118551455</v>
       </c>
       <c r="B232" t="n">
         <v>97846</v>
@@ -27056,10 +27056,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>478368</v>
+        <v>478332</v>
       </c>
       <c r="R232" t="n">
-        <v>6770798</v>
+        <v>6770666</v>
       </c>
       <c r="S232" t="n">
         <v>1</v>
@@ -27118,7 +27118,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>118551266</v>
+        <v>118552162</v>
       </c>
       <c r="B233" t="n">
         <v>97846</v>
@@ -27153,7 +27153,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J233" t="inlineStr"/>
@@ -27170,10 +27170,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>478361</v>
+        <v>478349</v>
       </c>
       <c r="R233" t="n">
-        <v>6770574</v>
+        <v>6770751</v>
       </c>
       <c r="S233" t="n">
         <v>1</v>
@@ -27214,7 +27214,6 @@
       <c r="AE233" t="b">
         <v>0</v>
       </c>
-      <c r="AF233" t="inlineStr"/>
       <c r="AG233" t="b">
         <v>0</v>
       </c>
@@ -27226,14 +27225,14 @@
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>118551455</v>
+        <v>118552724</v>
       </c>
       <c r="B234" t="n">
         <v>97846</v>
@@ -27285,10 +27284,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>478332</v>
+        <v>478468</v>
       </c>
       <c r="R234" t="n">
-        <v>6770666</v>
+        <v>6770769</v>
       </c>
       <c r="S234" t="n">
         <v>1</v>
@@ -27329,6 +27328,7 @@
       <c r="AE234" t="b">
         <v>0</v>
       </c>
+      <c r="AF234" t="inlineStr"/>
       <c r="AG234" t="b">
         <v>0</v>
       </c>
@@ -27347,7 +27347,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>118552162</v>
+        <v>118552203</v>
       </c>
       <c r="B235" t="n">
         <v>97846</v>
@@ -27382,7 +27382,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J235" t="inlineStr"/>
@@ -27399,10 +27399,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>478349</v>
+        <v>478351</v>
       </c>
       <c r="R235" t="n">
-        <v>6770751</v>
+        <v>6770795</v>
       </c>
       <c r="S235" t="n">
         <v>1</v>
@@ -27461,7 +27461,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>118552724</v>
+        <v>118552684</v>
       </c>
       <c r="B236" t="n">
         <v>97846</v>
@@ -27513,10 +27513,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>478468</v>
+        <v>478471</v>
       </c>
       <c r="R236" t="n">
-        <v>6770769</v>
+        <v>6770711</v>
       </c>
       <c r="S236" t="n">
         <v>1</v>

--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -15069,10 +15069,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118462660</v>
+        <v>118462702</v>
       </c>
       <c r="B128" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15081,30 +15081,43 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
@@ -15112,10 +15125,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>478311</v>
+        <v>478309</v>
       </c>
       <c r="R128" t="n">
-        <v>6770344</v>
+        <v>6770345</v>
       </c>
       <c r="S128" t="n">
         <v>1</v>
@@ -15175,7 +15188,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118462702</v>
+        <v>118462763</v>
       </c>
       <c r="B129" t="n">
         <v>97846</v>
@@ -15213,14 +15226,10 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -15231,10 +15240,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>478309</v>
+        <v>478290</v>
       </c>
       <c r="R129" t="n">
-        <v>6770345</v>
+        <v>6770394</v>
       </c>
       <c r="S129" t="n">
         <v>1</v>
@@ -15294,10 +15303,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118462763</v>
+        <v>118462660</v>
       </c>
       <c r="B130" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15306,39 +15315,30 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -15346,10 +15346,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478290</v>
+        <v>478311</v>
       </c>
       <c r="R130" t="n">
-        <v>6770394</v>
+        <v>6770344</v>
       </c>
       <c r="S130" t="n">
         <v>1</v>
@@ -20015,7 +20015,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>118493993</v>
+        <v>118496200</v>
       </c>
       <c r="B171" t="n">
         <v>97846</v>
@@ -20067,10 +20067,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>478306</v>
+        <v>478281</v>
       </c>
       <c r="R171" t="n">
-        <v>6770453</v>
+        <v>6770576</v>
       </c>
       <c r="S171" t="n">
         <v>1</v>
@@ -20130,7 +20130,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>118496200</v>
+        <v>118493993</v>
       </c>
       <c r="B172" t="n">
         <v>97846</v>
@@ -20182,10 +20182,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>478281</v>
+        <v>478306</v>
       </c>
       <c r="R172" t="n">
-        <v>6770576</v>
+        <v>6770453</v>
       </c>
       <c r="S172" t="n">
         <v>1</v>
@@ -20582,10 +20582,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>118493975</v>
+        <v>118494242</v>
       </c>
       <c r="B176" t="n">
-        <v>90504</v>
+        <v>97846</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -20594,30 +20594,39 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
@@ -20625,10 +20634,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>478308</v>
+        <v>478300</v>
       </c>
       <c r="R176" t="n">
-        <v>6770435</v>
+        <v>6770420</v>
       </c>
       <c r="S176" t="n">
         <v>1</v>
@@ -20688,10 +20697,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>118493978</v>
+        <v>118493975</v>
       </c>
       <c r="B177" t="n">
-        <v>97846</v>
+        <v>90504</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -20700,39 +20709,30 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
@@ -20740,10 +20740,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>478306</v>
+        <v>478308</v>
       </c>
       <c r="R177" t="n">
-        <v>6770436</v>
+        <v>6770435</v>
       </c>
       <c r="S177" t="n">
         <v>1</v>
@@ -20803,10 +20803,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>118494242</v>
+        <v>118496262</v>
       </c>
       <c r="B178" t="n">
-        <v>97846</v>
+        <v>97880</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -20815,36 +20815,40 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L178" t="inlineStr"/>
@@ -20855,10 +20859,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>478300</v>
+        <v>478282</v>
       </c>
       <c r="R178" t="n">
-        <v>6770420</v>
+        <v>6770599</v>
       </c>
       <c r="S178" t="n">
         <v>1</v>
@@ -20918,10 +20922,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>118496262</v>
+        <v>118493978</v>
       </c>
       <c r="B179" t="n">
-        <v>97880</v>
+        <v>97846</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -20930,40 +20934,36 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L179" t="inlineStr"/>
@@ -20974,10 +20974,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>478282</v>
+        <v>478306</v>
       </c>
       <c r="R179" t="n">
-        <v>6770599</v>
+        <v>6770436</v>
       </c>
       <c r="S179" t="n">
         <v>1</v>
@@ -22408,10 +22408,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>118495878</v>
+        <v>118495810</v>
       </c>
       <c r="B192" t="n">
-        <v>5166</v>
+        <v>97846</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -22420,36 +22420,39 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
@@ -22457,10 +22460,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>478232</v>
+        <v>478260</v>
       </c>
       <c r="R192" t="n">
-        <v>6770403</v>
+        <v>6770405</v>
       </c>
       <c r="S192" t="n">
         <v>1</v>
@@ -22520,7 +22523,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>118495810</v>
+        <v>118495789</v>
       </c>
       <c r="B193" t="n">
         <v>97846</v>
@@ -22572,10 +22575,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>478260</v>
+        <v>478259</v>
       </c>
       <c r="R193" t="n">
-        <v>6770405</v>
+        <v>6770408</v>
       </c>
       <c r="S193" t="n">
         <v>1</v>
@@ -22635,10 +22638,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>118495789</v>
+        <v>118496176</v>
       </c>
       <c r="B194" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -22647,36 +22650,40 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L194" t="inlineStr"/>
@@ -22687,10 +22694,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>478259</v>
+        <v>478287</v>
       </c>
       <c r="R194" t="n">
-        <v>6770408</v>
+        <v>6770544</v>
       </c>
       <c r="S194" t="n">
         <v>1</v>
@@ -22750,10 +22757,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>118496176</v>
+        <v>118495878</v>
       </c>
       <c r="B195" t="n">
-        <v>104940</v>
+        <v>5166</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22766,39 +22773,32 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
@@ -22806,10 +22806,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>478287</v>
+        <v>478232</v>
       </c>
       <c r="R195" t="n">
-        <v>6770544</v>
+        <v>6770403</v>
       </c>
       <c r="S195" t="n">
         <v>1</v>
@@ -23213,10 +23213,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>118493987</v>
+        <v>118496309</v>
       </c>
       <c r="B199" t="n">
-        <v>97846</v>
+        <v>97869</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -23225,25 +23225,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -23254,7 +23254,7 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L199" t="inlineStr"/>
@@ -23265,10 +23265,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>478306</v>
+        <v>478334</v>
       </c>
       <c r="R199" t="n">
-        <v>6770444</v>
+        <v>6770571</v>
       </c>
       <c r="S199" t="n">
         <v>1</v>
@@ -23328,10 +23328,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>118496309</v>
+        <v>118493987</v>
       </c>
       <c r="B200" t="n">
-        <v>97869</v>
+        <v>97846</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -23340,25 +23340,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -23369,7 +23369,7 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L200" t="inlineStr"/>
@@ -23380,10 +23380,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>478334</v>
+        <v>478306</v>
       </c>
       <c r="R200" t="n">
-        <v>6770571</v>
+        <v>6770444</v>
       </c>
       <c r="S200" t="n">
         <v>1</v>
@@ -23557,10 +23557,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>118494239</v>
+        <v>118496290</v>
       </c>
       <c r="B202" t="n">
-        <v>5166</v>
+        <v>78518</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -23569,36 +23569,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
@@ -23606,10 +23608,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>478296</v>
+        <v>478300</v>
       </c>
       <c r="R202" t="n">
-        <v>6770423</v>
+        <v>6770569</v>
       </c>
       <c r="S202" t="n">
         <v>1</v>
@@ -23669,10 +23671,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>118496290</v>
+        <v>118494239</v>
       </c>
       <c r="B203" t="n">
-        <v>78518</v>
+        <v>5166</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -23681,38 +23683,36 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
@@ -23720,10 +23720,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>478300</v>
+        <v>478296</v>
       </c>
       <c r="R203" t="n">
-        <v>6770569</v>
+        <v>6770423</v>
       </c>
       <c r="S203" t="n">
         <v>1</v>
@@ -24481,7 +24481,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>118494025</v>
+        <v>118496218</v>
       </c>
       <c r="B210" t="n">
         <v>97846</v>
@@ -24516,7 +24516,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J210" t="inlineStr"/>
@@ -24533,10 +24533,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>478305</v>
+        <v>478212</v>
       </c>
       <c r="R210" t="n">
-        <v>6770435</v>
+        <v>6770545</v>
       </c>
       <c r="S210" t="n">
         <v>1</v>
@@ -24596,7 +24596,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>118495946</v>
+        <v>118494025</v>
       </c>
       <c r="B211" t="n">
         <v>97846</v>
@@ -24631,13 +24631,13 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L211" t="inlineStr"/>
@@ -24648,10 +24648,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>478291</v>
+        <v>478305</v>
       </c>
       <c r="R211" t="n">
-        <v>6770492</v>
+        <v>6770435</v>
       </c>
       <c r="S211" t="n">
         <v>1</v>
@@ -24711,7 +24711,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>118496218</v>
+        <v>118495946</v>
       </c>
       <c r="B212" t="n">
         <v>97846</v>
@@ -24752,7 +24752,7 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L212" t="inlineStr"/>
@@ -24763,10 +24763,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>478212</v>
+        <v>478291</v>
       </c>
       <c r="R212" t="n">
-        <v>6770545</v>
+        <v>6770492</v>
       </c>
       <c r="S212" t="n">
         <v>1</v>
@@ -38115,10 +38115,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>118552116</v>
+        <v>118551318</v>
       </c>
       <c r="B329" t="n">
-        <v>97846</v>
+        <v>58133</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -38127,25 +38127,25 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -38154,12 +38154,9 @@
         </is>
       </c>
       <c r="J329" t="inlineStr"/>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr"/>
+      <c r="M329" t="inlineStr"/>
       <c r="N329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
         <is>
@@ -38167,10 +38164,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>478316</v>
+        <v>478326</v>
       </c>
       <c r="R329" t="n">
-        <v>6770733</v>
+        <v>6770593</v>
       </c>
       <c r="S329" t="n">
         <v>1</v>
@@ -38229,7 +38226,7 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>118553013</v>
+        <v>118552116</v>
       </c>
       <c r="B330" t="n">
         <v>97846</v>
@@ -38281,10 +38278,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>478467</v>
+        <v>478316</v>
       </c>
       <c r="R330" t="n">
-        <v>6770793</v>
+        <v>6770733</v>
       </c>
       <c r="S330" t="n">
         <v>1</v>
@@ -38325,7 +38322,6 @@
       <c r="AE330" t="b">
         <v>0</v>
       </c>
-      <c r="AF330" t="inlineStr"/>
       <c r="AG330" t="b">
         <v>0</v>
       </c>
@@ -38344,7 +38340,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>118552791</v>
+        <v>118553013</v>
       </c>
       <c r="B331" t="n">
         <v>97846</v>
@@ -38396,10 +38392,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>478490</v>
+        <v>478467</v>
       </c>
       <c r="R331" t="n">
-        <v>6770832</v>
+        <v>6770793</v>
       </c>
       <c r="S331" t="n">
         <v>1</v>
@@ -38459,7 +38455,7 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>118551889</v>
+        <v>118552791</v>
       </c>
       <c r="B332" t="n">
         <v>97846</v>
@@ -38511,10 +38507,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>478330</v>
+        <v>478490</v>
       </c>
       <c r="R332" t="n">
-        <v>6770712</v>
+        <v>6770832</v>
       </c>
       <c r="S332" t="n">
         <v>1</v>
@@ -38574,7 +38570,7 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>118552308</v>
+        <v>118551889</v>
       </c>
       <c r="B333" t="n">
         <v>97846</v>
@@ -38609,7 +38605,7 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J333" t="inlineStr"/>
@@ -38626,10 +38622,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>478296</v>
+        <v>478330</v>
       </c>
       <c r="R333" t="n">
-        <v>6770682</v>
+        <v>6770712</v>
       </c>
       <c r="S333" t="n">
         <v>1</v>
@@ -38689,7 +38685,7 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>118553035</v>
+        <v>118552308</v>
       </c>
       <c r="B334" t="n">
         <v>97846</v>
@@ -38741,10 +38737,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>478473</v>
+        <v>478296</v>
       </c>
       <c r="R334" t="n">
-        <v>6770776</v>
+        <v>6770682</v>
       </c>
       <c r="S334" t="n">
         <v>1</v>
@@ -38804,7 +38800,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>118552375</v>
+        <v>118553035</v>
       </c>
       <c r="B335" t="n">
         <v>97846</v>
@@ -38839,7 +38835,7 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J335" t="inlineStr"/>
@@ -38856,10 +38852,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>478399</v>
+        <v>478473</v>
       </c>
       <c r="R335" t="n">
-        <v>6770573</v>
+        <v>6770776</v>
       </c>
       <c r="S335" t="n">
         <v>1</v>
@@ -38919,7 +38915,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>118552953</v>
+        <v>118552375</v>
       </c>
       <c r="B336" t="n">
         <v>97846</v>
@@ -38954,7 +38950,7 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J336" t="inlineStr"/>
@@ -38971,10 +38967,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>478438</v>
+        <v>478399</v>
       </c>
       <c r="R336" t="n">
-        <v>6770852</v>
+        <v>6770573</v>
       </c>
       <c r="S336" t="n">
         <v>1</v>
@@ -39034,10 +39030,10 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>118551318</v>
+        <v>118552953</v>
       </c>
       <c r="B337" t="n">
-        <v>58133</v>
+        <v>97846</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -39046,25 +39042,25 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -39073,9 +39069,12 @@
         </is>
       </c>
       <c r="J337" t="inlineStr"/>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr"/>
-      <c r="M337" t="inlineStr"/>
       <c r="N337" t="inlineStr"/>
       <c r="P337" t="inlineStr">
         <is>
@@ -39083,10 +39082,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>478326</v>
+        <v>478438</v>
       </c>
       <c r="R337" t="n">
-        <v>6770593</v>
+        <v>6770852</v>
       </c>
       <c r="S337" t="n">
         <v>1</v>
@@ -39127,6 +39126,7 @@
       <c r="AE337" t="b">
         <v>0</v>
       </c>
+      <c r="AF337" t="inlineStr"/>
       <c r="AG337" t="b">
         <v>0</v>
       </c>
@@ -40291,7 +40291,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>118552307</v>
+        <v>118552221</v>
       </c>
       <c r="B348" t="n">
         <v>97846</v>
@@ -40343,10 +40343,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>478282</v>
+        <v>478277</v>
       </c>
       <c r="R348" t="n">
-        <v>6770685</v>
+        <v>6770726</v>
       </c>
       <c r="S348" t="n">
         <v>1</v>
@@ -40387,7 +40387,6 @@
       <c r="AE348" t="b">
         <v>0</v>
       </c>
-      <c r="AF348" t="inlineStr"/>
       <c r="AG348" t="b">
         <v>0</v>
       </c>
@@ -40406,7 +40405,7 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>118552855</v>
+        <v>118552005</v>
       </c>
       <c r="B349" t="n">
         <v>97846</v>
@@ -40441,7 +40440,7 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J349" t="inlineStr"/>
@@ -40458,10 +40457,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>478446</v>
+        <v>478393</v>
       </c>
       <c r="R349" t="n">
-        <v>6770856</v>
+        <v>6770765</v>
       </c>
       <c r="S349" t="n">
         <v>1</v>
@@ -40502,7 +40501,6 @@
       <c r="AE349" t="b">
         <v>0</v>
       </c>
-      <c r="AF349" t="inlineStr"/>
       <c r="AG349" t="b">
         <v>0</v>
       </c>
@@ -40521,7 +40519,7 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>118552221</v>
+        <v>118552091</v>
       </c>
       <c r="B350" t="n">
         <v>97846</v>
@@ -40556,7 +40554,7 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J350" t="inlineStr"/>
@@ -40573,10 +40571,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>478277</v>
+        <v>478331</v>
       </c>
       <c r="R350" t="n">
-        <v>6770726</v>
+        <v>6770732</v>
       </c>
       <c r="S350" t="n">
         <v>1</v>
@@ -40635,7 +40633,7 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>118552005</v>
+        <v>118551822</v>
       </c>
       <c r="B351" t="n">
         <v>97846</v>
@@ -40670,7 +40668,7 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J351" t="inlineStr"/>
@@ -40687,10 +40685,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>478393</v>
+        <v>478354</v>
       </c>
       <c r="R351" t="n">
-        <v>6770765</v>
+        <v>6770678</v>
       </c>
       <c r="S351" t="n">
         <v>1</v>
@@ -40731,6 +40729,7 @@
       <c r="AE351" t="b">
         <v>0</v>
       </c>
+      <c r="AF351" t="inlineStr"/>
       <c r="AG351" t="b">
         <v>0</v>
       </c>
@@ -40749,7 +40748,7 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>118552091</v>
+        <v>118551450</v>
       </c>
       <c r="B352" t="n">
         <v>97846</v>
@@ -40784,7 +40783,7 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J352" t="inlineStr"/>
@@ -40804,7 +40803,7 @@
         <v>478331</v>
       </c>
       <c r="R352" t="n">
-        <v>6770732</v>
+        <v>6770654</v>
       </c>
       <c r="S352" t="n">
         <v>1</v>
@@ -40863,7 +40862,7 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>118551822</v>
+        <v>118552678</v>
       </c>
       <c r="B353" t="n">
         <v>97846</v>
@@ -40904,7 +40903,7 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L353" t="inlineStr"/>
@@ -40915,10 +40914,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>478354</v>
+        <v>478447</v>
       </c>
       <c r="R353" t="n">
-        <v>6770678</v>
+        <v>6770662</v>
       </c>
       <c r="S353" t="n">
         <v>1</v>
@@ -40978,7 +40977,7 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>118551450</v>
+        <v>118551416</v>
       </c>
       <c r="B354" t="n">
         <v>97846</v>
@@ -41030,10 +41029,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>478331</v>
+        <v>478398</v>
       </c>
       <c r="R354" t="n">
-        <v>6770654</v>
+        <v>6770626</v>
       </c>
       <c r="S354" t="n">
         <v>1</v>
@@ -41092,7 +41091,7 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>118552678</v>
+        <v>118551531</v>
       </c>
       <c r="B355" t="n">
         <v>97846</v>
@@ -41127,13 +41126,13 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L355" t="inlineStr"/>
@@ -41144,10 +41143,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>478447</v>
+        <v>478313</v>
       </c>
       <c r="R355" t="n">
-        <v>6770662</v>
+        <v>6770678</v>
       </c>
       <c r="S355" t="n">
         <v>1</v>
@@ -41188,7 +41187,6 @@
       <c r="AE355" t="b">
         <v>0</v>
       </c>
-      <c r="AF355" t="inlineStr"/>
       <c r="AG355" t="b">
         <v>0</v>
       </c>
@@ -41207,7 +41205,7 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>118551416</v>
+        <v>118552220</v>
       </c>
       <c r="B356" t="n">
         <v>97846</v>
@@ -41259,10 +41257,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>478398</v>
+        <v>478282</v>
       </c>
       <c r="R356" t="n">
-        <v>6770626</v>
+        <v>6770728</v>
       </c>
       <c r="S356" t="n">
         <v>1</v>
@@ -41321,7 +41319,7 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>118551531</v>
+        <v>118553022</v>
       </c>
       <c r="B357" t="n">
         <v>97846</v>
@@ -41356,7 +41354,7 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J357" t="inlineStr"/>
@@ -41373,10 +41371,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>478313</v>
+        <v>478470</v>
       </c>
       <c r="R357" t="n">
-        <v>6770678</v>
+        <v>6770788</v>
       </c>
       <c r="S357" t="n">
         <v>1</v>
@@ -41417,6 +41415,7 @@
       <c r="AE357" t="b">
         <v>0</v>
       </c>
+      <c r="AF357" t="inlineStr"/>
       <c r="AG357" t="b">
         <v>0</v>
       </c>
@@ -41435,7 +41434,7 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>118552220</v>
+        <v>118551482</v>
       </c>
       <c r="B358" t="n">
         <v>97846</v>
@@ -41487,10 +41486,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>478282</v>
+        <v>478332</v>
       </c>
       <c r="R358" t="n">
-        <v>6770728</v>
+        <v>6770676</v>
       </c>
       <c r="S358" t="n">
         <v>1</v>
@@ -41549,7 +41548,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>118553022</v>
+        <v>118551489</v>
       </c>
       <c r="B359" t="n">
         <v>97846</v>
@@ -41601,10 +41600,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>478470</v>
+        <v>478331</v>
       </c>
       <c r="R359" t="n">
-        <v>6770788</v>
+        <v>6770672</v>
       </c>
       <c r="S359" t="n">
         <v>1</v>
@@ -41645,7 +41644,6 @@
       <c r="AE359" t="b">
         <v>0</v>
       </c>
-      <c r="AF359" t="inlineStr"/>
       <c r="AG359" t="b">
         <v>0</v>
       </c>
@@ -41664,7 +41662,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>118551482</v>
+        <v>118552320</v>
       </c>
       <c r="B360" t="n">
         <v>97846</v>
@@ -41716,10 +41714,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>478332</v>
+        <v>478299</v>
       </c>
       <c r="R360" t="n">
-        <v>6770676</v>
+        <v>6770658</v>
       </c>
       <c r="S360" t="n">
         <v>1</v>
@@ -41760,6 +41758,7 @@
       <c r="AE360" t="b">
         <v>0</v>
       </c>
+      <c r="AF360" t="inlineStr"/>
       <c r="AG360" t="b">
         <v>0</v>
       </c>
@@ -41778,7 +41777,7 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>118551489</v>
+        <v>118551224</v>
       </c>
       <c r="B361" t="n">
         <v>97846</v>
@@ -41830,10 +41829,10 @@
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>478331</v>
+        <v>478365</v>
       </c>
       <c r="R361" t="n">
-        <v>6770672</v>
+        <v>6770570</v>
       </c>
       <c r="S361" t="n">
         <v>1</v>
@@ -41874,6 +41873,7 @@
       <c r="AE361" t="b">
         <v>0</v>
       </c>
+      <c r="AF361" t="inlineStr"/>
       <c r="AG361" t="b">
         <v>0</v>
       </c>
@@ -41885,14 +41885,14 @@
       </c>
       <c r="AX361" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>118552320</v>
+        <v>118552307</v>
       </c>
       <c r="B362" t="n">
         <v>97846</v>
@@ -41944,10 +41944,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>478299</v>
+        <v>478282</v>
       </c>
       <c r="R362" t="n">
-        <v>6770658</v>
+        <v>6770685</v>
       </c>
       <c r="S362" t="n">
         <v>1</v>
@@ -42007,7 +42007,7 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>118551224</v>
+        <v>118552855</v>
       </c>
       <c r="B363" t="n">
         <v>97846</v>
@@ -42042,7 +42042,7 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J363" t="inlineStr"/>
@@ -42059,10 +42059,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>478365</v>
+        <v>478446</v>
       </c>
       <c r="R363" t="n">
-        <v>6770570</v>
+        <v>6770856</v>
       </c>
       <c r="S363" t="n">
         <v>1</v>
@@ -42115,14 +42115,14 @@
       </c>
       <c r="AX363" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>118552249</v>
+        <v>118552426</v>
       </c>
       <c r="B364" t="n">
         <v>97846</v>
@@ -42157,7 +42157,7 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J364" t="inlineStr"/>
@@ -42174,10 +42174,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>478300</v>
+        <v>478405</v>
       </c>
       <c r="R364" t="n">
-        <v>6770709</v>
+        <v>6770584</v>
       </c>
       <c r="S364" t="n">
         <v>1</v>
@@ -42218,6 +42218,7 @@
       <c r="AE364" t="b">
         <v>0</v>
       </c>
+      <c r="AF364" t="inlineStr"/>
       <c r="AG364" t="b">
         <v>0</v>
       </c>
@@ -42351,7 +42352,7 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>118552426</v>
+        <v>118552249</v>
       </c>
       <c r="B366" t="n">
         <v>97846</v>
@@ -42386,7 +42387,7 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J366" t="inlineStr"/>
@@ -42403,10 +42404,10 @@
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>478405</v>
+        <v>478300</v>
       </c>
       <c r="R366" t="n">
-        <v>6770584</v>
+        <v>6770709</v>
       </c>
       <c r="S366" t="n">
         <v>1</v>
@@ -42447,7 +42448,6 @@
       <c r="AE366" t="b">
         <v>0</v>
       </c>
-      <c r="AF366" t="inlineStr"/>
       <c r="AG366" t="b">
         <v>0</v>
       </c>
@@ -43498,7 +43498,7 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>118552393</v>
+        <v>118552128</v>
       </c>
       <c r="B376" t="n">
         <v>97846</v>
@@ -43533,7 +43533,7 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J376" t="inlineStr"/>
@@ -43550,10 +43550,10 @@
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>478402</v>
+        <v>478363</v>
       </c>
       <c r="R376" t="n">
-        <v>6770574</v>
+        <v>6770718</v>
       </c>
       <c r="S376" t="n">
         <v>1</v>
@@ -43594,7 +43594,6 @@
       <c r="AE376" t="b">
         <v>0</v>
       </c>
-      <c r="AF376" t="inlineStr"/>
       <c r="AG376" t="b">
         <v>0</v>
       </c>
@@ -43613,7 +43612,7 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>118552741</v>
+        <v>118552384</v>
       </c>
       <c r="B377" t="n">
         <v>97846</v>
@@ -43665,10 +43664,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>478481</v>
+        <v>478402</v>
       </c>
       <c r="R377" t="n">
-        <v>6770782</v>
+        <v>6770576</v>
       </c>
       <c r="S377" t="n">
         <v>1</v>
@@ -43728,7 +43727,7 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>118552128</v>
+        <v>118551541</v>
       </c>
       <c r="B378" t="n">
         <v>97846</v>
@@ -43780,10 +43779,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>478363</v>
+        <v>478311</v>
       </c>
       <c r="R378" t="n">
-        <v>6770718</v>
+        <v>6770690</v>
       </c>
       <c r="S378" t="n">
         <v>1</v>
@@ -43842,7 +43841,7 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>118552384</v>
+        <v>118551971</v>
       </c>
       <c r="B379" t="n">
         <v>97846</v>
@@ -43894,10 +43893,10 @@
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>478402</v>
+        <v>478350</v>
       </c>
       <c r="R379" t="n">
-        <v>6770576</v>
+        <v>6770664</v>
       </c>
       <c r="S379" t="n">
         <v>1</v>
@@ -43957,7 +43956,7 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>118551541</v>
+        <v>118552243</v>
       </c>
       <c r="B380" t="n">
         <v>97846</v>
@@ -44009,10 +44008,10 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>478311</v>
+        <v>478301</v>
       </c>
       <c r="R380" t="n">
-        <v>6770690</v>
+        <v>6770717</v>
       </c>
       <c r="S380" t="n">
         <v>1</v>
@@ -44071,7 +44070,7 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>118551971</v>
+        <v>118552393</v>
       </c>
       <c r="B381" t="n">
         <v>97846</v>
@@ -44106,7 +44105,7 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J381" t="inlineStr"/>
@@ -44123,10 +44122,10 @@
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>478350</v>
+        <v>478402</v>
       </c>
       <c r="R381" t="n">
-        <v>6770664</v>
+        <v>6770574</v>
       </c>
       <c r="S381" t="n">
         <v>1</v>
@@ -44186,7 +44185,7 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>118552243</v>
+        <v>118552741</v>
       </c>
       <c r="B382" t="n">
         <v>97846</v>
@@ -44238,10 +44237,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>478301</v>
+        <v>478481</v>
       </c>
       <c r="R382" t="n">
-        <v>6770717</v>
+        <v>6770782</v>
       </c>
       <c r="S382" t="n">
         <v>1</v>
@@ -44282,6 +44281,7 @@
       <c r="AE382" t="b">
         <v>0</v>
       </c>
+      <c r="AF382" t="inlineStr"/>
       <c r="AG382" t="b">
         <v>0</v>
       </c>
@@ -44300,10 +44300,10 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>118552431</v>
+        <v>118552054</v>
       </c>
       <c r="B383" t="n">
-        <v>97846</v>
+        <v>78518</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -44312,25 +44312,25 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -44338,13 +44338,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J383" t="inlineStr"/>
-      <c r="K383" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L383" t="inlineStr"/>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr"/>
       <c r="N383" t="inlineStr"/>
       <c r="P383" t="inlineStr">
         <is>
@@ -44352,10 +44351,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>478409</v>
+        <v>478407</v>
       </c>
       <c r="R383" t="n">
-        <v>6770592</v>
+        <v>6770699</v>
       </c>
       <c r="S383" t="n">
         <v>1</v>
@@ -44396,7 +44395,6 @@
       <c r="AE383" t="b">
         <v>0</v>
       </c>
-      <c r="AF383" t="inlineStr"/>
       <c r="AG383" t="b">
         <v>0</v>
       </c>
@@ -44415,10 +44413,10 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>118552054</v>
+        <v>118552205</v>
       </c>
       <c r="B384" t="n">
-        <v>78518</v>
+        <v>97846</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -44427,25 +44425,25 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -44453,12 +44451,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J384" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="J384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr"/>
       <c r="N384" t="inlineStr"/>
       <c r="P384" t="inlineStr">
         <is>
@@ -44466,10 +44465,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>478407</v>
+        <v>478346</v>
       </c>
       <c r="R384" t="n">
-        <v>6770699</v>
+        <v>6770808</v>
       </c>
       <c r="S384" t="n">
         <v>1</v>
@@ -44528,7 +44527,7 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>118552205</v>
+        <v>118552201</v>
       </c>
       <c r="B385" t="n">
         <v>97846</v>
@@ -44580,10 +44579,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>478346</v>
+        <v>478354</v>
       </c>
       <c r="R385" t="n">
-        <v>6770808</v>
+        <v>6770801</v>
       </c>
       <c r="S385" t="n">
         <v>1</v>
@@ -44642,7 +44641,7 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>118552201</v>
+        <v>118552991</v>
       </c>
       <c r="B386" t="n">
         <v>97846</v>
@@ -44677,7 +44676,7 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J386" t="inlineStr"/>
@@ -44694,10 +44693,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>478354</v>
+        <v>478461</v>
       </c>
       <c r="R386" t="n">
-        <v>6770801</v>
+        <v>6770811</v>
       </c>
       <c r="S386" t="n">
         <v>1</v>
@@ -44738,6 +44737,7 @@
       <c r="AE386" t="b">
         <v>0</v>
       </c>
+      <c r="AF386" t="inlineStr"/>
       <c r="AG386" t="b">
         <v>0</v>
       </c>
@@ -44756,7 +44756,7 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>118552991</v>
+        <v>118552517</v>
       </c>
       <c r="B387" t="n">
         <v>97846</v>
@@ -44791,7 +44791,7 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J387" t="inlineStr"/>
@@ -44808,10 +44808,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>478461</v>
+        <v>478418</v>
       </c>
       <c r="R387" t="n">
-        <v>6770811</v>
+        <v>6770615</v>
       </c>
       <c r="S387" t="n">
         <v>1</v>
@@ -44871,7 +44871,7 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>118552517</v>
+        <v>118552951</v>
       </c>
       <c r="B388" t="n">
         <v>97846</v>
@@ -44906,7 +44906,7 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J388" t="inlineStr"/>
@@ -44923,10 +44923,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>478418</v>
+        <v>478444</v>
       </c>
       <c r="R388" t="n">
-        <v>6770615</v>
+        <v>6770854</v>
       </c>
       <c r="S388" t="n">
         <v>1</v>
@@ -44986,7 +44986,7 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>118552951</v>
+        <v>118551967</v>
       </c>
       <c r="B389" t="n">
         <v>97846</v>
@@ -45021,7 +45021,7 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J389" t="inlineStr"/>
@@ -45038,10 +45038,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>478444</v>
+        <v>478370</v>
       </c>
       <c r="R389" t="n">
-        <v>6770854</v>
+        <v>6770656</v>
       </c>
       <c r="S389" t="n">
         <v>1</v>
@@ -45101,7 +45101,7 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>118551967</v>
+        <v>118552241</v>
       </c>
       <c r="B390" t="n">
         <v>97846</v>
@@ -45136,7 +45136,7 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J390" t="inlineStr"/>
@@ -45153,10 +45153,10 @@
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>478370</v>
+        <v>478310</v>
       </c>
       <c r="R390" t="n">
-        <v>6770656</v>
+        <v>6770728</v>
       </c>
       <c r="S390" t="n">
         <v>1</v>
@@ -45197,7 +45197,6 @@
       <c r="AE390" t="b">
         <v>0</v>
       </c>
-      <c r="AF390" t="inlineStr"/>
       <c r="AG390" t="b">
         <v>0</v>
       </c>
@@ -45216,7 +45215,7 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>118552241</v>
+        <v>118553019</v>
       </c>
       <c r="B391" t="n">
         <v>97846</v>
@@ -45251,7 +45250,7 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J391" t="inlineStr"/>
@@ -45268,10 +45267,10 @@
         </is>
       </c>
       <c r="Q391" t="n">
-        <v>478310</v>
+        <v>478472</v>
       </c>
       <c r="R391" t="n">
-        <v>6770728</v>
+        <v>6770786</v>
       </c>
       <c r="S391" t="n">
         <v>1</v>
@@ -45312,6 +45311,7 @@
       <c r="AE391" t="b">
         <v>0</v>
       </c>
+      <c r="AF391" t="inlineStr"/>
       <c r="AG391" t="b">
         <v>0</v>
       </c>
@@ -45330,7 +45330,7 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>118553019</v>
+        <v>118552724</v>
       </c>
       <c r="B392" t="n">
         <v>97846</v>
@@ -45382,10 +45382,10 @@
         </is>
       </c>
       <c r="Q392" t="n">
-        <v>478472</v>
+        <v>478468</v>
       </c>
       <c r="R392" t="n">
-        <v>6770786</v>
+        <v>6770769</v>
       </c>
       <c r="S392" t="n">
         <v>1</v>
@@ -45445,7 +45445,7 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>118552724</v>
+        <v>118552431</v>
       </c>
       <c r="B393" t="n">
         <v>97846</v>
@@ -45497,10 +45497,10 @@
         </is>
       </c>
       <c r="Q393" t="n">
-        <v>478468</v>
+        <v>478409</v>
       </c>
       <c r="R393" t="n">
-        <v>6770769</v>
+        <v>6770592</v>
       </c>
       <c r="S393" t="n">
         <v>1</v>
@@ -45560,7 +45560,7 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>118551290</v>
+        <v>118552095</v>
       </c>
       <c r="B394" t="n">
         <v>97846</v>
@@ -45612,10 +45612,10 @@
         </is>
       </c>
       <c r="Q394" t="n">
-        <v>478337</v>
+        <v>478328</v>
       </c>
       <c r="R394" t="n">
-        <v>6770585</v>
+        <v>6770742</v>
       </c>
       <c r="S394" t="n">
         <v>1</v>
@@ -45656,7 +45656,6 @@
       <c r="AE394" t="b">
         <v>0</v>
       </c>
-      <c r="AF394" t="inlineStr"/>
       <c r="AG394" t="b">
         <v>0</v>
       </c>
@@ -45668,14 +45667,14 @@
       </c>
       <c r="AX394" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>118552352</v>
+        <v>118551290</v>
       </c>
       <c r="B395" t="n">
         <v>97846</v>
@@ -45716,7 +45715,7 @@
       <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L395" t="inlineStr"/>
@@ -45727,10 +45726,10 @@
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>478237</v>
+        <v>478337</v>
       </c>
       <c r="R395" t="n">
-        <v>6770629</v>
+        <v>6770585</v>
       </c>
       <c r="S395" t="n">
         <v>1</v>
@@ -45783,14 +45782,14 @@
       </c>
       <c r="AX395" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>118552259</v>
+        <v>118552352</v>
       </c>
       <c r="B396" t="n">
         <v>97846</v>
@@ -45831,7 +45830,7 @@
       <c r="J396" t="inlineStr"/>
       <c r="K396" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L396" t="inlineStr"/>
@@ -45842,10 +45841,10 @@
         </is>
       </c>
       <c r="Q396" t="n">
-        <v>478292</v>
+        <v>478237</v>
       </c>
       <c r="R396" t="n">
-        <v>6770717</v>
+        <v>6770629</v>
       </c>
       <c r="S396" t="n">
         <v>1</v>
@@ -45886,6 +45885,7 @@
       <c r="AE396" t="b">
         <v>0</v>
       </c>
+      <c r="AF396" t="inlineStr"/>
       <c r="AG396" t="b">
         <v>0</v>
       </c>
@@ -45904,7 +45904,7 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>118552198</v>
+        <v>118552259</v>
       </c>
       <c r="B397" t="n">
         <v>97846</v>
@@ -45956,10 +45956,10 @@
         </is>
       </c>
       <c r="Q397" t="n">
-        <v>478354</v>
+        <v>478292</v>
       </c>
       <c r="R397" t="n">
-        <v>6770800</v>
+        <v>6770717</v>
       </c>
       <c r="S397" t="n">
         <v>1</v>
@@ -46018,7 +46018,7 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>118552250</v>
+        <v>118552198</v>
       </c>
       <c r="B398" t="n">
         <v>97846</v>
@@ -46053,7 +46053,7 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J398" t="inlineStr"/>
@@ -46070,10 +46070,10 @@
         </is>
       </c>
       <c r="Q398" t="n">
-        <v>478296</v>
+        <v>478354</v>
       </c>
       <c r="R398" t="n">
-        <v>6770711</v>
+        <v>6770800</v>
       </c>
       <c r="S398" t="n">
         <v>1</v>
@@ -46132,7 +46132,7 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>118552494</v>
+        <v>118552250</v>
       </c>
       <c r="B399" t="n">
         <v>97846</v>
@@ -46167,7 +46167,7 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J399" t="inlineStr"/>
@@ -46184,10 +46184,10 @@
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>478411</v>
+        <v>478296</v>
       </c>
       <c r="R399" t="n">
-        <v>6770610</v>
+        <v>6770711</v>
       </c>
       <c r="S399" t="n">
         <v>1</v>
@@ -46228,7 +46228,6 @@
       <c r="AE399" t="b">
         <v>0</v>
       </c>
-      <c r="AF399" t="inlineStr"/>
       <c r="AG399" t="b">
         <v>0</v>
       </c>
@@ -46247,7 +46246,7 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>118551239</v>
+        <v>118552494</v>
       </c>
       <c r="B400" t="n">
         <v>97846</v>
@@ -46282,7 +46281,7 @@
       </c>
       <c r="I400" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J400" t="inlineStr"/>
@@ -46299,10 +46298,10 @@
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>478369</v>
+        <v>478411</v>
       </c>
       <c r="R400" t="n">
-        <v>6770563</v>
+        <v>6770610</v>
       </c>
       <c r="S400" t="n">
         <v>1</v>
@@ -46355,14 +46354,14 @@
       </c>
       <c r="AX400" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>118551307</v>
+        <v>118551239</v>
       </c>
       <c r="B401" t="n">
         <v>97846</v>
@@ -46414,10 +46413,10 @@
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>478319</v>
+        <v>478369</v>
       </c>
       <c r="R401" t="n">
-        <v>6770595</v>
+        <v>6770563</v>
       </c>
       <c r="S401" t="n">
         <v>1</v>
@@ -46458,6 +46457,7 @@
       <c r="AE401" t="b">
         <v>0</v>
       </c>
+      <c r="AF401" t="inlineStr"/>
       <c r="AG401" t="b">
         <v>0</v>
       </c>
@@ -46469,14 +46469,14 @@
       </c>
       <c r="AX401" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>118551921</v>
+        <v>118551307</v>
       </c>
       <c r="B402" t="n">
         <v>97846</v>
@@ -46528,10 +46528,10 @@
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>478361</v>
+        <v>478319</v>
       </c>
       <c r="R402" t="n">
-        <v>6770675</v>
+        <v>6770595</v>
       </c>
       <c r="S402" t="n">
         <v>1</v>
@@ -46572,7 +46572,6 @@
       <c r="AE402" t="b">
         <v>0</v>
       </c>
-      <c r="AF402" t="inlineStr"/>
       <c r="AG402" t="b">
         <v>0</v>
       </c>
@@ -46591,7 +46590,7 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>118552213</v>
+        <v>118551921</v>
       </c>
       <c r="B403" t="n">
         <v>97846</v>
@@ -46643,10 +46642,10 @@
         </is>
       </c>
       <c r="Q403" t="n">
-        <v>478288</v>
+        <v>478361</v>
       </c>
       <c r="R403" t="n">
-        <v>6770774</v>
+        <v>6770675</v>
       </c>
       <c r="S403" t="n">
         <v>1</v>
@@ -46687,6 +46686,7 @@
       <c r="AE403" t="b">
         <v>0</v>
       </c>
+      <c r="AF403" t="inlineStr"/>
       <c r="AG403" t="b">
         <v>0</v>
       </c>
@@ -46705,7 +46705,7 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>118551948</v>
+        <v>118552213</v>
       </c>
       <c r="B404" t="n">
         <v>97846</v>
@@ -46757,10 +46757,10 @@
         </is>
       </c>
       <c r="Q404" t="n">
-        <v>478353</v>
+        <v>478288</v>
       </c>
       <c r="R404" t="n">
-        <v>6770769</v>
+        <v>6770774</v>
       </c>
       <c r="S404" t="n">
         <v>1</v>
@@ -46801,7 +46801,6 @@
       <c r="AE404" t="b">
         <v>0</v>
       </c>
-      <c r="AF404" t="inlineStr"/>
       <c r="AG404" t="b">
         <v>0</v>
       </c>
@@ -46820,7 +46819,7 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>118552773</v>
+        <v>118551948</v>
       </c>
       <c r="B405" t="n">
         <v>97846</v>
@@ -46855,13 +46854,13 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J405" t="inlineStr"/>
       <c r="K405" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L405" t="inlineStr"/>
@@ -46872,10 +46871,10 @@
         </is>
       </c>
       <c r="Q405" t="n">
-        <v>478485</v>
+        <v>478353</v>
       </c>
       <c r="R405" t="n">
-        <v>6770819</v>
+        <v>6770769</v>
       </c>
       <c r="S405" t="n">
         <v>1</v>
@@ -46935,7 +46934,7 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>118552095</v>
+        <v>118552773</v>
       </c>
       <c r="B406" t="n">
         <v>97846</v>
@@ -46970,13 +46969,13 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L406" t="inlineStr"/>
@@ -46987,10 +46986,10 @@
         </is>
       </c>
       <c r="Q406" t="n">
-        <v>478328</v>
+        <v>478485</v>
       </c>
       <c r="R406" t="n">
-        <v>6770742</v>
+        <v>6770819</v>
       </c>
       <c r="S406" t="n">
         <v>1</v>
@@ -47031,6 +47030,7 @@
       <c r="AE406" t="b">
         <v>0</v>
       </c>
+      <c r="AF406" t="inlineStr"/>
       <c r="AG406" t="b">
         <v>0</v>
       </c>
@@ -49802,7 +49802,7 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>118568454</v>
+        <v>118568676</v>
       </c>
       <c r="B431" t="n">
         <v>97846</v>
@@ -49843,7 +49843,7 @@
       <c r="J431" t="inlineStr"/>
       <c r="K431" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L431" t="inlineStr"/>
@@ -49854,10 +49854,10 @@
         </is>
       </c>
       <c r="Q431" t="n">
-        <v>478303</v>
+        <v>478205</v>
       </c>
       <c r="R431" t="n">
-        <v>6771080</v>
+        <v>6770866</v>
       </c>
       <c r="S431" t="n">
         <v>1</v>
@@ -49917,7 +49917,7 @@
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>118568300</v>
+        <v>118568454</v>
       </c>
       <c r="B432" t="n">
         <v>97846</v>
@@ -49952,13 +49952,13 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J432" t="inlineStr"/>
       <c r="K432" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L432" t="inlineStr"/>
@@ -49969,10 +49969,10 @@
         </is>
       </c>
       <c r="Q432" t="n">
-        <v>478316</v>
+        <v>478303</v>
       </c>
       <c r="R432" t="n">
-        <v>6771003</v>
+        <v>6771080</v>
       </c>
       <c r="S432" t="n">
         <v>1</v>
@@ -50032,7 +50032,7 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>118568687</v>
+        <v>118568300</v>
       </c>
       <c r="B433" t="n">
         <v>97846</v>
@@ -50067,7 +50067,7 @@
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J433" t="inlineStr"/>
@@ -50084,10 +50084,10 @@
         </is>
       </c>
       <c r="Q433" t="n">
-        <v>478296</v>
+        <v>478316</v>
       </c>
       <c r="R433" t="n">
-        <v>6770931</v>
+        <v>6771003</v>
       </c>
       <c r="S433" t="n">
         <v>1</v>
@@ -50147,7 +50147,7 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>118568634</v>
+        <v>118568687</v>
       </c>
       <c r="B434" t="n">
         <v>97846</v>
@@ -50182,13 +50182,13 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J434" t="inlineStr"/>
       <c r="K434" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L434" t="inlineStr"/>
@@ -50199,10 +50199,10 @@
         </is>
       </c>
       <c r="Q434" t="n">
-        <v>478201</v>
+        <v>478296</v>
       </c>
       <c r="R434" t="n">
-        <v>6770878</v>
+        <v>6770931</v>
       </c>
       <c r="S434" t="n">
         <v>1</v>
@@ -50262,7 +50262,7 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>118568676</v>
+        <v>118568634</v>
       </c>
       <c r="B435" t="n">
         <v>97846</v>
@@ -50303,7 +50303,7 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L435" t="inlineStr"/>
@@ -50314,10 +50314,10 @@
         </is>
       </c>
       <c r="Q435" t="n">
-        <v>478205</v>
+        <v>478201</v>
       </c>
       <c r="R435" t="n">
-        <v>6770866</v>
+        <v>6770878</v>
       </c>
       <c r="S435" t="n">
         <v>1</v>
@@ -53016,10 +53016,10 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>118568160</v>
+        <v>118568756</v>
       </c>
       <c r="B459" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
@@ -53028,35 +53028,39 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E459" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I459" t="inlineStr"/>
-      <c r="K459" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr"/>
-      <c r="M459" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N459" t="inlineStr"/>
       <c r="P459" t="inlineStr">
         <is>
@@ -53064,10 +53068,10 @@
         </is>
       </c>
       <c r="Q459" t="n">
-        <v>478342</v>
+        <v>478328</v>
       </c>
       <c r="R459" t="n">
-        <v>6770857</v>
+        <v>6771027</v>
       </c>
       <c r="S459" t="n">
         <v>1</v>
@@ -53108,6 +53112,7 @@
       <c r="AE459" t="b">
         <v>0</v>
       </c>
+      <c r="AF459" t="inlineStr"/>
       <c r="AG459" t="b">
         <v>0</v>
       </c>
@@ -53586,10 +53591,10 @@
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>118568756</v>
+        <v>118568160</v>
       </c>
       <c r="B464" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
@@ -53598,39 +53603,35 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E464" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I464" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J464" t="inlineStr"/>
-      <c r="K464" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr"/>
+      <c r="K464" t="inlineStr"/>
       <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N464" t="inlineStr"/>
       <c r="P464" t="inlineStr">
         <is>
@@ -53638,10 +53639,10 @@
         </is>
       </c>
       <c r="Q464" t="n">
-        <v>478328</v>
+        <v>478342</v>
       </c>
       <c r="R464" t="n">
-        <v>6771027</v>
+        <v>6770857</v>
       </c>
       <c r="S464" t="n">
         <v>1</v>
@@ -53682,7 +53683,6 @@
       <c r="AE464" t="b">
         <v>0</v>
       </c>
-      <c r="AF464" t="inlineStr"/>
       <c r="AG464" t="b">
         <v>0</v>
       </c>
@@ -56341,7 +56341,7 @@
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>118568624</v>
+        <v>118568615</v>
       </c>
       <c r="B488" t="n">
         <v>97846</v>
@@ -56376,13 +56376,13 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L488" t="inlineStr"/>
@@ -56393,10 +56393,10 @@
         </is>
       </c>
       <c r="Q488" t="n">
-        <v>478299</v>
+        <v>478296</v>
       </c>
       <c r="R488" t="n">
-        <v>6770903</v>
+        <v>6770908</v>
       </c>
       <c r="S488" t="n">
         <v>1</v>
@@ -56692,7 +56692,7 @@
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>118568615</v>
+        <v>118568624</v>
       </c>
       <c r="B491" t="n">
         <v>97846</v>
@@ -56727,13 +56727,13 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L491" t="inlineStr"/>
@@ -56744,10 +56744,10 @@
         </is>
       </c>
       <c r="Q491" t="n">
-        <v>478296</v>
+        <v>478299</v>
       </c>
       <c r="R491" t="n">
-        <v>6770908</v>
+        <v>6770903</v>
       </c>
       <c r="S491" t="n">
         <v>1</v>
@@ -57940,10 +57940,10 @@
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>118610721</v>
+        <v>118610640</v>
       </c>
       <c r="B502" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C502" t="inlineStr">
         <is>
@@ -57952,39 +57952,35 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E502" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I502" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J502" t="inlineStr"/>
-      <c r="K502" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr"/>
+      <c r="K502" t="inlineStr"/>
       <c r="L502" t="inlineStr"/>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N502" t="inlineStr"/>
       <c r="P502" t="inlineStr">
         <is>
@@ -57992,10 +57988,10 @@
         </is>
       </c>
       <c r="Q502" t="n">
-        <v>478200</v>
+        <v>478168</v>
       </c>
       <c r="R502" t="n">
-        <v>6770508</v>
+        <v>6770438</v>
       </c>
       <c r="S502" t="n">
         <v>1</v>
@@ -58036,7 +58032,6 @@
       <c r="AE502" t="b">
         <v>0</v>
       </c>
-      <c r="AF502" t="inlineStr"/>
       <c r="AG502" t="b">
         <v>0</v>
       </c>
@@ -58055,10 +58050,10 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>118610640</v>
+        <v>118610721</v>
       </c>
       <c r="B503" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
@@ -58067,35 +58062,39 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E503" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I503" t="inlineStr"/>
-      <c r="K503" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr"/>
-      <c r="M503" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N503" t="inlineStr"/>
       <c r="P503" t="inlineStr">
         <is>
@@ -58103,10 +58102,10 @@
         </is>
       </c>
       <c r="Q503" t="n">
-        <v>478168</v>
+        <v>478200</v>
       </c>
       <c r="R503" t="n">
-        <v>6770438</v>
+        <v>6770508</v>
       </c>
       <c r="S503" t="n">
         <v>1</v>
@@ -58147,6 +58146,7 @@
       <c r="AE503" t="b">
         <v>0</v>
       </c>
+      <c r="AF503" t="inlineStr"/>
       <c r="AG503" t="b">
         <v>0</v>
       </c>
@@ -58726,10 +58726,10 @@
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>118610627</v>
+        <v>118610755</v>
       </c>
       <c r="B509" t="n">
-        <v>5166</v>
+        <v>78518</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
@@ -58738,32 +58738,38 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E509" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I509" t="inlineStr"/>
-      <c r="J509" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K509" t="inlineStr"/>
-      <c r="L509" t="inlineStr"/>
-      <c r="M509" t="inlineStr"/>
       <c r="N509" t="inlineStr"/>
       <c r="P509" t="inlineStr">
         <is>
@@ -58771,10 +58777,10 @@
         </is>
       </c>
       <c r="Q509" t="n">
-        <v>478176</v>
+        <v>478215</v>
       </c>
       <c r="R509" t="n">
-        <v>6770431</v>
+        <v>6770523</v>
       </c>
       <c r="S509" t="n">
         <v>1</v>
@@ -58834,10 +58840,10 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>118610755</v>
+        <v>118610627</v>
       </c>
       <c r="B510" t="n">
-        <v>78518</v>
+        <v>5166</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
@@ -58846,38 +58852,32 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E510" t="n">
-        <v>185</v>
+        <v>100526</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I510" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J510" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr"/>
+      <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr"/>
+      <c r="L510" t="inlineStr"/>
+      <c r="M510" t="inlineStr"/>
       <c r="N510" t="inlineStr"/>
       <c r="P510" t="inlineStr">
         <is>
@@ -58885,10 +58885,10 @@
         </is>
       </c>
       <c r="Q510" t="n">
-        <v>478215</v>
+        <v>478176</v>
       </c>
       <c r="R510" t="n">
-        <v>6770523</v>
+        <v>6770431</v>
       </c>
       <c r="S510" t="n">
         <v>1</v>
@@ -58948,10 +58948,10 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>118610739</v>
+        <v>118610619</v>
       </c>
       <c r="B511" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
@@ -58960,39 +58960,35 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E511" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I511" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J511" t="inlineStr"/>
-      <c r="K511" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr"/>
+      <c r="K511" t="inlineStr"/>
       <c r="L511" t="inlineStr"/>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N511" t="inlineStr"/>
       <c r="P511" t="inlineStr">
         <is>
@@ -59000,10 +58996,10 @@
         </is>
       </c>
       <c r="Q511" t="n">
-        <v>478207</v>
+        <v>478183</v>
       </c>
       <c r="R511" t="n">
-        <v>6770501</v>
+        <v>6770433</v>
       </c>
       <c r="S511" t="n">
         <v>1</v>
@@ -59044,7 +59040,6 @@
       <c r="AE511" t="b">
         <v>0</v>
       </c>
-      <c r="AF511" t="inlineStr"/>
       <c r="AG511" t="b">
         <v>0</v>
       </c>
@@ -59175,10 +59170,10 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>118610619</v>
+        <v>118610739</v>
       </c>
       <c r="B513" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
@@ -59187,35 +59182,39 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E513" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I513" t="inlineStr"/>
-      <c r="K513" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr"/>
-      <c r="M513" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N513" t="inlineStr"/>
       <c r="P513" t="inlineStr">
         <is>
@@ -59223,10 +59222,10 @@
         </is>
       </c>
       <c r="Q513" t="n">
-        <v>478183</v>
+        <v>478207</v>
       </c>
       <c r="R513" t="n">
-        <v>6770433</v>
+        <v>6770501</v>
       </c>
       <c r="S513" t="n">
         <v>1</v>
@@ -59267,6 +59266,7 @@
       <c r="AE513" t="b">
         <v>0</v>
       </c>
+      <c r="AF513" t="inlineStr"/>
       <c r="AG513" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -11930,7 +11930,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118462365</v>
+        <v>118463045</v>
       </c>
       <c r="B101" t="n">
         <v>97853</v>
@@ -11982,10 +11982,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>478405</v>
+        <v>478292</v>
       </c>
       <c r="R101" t="n">
-        <v>6770539</v>
+        <v>6770319</v>
       </c>
       <c r="S101" t="n">
         <v>1</v>
@@ -12045,7 +12045,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118462752</v>
+        <v>118462458</v>
       </c>
       <c r="B102" t="n">
         <v>97853</v>
@@ -12097,10 +12097,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>478293</v>
+        <v>478391</v>
       </c>
       <c r="R102" t="n">
-        <v>6770400</v>
+        <v>6770492</v>
       </c>
       <c r="S102" t="n">
         <v>1</v>
@@ -12160,7 +12160,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118462570</v>
+        <v>118462164</v>
       </c>
       <c r="B103" t="n">
         <v>97853</v>
@@ -12198,7 +12198,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -12212,10 +12216,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>478322</v>
+        <v>478359</v>
       </c>
       <c r="R103" t="n">
-        <v>6770436</v>
+        <v>6770485</v>
       </c>
       <c r="S103" t="n">
         <v>1</v>
@@ -12275,7 +12279,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118462505</v>
+        <v>118462365</v>
       </c>
       <c r="B104" t="n">
         <v>97853</v>
@@ -12327,10 +12331,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>478361</v>
+        <v>478405</v>
       </c>
       <c r="R104" t="n">
-        <v>6770471</v>
+        <v>6770539</v>
       </c>
       <c r="S104" t="n">
         <v>1</v>
@@ -12390,7 +12394,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118463045</v>
+        <v>118462752</v>
       </c>
       <c r="B105" t="n">
         <v>97853</v>
@@ -12442,10 +12446,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>478292</v>
+        <v>478293</v>
       </c>
       <c r="R105" t="n">
-        <v>6770319</v>
+        <v>6770400</v>
       </c>
       <c r="S105" t="n">
         <v>1</v>
@@ -12505,7 +12509,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118462458</v>
+        <v>118462570</v>
       </c>
       <c r="B106" t="n">
         <v>97853</v>
@@ -12557,10 +12561,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>478391</v>
+        <v>478322</v>
       </c>
       <c r="R106" t="n">
-        <v>6770492</v>
+        <v>6770436</v>
       </c>
       <c r="S106" t="n">
         <v>1</v>
@@ -12620,7 +12624,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118462164</v>
+        <v>118462505</v>
       </c>
       <c r="B107" t="n">
         <v>97853</v>
@@ -12658,11 +12662,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -12676,10 +12676,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>478359</v>
+        <v>478361</v>
       </c>
       <c r="R107" t="n">
-        <v>6770485</v>
+        <v>6770471</v>
       </c>
       <c r="S107" t="n">
         <v>1</v>
@@ -15286,10 +15286,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118462616</v>
+        <v>118462304</v>
       </c>
       <c r="B130" t="n">
-        <v>78491</v>
+        <v>97853</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15298,38 +15298,43 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -15337,10 +15342,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>478368</v>
+        <v>478402</v>
       </c>
       <c r="R130" t="n">
-        <v>6770403</v>
+        <v>6770520</v>
       </c>
       <c r="S130" t="n">
         <v>1</v>
@@ -15400,7 +15405,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118462304</v>
+        <v>118462340</v>
       </c>
       <c r="B131" t="n">
         <v>97853</v>
@@ -15438,11 +15443,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -15456,10 +15457,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>478402</v>
+        <v>478401</v>
       </c>
       <c r="R131" t="n">
-        <v>6770520</v>
+        <v>6770529</v>
       </c>
       <c r="S131" t="n">
         <v>1</v>
@@ -15519,7 +15520,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118462340</v>
+        <v>118462977</v>
       </c>
       <c r="B132" t="n">
         <v>97853</v>
@@ -15571,10 +15572,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>478401</v>
+        <v>478283</v>
       </c>
       <c r="R132" t="n">
-        <v>6770529</v>
+        <v>6770322</v>
       </c>
       <c r="S132" t="n">
         <v>1</v>
@@ -15634,7 +15635,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118462977</v>
+        <v>118462263</v>
       </c>
       <c r="B133" t="n">
         <v>97853</v>
@@ -15672,7 +15673,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr"/>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K133" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -15686,10 +15691,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>478283</v>
+        <v>478401</v>
       </c>
       <c r="R133" t="n">
-        <v>6770322</v>
+        <v>6770517</v>
       </c>
       <c r="S133" t="n">
         <v>1</v>
@@ -15749,7 +15754,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118462263</v>
+        <v>118462930</v>
       </c>
       <c r="B134" t="n">
         <v>97853</v>
@@ -15787,11 +15792,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -15805,10 +15806,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>478401</v>
+        <v>478280</v>
       </c>
       <c r="R134" t="n">
-        <v>6770517</v>
+        <v>6770391</v>
       </c>
       <c r="S134" t="n">
         <v>1</v>
@@ -15868,10 +15869,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118462930</v>
+        <v>118462616</v>
       </c>
       <c r="B135" t="n">
-        <v>97853</v>
+        <v>78491</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15880,39 +15881,38 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -15920,10 +15920,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>478280</v>
+        <v>478368</v>
       </c>
       <c r="R135" t="n">
-        <v>6770391</v>
+        <v>6770403</v>
       </c>
       <c r="S135" t="n">
         <v>1</v>
@@ -17486,7 +17486,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118463069</v>
+        <v>118462785</v>
       </c>
       <c r="B149" t="n">
         <v>97853</v>
@@ -17538,10 +17538,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>478281</v>
+        <v>478286</v>
       </c>
       <c r="R149" t="n">
-        <v>6770346</v>
+        <v>6770399</v>
       </c>
       <c r="S149" t="n">
         <v>1</v>
@@ -17601,7 +17601,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118462785</v>
+        <v>118462714</v>
       </c>
       <c r="B150" t="n">
         <v>97853</v>
@@ -17653,10 +17653,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>478286</v>
+        <v>478325</v>
       </c>
       <c r="R150" t="n">
-        <v>6770399</v>
+        <v>6770392</v>
       </c>
       <c r="S150" t="n">
         <v>1</v>
@@ -17716,7 +17716,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118462714</v>
+        <v>118463069</v>
       </c>
       <c r="B151" t="n">
         <v>97853</v>
@@ -17768,10 +17768,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>478325</v>
+        <v>478281</v>
       </c>
       <c r="R151" t="n">
-        <v>6770392</v>
+        <v>6770346</v>
       </c>
       <c r="S151" t="n">
         <v>1</v>
@@ -18865,7 +18865,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>118462579</v>
+        <v>118462178</v>
       </c>
       <c r="B161" t="n">
         <v>97853</v>
@@ -18903,7 +18903,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr"/>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K161" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -18917,10 +18921,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>478318</v>
+        <v>478358</v>
       </c>
       <c r="R161" t="n">
-        <v>6770433</v>
+        <v>6770480</v>
       </c>
       <c r="S161" t="n">
         <v>1</v>
@@ -18980,7 +18984,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>118462547</v>
+        <v>118462916</v>
       </c>
       <c r="B162" t="n">
         <v>97853</v>
@@ -19032,10 +19036,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>478350</v>
+        <v>478284</v>
       </c>
       <c r="R162" t="n">
-        <v>6770467</v>
+        <v>6770405</v>
       </c>
       <c r="S162" t="n">
         <v>1</v>
@@ -19095,7 +19099,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>118462178</v>
+        <v>118462579</v>
       </c>
       <c r="B163" t="n">
         <v>97853</v>
@@ -19133,11 +19137,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -19151,10 +19151,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>478358</v>
+        <v>478318</v>
       </c>
       <c r="R163" t="n">
-        <v>6770480</v>
+        <v>6770433</v>
       </c>
       <c r="S163" t="n">
         <v>1</v>
@@ -19214,7 +19214,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>118462916</v>
+        <v>118462547</v>
       </c>
       <c r="B164" t="n">
         <v>97853</v>
@@ -19266,10 +19266,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>478284</v>
+        <v>478350</v>
       </c>
       <c r="R164" t="n">
-        <v>6770405</v>
+        <v>6770467</v>
       </c>
       <c r="S164" t="n">
         <v>1</v>
@@ -19329,10 +19329,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>118496005</v>
+        <v>118496176</v>
       </c>
       <c r="B165" t="n">
-        <v>78491</v>
+        <v>104947</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -19341,25 +19341,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>221144</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -19369,10 +19369,15 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
@@ -19380,10 +19385,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>478300</v>
+        <v>478287</v>
       </c>
       <c r="R165" t="n">
-        <v>6770489</v>
+        <v>6770544</v>
       </c>
       <c r="S165" t="n">
         <v>1</v>
@@ -19416,11 +19421,6 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>25 cm långa, kraftiga</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19448,10 +19448,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>118494230</v>
+        <v>118496005</v>
       </c>
       <c r="B166" t="n">
-        <v>97853</v>
+        <v>78491</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -19460,39 +19460,38 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
@@ -19500,10 +19499,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>478297</v>
+        <v>478300</v>
       </c>
       <c r="R166" t="n">
-        <v>6770421</v>
+        <v>6770489</v>
       </c>
       <c r="S166" t="n">
         <v>1</v>
@@ -19536,6 +19535,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2024-07-16</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>25 cm långa, kraftiga</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19563,7 +19567,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>118494222</v>
+        <v>118494230</v>
       </c>
       <c r="B167" t="n">
         <v>97853</v>
@@ -19598,7 +19602,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J167" t="inlineStr"/>
@@ -19615,10 +19619,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>478305</v>
+        <v>478297</v>
       </c>
       <c r="R167" t="n">
-        <v>6770433</v>
+        <v>6770421</v>
       </c>
       <c r="S167" t="n">
         <v>1</v>
@@ -19793,10 +19797,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>118496176</v>
+        <v>118494222</v>
       </c>
       <c r="B169" t="n">
-        <v>104947</v>
+        <v>97853</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -19805,40 +19809,36 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L169" t="inlineStr"/>
@@ -19849,10 +19849,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>478287</v>
+        <v>478305</v>
       </c>
       <c r="R169" t="n">
-        <v>6770544</v>
+        <v>6770433</v>
       </c>
       <c r="S169" t="n">
         <v>1</v>
@@ -21402,10 +21402,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>118493975</v>
+        <v>118496212</v>
       </c>
       <c r="B183" t="n">
-        <v>90511</v>
+        <v>97853</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -21414,30 +21414,39 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
@@ -21445,10 +21454,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>478308</v>
+        <v>478265</v>
       </c>
       <c r="R183" t="n">
-        <v>6770435</v>
+        <v>6770561</v>
       </c>
       <c r="S183" t="n">
         <v>1</v>
@@ -21508,7 +21517,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>118496212</v>
+        <v>118493980</v>
       </c>
       <c r="B184" t="n">
         <v>97853</v>
@@ -21541,11 +21550,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
@@ -21560,10 +21565,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>478265</v>
+        <v>478304</v>
       </c>
       <c r="R184" t="n">
-        <v>6770561</v>
+        <v>6770445</v>
       </c>
       <c r="S184" t="n">
         <v>1</v>
@@ -21623,7 +21628,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>118493980</v>
+        <v>118493978</v>
       </c>
       <c r="B185" t="n">
         <v>97853</v>
@@ -21656,7 +21661,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
@@ -21671,10 +21680,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>478304</v>
+        <v>478306</v>
       </c>
       <c r="R185" t="n">
-        <v>6770445</v>
+        <v>6770436</v>
       </c>
       <c r="S185" t="n">
         <v>1</v>
@@ -21734,10 +21743,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>118493978</v>
+        <v>118493975</v>
       </c>
       <c r="B186" t="n">
-        <v>97853</v>
+        <v>90511</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -21746,39 +21755,30 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
@@ -21786,10 +21786,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>478306</v>
+        <v>478308</v>
       </c>
       <c r="R186" t="n">
-        <v>6770436</v>
+        <v>6770435</v>
       </c>
       <c r="S186" t="n">
         <v>1</v>
@@ -21849,10 +21849,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>118495968</v>
+        <v>118496290</v>
       </c>
       <c r="B187" t="n">
-        <v>5166</v>
+        <v>78525</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -21861,36 +21861,38 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100526</v>
+        <v>185</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
@@ -21898,10 +21900,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>478303</v>
+        <v>478300</v>
       </c>
       <c r="R187" t="n">
-        <v>6770485</v>
+        <v>6770569</v>
       </c>
       <c r="S187" t="n">
         <v>1</v>
@@ -21961,10 +21963,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>118493987</v>
+        <v>118495968</v>
       </c>
       <c r="B188" t="n">
-        <v>97853</v>
+        <v>5166</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -21973,39 +21975,36 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
@@ -22013,10 +22012,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>478306</v>
+        <v>478303</v>
       </c>
       <c r="R188" t="n">
-        <v>6770444</v>
+        <v>6770485</v>
       </c>
       <c r="S188" t="n">
         <v>1</v>
@@ -22076,10 +22075,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>118496290</v>
+        <v>118493987</v>
       </c>
       <c r="B189" t="n">
-        <v>78525</v>
+        <v>97853</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -22088,25 +22087,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -22114,12 +22113,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
@@ -22127,10 +22127,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>478300</v>
+        <v>478306</v>
       </c>
       <c r="R189" t="n">
-        <v>6770569</v>
+        <v>6770444</v>
       </c>
       <c r="S189" t="n">
         <v>1</v>
@@ -22765,10 +22765,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>118496187</v>
+        <v>118493972</v>
       </c>
       <c r="B195" t="n">
-        <v>5166</v>
+        <v>97853</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -22777,36 +22777,39 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
@@ -22814,10 +22817,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>478282</v>
+        <v>478311</v>
       </c>
       <c r="R195" t="n">
-        <v>6770552</v>
+        <v>6770451</v>
       </c>
       <c r="S195" t="n">
         <v>1</v>
@@ -22877,10 +22880,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>118495913</v>
+        <v>118495822</v>
       </c>
       <c r="B196" t="n">
-        <v>78525</v>
+        <v>97853</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -22889,25 +22892,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -22915,12 +22918,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
@@ -22928,10 +22932,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>478288</v>
+        <v>478256</v>
       </c>
       <c r="R196" t="n">
-        <v>6770486</v>
+        <v>6770395</v>
       </c>
       <c r="S196" t="n">
         <v>1</v>
@@ -22991,10 +22995,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>118493972</v>
+        <v>118495913</v>
       </c>
       <c r="B197" t="n">
-        <v>97853</v>
+        <v>78525</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -23003,25 +23007,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -23029,13 +23033,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr"/>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
       <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
@@ -23043,10 +23046,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>478311</v>
+        <v>478288</v>
       </c>
       <c r="R197" t="n">
-        <v>6770451</v>
+        <v>6770486</v>
       </c>
       <c r="S197" t="n">
         <v>1</v>
@@ -23106,10 +23109,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>118495822</v>
+        <v>118496187</v>
       </c>
       <c r="B198" t="n">
-        <v>97853</v>
+        <v>5166</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -23118,39 +23121,36 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
@@ -23158,10 +23158,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>478256</v>
+        <v>478282</v>
       </c>
       <c r="R198" t="n">
-        <v>6770395</v>
+        <v>6770552</v>
       </c>
       <c r="S198" t="n">
         <v>1</v>
@@ -24717,10 +24717,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>118495982</v>
+        <v>118494003</v>
       </c>
       <c r="B212" t="n">
-        <v>78525</v>
+        <v>57290</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -24733,34 +24733,31 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
@@ -24768,10 +24765,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>478304</v>
+        <v>478303</v>
       </c>
       <c r="R212" t="n">
-        <v>6770488</v>
+        <v>6770456</v>
       </c>
       <c r="S212" t="n">
         <v>1</v>
@@ -24812,7 +24809,6 @@
       <c r="AE212" t="b">
         <v>0</v>
       </c>
-      <c r="AF212" t="inlineStr"/>
       <c r="AG212" t="b">
         <v>0</v>
       </c>
@@ -24831,10 +24827,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>118494003</v>
+        <v>118495982</v>
       </c>
       <c r="B213" t="n">
-        <v>57290</v>
+        <v>78525</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -24847,31 +24843,34 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K213" t="inlineStr"/>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
@@ -24879,10 +24878,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>478303</v>
+        <v>478304</v>
       </c>
       <c r="R213" t="n">
-        <v>6770456</v>
+        <v>6770488</v>
       </c>
       <c r="S213" t="n">
         <v>1</v>
@@ -24923,6 +24922,7 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
+      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
@@ -26088,10 +26088,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>118553085</v>
+        <v>118552221</v>
       </c>
       <c r="B224" t="n">
-        <v>57443</v>
+        <v>97853</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -26100,35 +26100,39 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
@@ -26136,13 +26140,13 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>478361</v>
+        <v>478277</v>
       </c>
       <c r="R224" t="n">
-        <v>6770534</v>
+        <v>6770726</v>
       </c>
       <c r="S224" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -26198,7 +26202,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>118552221</v>
+        <v>118551408</v>
       </c>
       <c r="B225" t="n">
         <v>97853</v>
@@ -26233,7 +26237,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J225" t="inlineStr"/>
@@ -26250,10 +26254,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>478277</v>
+        <v>478300</v>
       </c>
       <c r="R225" t="n">
-        <v>6770726</v>
+        <v>6770603</v>
       </c>
       <c r="S225" t="n">
         <v>1</v>
@@ -26312,7 +26316,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>118551408</v>
+        <v>118551493</v>
       </c>
       <c r="B226" t="n">
         <v>97853</v>
@@ -26347,7 +26351,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J226" t="inlineStr"/>
@@ -26364,10 +26368,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>478300</v>
+        <v>478330</v>
       </c>
       <c r="R226" t="n">
-        <v>6770603</v>
+        <v>6770669</v>
       </c>
       <c r="S226" t="n">
         <v>1</v>
@@ -26426,7 +26430,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>118551493</v>
+        <v>118552745</v>
       </c>
       <c r="B227" t="n">
         <v>97853</v>
@@ -26478,10 +26482,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>478330</v>
+        <v>478482</v>
       </c>
       <c r="R227" t="n">
-        <v>6770669</v>
+        <v>6770784</v>
       </c>
       <c r="S227" t="n">
         <v>1</v>
@@ -26522,6 +26526,7 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
+      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -26540,7 +26545,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>118552745</v>
+        <v>118552241</v>
       </c>
       <c r="B228" t="n">
         <v>97853</v>
@@ -26575,7 +26580,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J228" t="inlineStr"/>
@@ -26592,10 +26597,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>478482</v>
+        <v>478310</v>
       </c>
       <c r="R228" t="n">
-        <v>6770784</v>
+        <v>6770728</v>
       </c>
       <c r="S228" t="n">
         <v>1</v>
@@ -26636,7 +26641,6 @@
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
@@ -26655,7 +26659,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>118552241</v>
+        <v>118552243</v>
       </c>
       <c r="B229" t="n">
         <v>97853</v>
@@ -26690,7 +26694,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J229" t="inlineStr"/>
@@ -26707,10 +26711,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>478310</v>
+        <v>478301</v>
       </c>
       <c r="R229" t="n">
-        <v>6770728</v>
+        <v>6770717</v>
       </c>
       <c r="S229" t="n">
         <v>1</v>
@@ -26769,10 +26773,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>118552243</v>
+        <v>118553085</v>
       </c>
       <c r="B230" t="n">
-        <v>97853</v>
+        <v>57443</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -26781,39 +26785,35 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr"/>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
@@ -26821,13 +26821,13 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>478301</v>
+        <v>478361</v>
       </c>
       <c r="R230" t="n">
-        <v>6770717</v>
+        <v>6770534</v>
       </c>
       <c r="S230" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>118551892</v>
+        <v>118551499</v>
       </c>
       <c r="B243" t="n">
         <v>97853</v>
@@ -28290,7 +28290,7 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J243" t="inlineStr"/>
@@ -28310,7 +28310,7 @@
         <v>478331</v>
       </c>
       <c r="R243" t="n">
-        <v>6770713</v>
+        <v>6770670</v>
       </c>
       <c r="S243" t="n">
         <v>1</v>
@@ -28351,7 +28351,6 @@
       <c r="AE243" t="b">
         <v>0</v>
       </c>
-      <c r="AF243" t="inlineStr"/>
       <c r="AG243" t="b">
         <v>0</v>
       </c>
@@ -28370,7 +28369,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>118551499</v>
+        <v>118551778</v>
       </c>
       <c r="B244" t="n">
         <v>97853</v>
@@ -28405,7 +28404,7 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J244" t="inlineStr"/>
@@ -28422,10 +28421,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>478331</v>
+        <v>478322</v>
       </c>
       <c r="R244" t="n">
-        <v>6770670</v>
+        <v>6770699</v>
       </c>
       <c r="S244" t="n">
         <v>1</v>
@@ -28484,7 +28483,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>118551778</v>
+        <v>118551892</v>
       </c>
       <c r="B245" t="n">
         <v>97853</v>
@@ -28536,10 +28535,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>478322</v>
+        <v>478331</v>
       </c>
       <c r="R245" t="n">
-        <v>6770699</v>
+        <v>6770713</v>
       </c>
       <c r="S245" t="n">
         <v>1</v>
@@ -28580,6 +28579,7 @@
       <c r="AE245" t="b">
         <v>0</v>
       </c>
+      <c r="AF245" t="inlineStr"/>
       <c r="AG245" t="b">
         <v>0</v>
       </c>
@@ -28598,10 +28598,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>118551318</v>
+        <v>118553013</v>
       </c>
       <c r="B246" t="n">
-        <v>58133</v>
+        <v>97853</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -28610,25 +28610,25 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -28637,9 +28637,12 @@
         </is>
       </c>
       <c r="J246" t="inlineStr"/>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr"/>
       <c r="N246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
@@ -28647,10 +28650,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>478326</v>
+        <v>478467</v>
       </c>
       <c r="R246" t="n">
-        <v>6770593</v>
+        <v>6770793</v>
       </c>
       <c r="S246" t="n">
         <v>1</v>
@@ -28691,6 +28694,7 @@
       <c r="AE246" t="b">
         <v>0</v>
       </c>
+      <c r="AF246" t="inlineStr"/>
       <c r="AG246" t="b">
         <v>0</v>
       </c>
@@ -28709,7 +28713,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>118553013</v>
+        <v>118552205</v>
       </c>
       <c r="B247" t="n">
         <v>97853</v>
@@ -28761,10 +28765,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>478467</v>
+        <v>478346</v>
       </c>
       <c r="R247" t="n">
-        <v>6770793</v>
+        <v>6770808</v>
       </c>
       <c r="S247" t="n">
         <v>1</v>
@@ -28805,7 +28809,6 @@
       <c r="AE247" t="b">
         <v>0</v>
       </c>
-      <c r="AF247" t="inlineStr"/>
       <c r="AG247" t="b">
         <v>0</v>
       </c>
@@ -28824,7 +28827,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>118552205</v>
+        <v>118552269</v>
       </c>
       <c r="B248" t="n">
         <v>97853</v>
@@ -28876,10 +28879,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>478346</v>
+        <v>478207</v>
       </c>
       <c r="R248" t="n">
-        <v>6770808</v>
+        <v>6770703</v>
       </c>
       <c r="S248" t="n">
         <v>1</v>
@@ -28920,6 +28923,7 @@
       <c r="AE248" t="b">
         <v>0</v>
       </c>
+      <c r="AF248" t="inlineStr"/>
       <c r="AG248" t="b">
         <v>0</v>
       </c>
@@ -28938,7 +28942,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>118552269</v>
+        <v>118552991</v>
       </c>
       <c r="B249" t="n">
         <v>97853</v>
@@ -28973,7 +28977,7 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J249" t="inlineStr"/>
@@ -28990,10 +28994,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>478207</v>
+        <v>478461</v>
       </c>
       <c r="R249" t="n">
-        <v>6770703</v>
+        <v>6770811</v>
       </c>
       <c r="S249" t="n">
         <v>1</v>
@@ -29053,7 +29057,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>118552991</v>
+        <v>118552517</v>
       </c>
       <c r="B250" t="n">
         <v>97853</v>
@@ -29088,7 +29092,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J250" t="inlineStr"/>
@@ -29105,10 +29109,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>478461</v>
+        <v>478418</v>
       </c>
       <c r="R250" t="n">
-        <v>6770811</v>
+        <v>6770615</v>
       </c>
       <c r="S250" t="n">
         <v>1</v>
@@ -29168,7 +29172,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>118552517</v>
+        <v>118551416</v>
       </c>
       <c r="B251" t="n">
         <v>97853</v>
@@ -29220,10 +29224,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>478418</v>
+        <v>478398</v>
       </c>
       <c r="R251" t="n">
-        <v>6770615</v>
+        <v>6770626</v>
       </c>
       <c r="S251" t="n">
         <v>1</v>
@@ -29264,7 +29268,6 @@
       <c r="AE251" t="b">
         <v>0</v>
       </c>
-      <c r="AF251" t="inlineStr"/>
       <c r="AG251" t="b">
         <v>0</v>
       </c>
@@ -29283,7 +29286,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>118551416</v>
+        <v>118552620</v>
       </c>
       <c r="B252" t="n">
         <v>97853</v>
@@ -29335,10 +29338,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>478398</v>
+        <v>478419</v>
       </c>
       <c r="R252" t="n">
-        <v>6770626</v>
+        <v>6770616</v>
       </c>
       <c r="S252" t="n">
         <v>1</v>
@@ -29379,6 +29382,7 @@
       <c r="AE252" t="b">
         <v>0</v>
       </c>
+      <c r="AF252" t="inlineStr"/>
       <c r="AG252" t="b">
         <v>0</v>
       </c>
@@ -29397,7 +29401,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>118552620</v>
+        <v>118551897</v>
       </c>
       <c r="B253" t="n">
         <v>97853</v>
@@ -29432,7 +29436,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J253" t="inlineStr"/>
@@ -29449,10 +29453,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>478419</v>
+        <v>478334</v>
       </c>
       <c r="R253" t="n">
-        <v>6770616</v>
+        <v>6770714</v>
       </c>
       <c r="S253" t="n">
         <v>1</v>
@@ -29512,10 +29516,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>118551897</v>
+        <v>118551318</v>
       </c>
       <c r="B254" t="n">
-        <v>97853</v>
+        <v>58133</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -29524,39 +29528,36 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J254" t="inlineStr"/>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
       <c r="N254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
@@ -29564,10 +29565,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>478334</v>
+        <v>478326</v>
       </c>
       <c r="R254" t="n">
-        <v>6770714</v>
+        <v>6770593</v>
       </c>
       <c r="S254" t="n">
         <v>1</v>
@@ -29608,7 +29609,6 @@
       <c r="AE254" t="b">
         <v>0</v>
       </c>
-      <c r="AF254" t="inlineStr"/>
       <c r="AG254" t="b">
         <v>0</v>
       </c>
@@ -31461,7 +31461,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>118551787</v>
+        <v>118552739</v>
       </c>
       <c r="B271" t="n">
         <v>97853</v>
@@ -31496,7 +31496,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J271" t="inlineStr"/>
@@ -31513,10 +31513,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>478332</v>
+        <v>478471</v>
       </c>
       <c r="R271" t="n">
-        <v>6770706</v>
+        <v>6770772</v>
       </c>
       <c r="S271" t="n">
         <v>1</v>
@@ -31557,6 +31557,7 @@
       <c r="AE271" t="b">
         <v>0</v>
       </c>
+      <c r="AF271" t="inlineStr"/>
       <c r="AG271" t="b">
         <v>0</v>
       </c>
@@ -31575,7 +31576,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>118552749</v>
+        <v>118551787</v>
       </c>
       <c r="B272" t="n">
         <v>97853</v>
@@ -31610,7 +31611,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J272" t="inlineStr"/>
@@ -31627,10 +31628,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>478499</v>
+        <v>478332</v>
       </c>
       <c r="R272" t="n">
-        <v>6770799</v>
+        <v>6770706</v>
       </c>
       <c r="S272" t="n">
         <v>1</v>
@@ -31671,7 +31672,6 @@
       <c r="AE272" t="b">
         <v>0</v>
       </c>
-      <c r="AF272" t="inlineStr"/>
       <c r="AG272" t="b">
         <v>0</v>
       </c>
@@ -31690,7 +31690,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>118552703</v>
+        <v>118552749</v>
       </c>
       <c r="B273" t="n">
         <v>97853</v>
@@ -31725,7 +31725,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J273" t="inlineStr"/>
@@ -31742,10 +31742,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>478481</v>
+        <v>478499</v>
       </c>
       <c r="R273" t="n">
-        <v>6770713</v>
+        <v>6770799</v>
       </c>
       <c r="S273" t="n">
         <v>1</v>
@@ -31805,7 +31805,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>118552680</v>
+        <v>118552703</v>
       </c>
       <c r="B274" t="n">
         <v>97853</v>
@@ -31857,10 +31857,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>478464</v>
+        <v>478481</v>
       </c>
       <c r="R274" t="n">
-        <v>6770688</v>
+        <v>6770713</v>
       </c>
       <c r="S274" t="n">
         <v>1</v>
@@ -31920,7 +31920,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>118552524</v>
+        <v>118552680</v>
       </c>
       <c r="B275" t="n">
         <v>97853</v>
@@ -31961,7 +31961,7 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L275" t="inlineStr"/>
@@ -31972,10 +31972,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>478415</v>
+        <v>478464</v>
       </c>
       <c r="R275" t="n">
-        <v>6770617</v>
+        <v>6770688</v>
       </c>
       <c r="S275" t="n">
         <v>1</v>
@@ -32035,7 +32035,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>118552105</v>
+        <v>118552524</v>
       </c>
       <c r="B276" t="n">
         <v>97853</v>
@@ -32076,7 +32076,7 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L276" t="inlineStr"/>
@@ -32087,10 +32087,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>478314</v>
+        <v>478415</v>
       </c>
       <c r="R276" t="n">
-        <v>6770748</v>
+        <v>6770617</v>
       </c>
       <c r="S276" t="n">
         <v>1</v>
@@ -32131,6 +32131,7 @@
       <c r="AE276" t="b">
         <v>0</v>
       </c>
+      <c r="AF276" t="inlineStr"/>
       <c r="AG276" t="b">
         <v>0</v>
       </c>
@@ -32149,7 +32150,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>118552473</v>
+        <v>118552105</v>
       </c>
       <c r="B277" t="n">
         <v>97853</v>
@@ -32184,13 +32185,13 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L277" t="inlineStr"/>
@@ -32201,10 +32202,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>478404</v>
+        <v>478314</v>
       </c>
       <c r="R277" t="n">
-        <v>6770597</v>
+        <v>6770748</v>
       </c>
       <c r="S277" t="n">
         <v>1</v>
@@ -32245,7 +32246,6 @@
       <c r="AE277" t="b">
         <v>0</v>
       </c>
-      <c r="AF277" t="inlineStr"/>
       <c r="AG277" t="b">
         <v>0</v>
       </c>
@@ -32264,7 +32264,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>118552088</v>
+        <v>118552473</v>
       </c>
       <c r="B278" t="n">
         <v>97853</v>
@@ -32299,13 +32299,13 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L278" t="inlineStr"/>
@@ -32316,10 +32316,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>478372</v>
+        <v>478404</v>
       </c>
       <c r="R278" t="n">
-        <v>6770717</v>
+        <v>6770597</v>
       </c>
       <c r="S278" t="n">
         <v>1</v>
@@ -32360,6 +32360,7 @@
       <c r="AE278" t="b">
         <v>0</v>
       </c>
+      <c r="AF278" t="inlineStr"/>
       <c r="AG278" t="b">
         <v>0</v>
       </c>
@@ -32378,7 +32379,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>118551224</v>
+        <v>118552088</v>
       </c>
       <c r="B279" t="n">
         <v>97853</v>
@@ -32430,10 +32431,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>478365</v>
+        <v>478372</v>
       </c>
       <c r="R279" t="n">
-        <v>6770570</v>
+        <v>6770717</v>
       </c>
       <c r="S279" t="n">
         <v>1</v>
@@ -32474,7 +32475,6 @@
       <c r="AE279" t="b">
         <v>0</v>
       </c>
-      <c r="AF279" t="inlineStr"/>
       <c r="AG279" t="b">
         <v>0</v>
       </c>
@@ -32486,14 +32486,14 @@
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>118552724</v>
+        <v>118551224</v>
       </c>
       <c r="B280" t="n">
         <v>97853</v>
@@ -32545,10 +32545,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>478468</v>
+        <v>478365</v>
       </c>
       <c r="R280" t="n">
-        <v>6770769</v>
+        <v>6770570</v>
       </c>
       <c r="S280" t="n">
         <v>1</v>
@@ -32601,14 +32601,14 @@
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>118552739</v>
+        <v>118552724</v>
       </c>
       <c r="B281" t="n">
         <v>97853</v>
@@ -32643,7 +32643,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J281" t="inlineStr"/>
@@ -32660,10 +32660,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>478471</v>
+        <v>478468</v>
       </c>
       <c r="R281" t="n">
-        <v>6770772</v>
+        <v>6770769</v>
       </c>
       <c r="S281" t="n">
         <v>1</v>
@@ -39140,7 +39140,7 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>118552416</v>
+        <v>118552260</v>
       </c>
       <c r="B338" t="n">
         <v>97853</v>
@@ -39175,7 +39175,7 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J338" t="inlineStr"/>
@@ -39192,10 +39192,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>478407</v>
+        <v>478290</v>
       </c>
       <c r="R338" t="n">
-        <v>6770575</v>
+        <v>6770717</v>
       </c>
       <c r="S338" t="n">
         <v>1</v>
@@ -39255,7 +39255,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>118552260</v>
+        <v>118552494</v>
       </c>
       <c r="B339" t="n">
         <v>97853</v>
@@ -39290,7 +39290,7 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J339" t="inlineStr"/>
@@ -39307,10 +39307,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>478290</v>
+        <v>478411</v>
       </c>
       <c r="R339" t="n">
-        <v>6770717</v>
+        <v>6770610</v>
       </c>
       <c r="S339" t="n">
         <v>1</v>
@@ -39370,7 +39370,7 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>118552494</v>
+        <v>118551531</v>
       </c>
       <c r="B340" t="n">
         <v>97853</v>
@@ -39405,7 +39405,7 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J340" t="inlineStr"/>
@@ -39422,10 +39422,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>478411</v>
+        <v>478313</v>
       </c>
       <c r="R340" t="n">
-        <v>6770610</v>
+        <v>6770678</v>
       </c>
       <c r="S340" t="n">
         <v>1</v>
@@ -39466,7 +39466,6 @@
       <c r="AE340" t="b">
         <v>0</v>
       </c>
-      <c r="AF340" t="inlineStr"/>
       <c r="AG340" t="b">
         <v>0</v>
       </c>
@@ -39485,7 +39484,7 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>118551531</v>
+        <v>118552217</v>
       </c>
       <c r="B341" t="n">
         <v>97853</v>
@@ -39520,7 +39519,7 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J341" t="inlineStr"/>
@@ -39537,10 +39536,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>478313</v>
+        <v>478288</v>
       </c>
       <c r="R341" t="n">
-        <v>6770678</v>
+        <v>6770773</v>
       </c>
       <c r="S341" t="n">
         <v>1</v>
@@ -39599,7 +39598,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>118551811</v>
+        <v>118551869</v>
       </c>
       <c r="B342" t="n">
         <v>97853</v>
@@ -39634,7 +39633,7 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J342" t="inlineStr"/>
@@ -39651,10 +39650,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>478343</v>
+        <v>478329</v>
       </c>
       <c r="R342" t="n">
-        <v>6770689</v>
+        <v>6770718</v>
       </c>
       <c r="S342" t="n">
         <v>1</v>
@@ -39695,6 +39694,7 @@
       <c r="AE342" t="b">
         <v>0</v>
       </c>
+      <c r="AF342" t="inlineStr"/>
       <c r="AG342" t="b">
         <v>0</v>
       </c>
@@ -39713,7 +39713,7 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>118551447</v>
+        <v>118551813</v>
       </c>
       <c r="B343" t="n">
         <v>97853</v>
@@ -39765,10 +39765,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>478341</v>
+        <v>478340</v>
       </c>
       <c r="R343" t="n">
-        <v>6770655</v>
+        <v>6770689</v>
       </c>
       <c r="S343" t="n">
         <v>1</v>
@@ -39827,7 +39827,7 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>118552217</v>
+        <v>118552309</v>
       </c>
       <c r="B344" t="n">
         <v>97853</v>
@@ -39879,10 +39879,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>478288</v>
+        <v>478296</v>
       </c>
       <c r="R344" t="n">
-        <v>6770773</v>
+        <v>6770679</v>
       </c>
       <c r="S344" t="n">
         <v>1</v>
@@ -39923,6 +39923,7 @@
       <c r="AE344" t="b">
         <v>0</v>
       </c>
+      <c r="AF344" t="inlineStr"/>
       <c r="AG344" t="b">
         <v>0</v>
       </c>
@@ -39941,7 +39942,7 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>118551869</v>
+        <v>118552162</v>
       </c>
       <c r="B345" t="n">
         <v>97853</v>
@@ -39976,7 +39977,7 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J345" t="inlineStr"/>
@@ -39993,10 +39994,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>478329</v>
+        <v>478349</v>
       </c>
       <c r="R345" t="n">
-        <v>6770718</v>
+        <v>6770751</v>
       </c>
       <c r="S345" t="n">
         <v>1</v>
@@ -40037,7 +40038,6 @@
       <c r="AE345" t="b">
         <v>0</v>
       </c>
-      <c r="AF345" t="inlineStr"/>
       <c r="AG345" t="b">
         <v>0</v>
       </c>
@@ -40056,7 +40056,7 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>118551813</v>
+        <v>118552416</v>
       </c>
       <c r="B346" t="n">
         <v>97853</v>
@@ -40091,7 +40091,7 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J346" t="inlineStr"/>
@@ -40108,10 +40108,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>478340</v>
+        <v>478407</v>
       </c>
       <c r="R346" t="n">
-        <v>6770689</v>
+        <v>6770575</v>
       </c>
       <c r="S346" t="n">
         <v>1</v>
@@ -40152,6 +40152,7 @@
       <c r="AE346" t="b">
         <v>0</v>
       </c>
+      <c r="AF346" t="inlineStr"/>
       <c r="AG346" t="b">
         <v>0</v>
       </c>
@@ -40170,7 +40171,7 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>118553035</v>
+        <v>118551811</v>
       </c>
       <c r="B347" t="n">
         <v>97853</v>
@@ -40205,7 +40206,7 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J347" t="inlineStr"/>
@@ -40222,10 +40223,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>478473</v>
+        <v>478343</v>
       </c>
       <c r="R347" t="n">
-        <v>6770776</v>
+        <v>6770689</v>
       </c>
       <c r="S347" t="n">
         <v>1</v>
@@ -40266,7 +40267,6 @@
       <c r="AE347" t="b">
         <v>0</v>
       </c>
-      <c r="AF347" t="inlineStr"/>
       <c r="AG347" t="b">
         <v>0</v>
       </c>
@@ -40285,7 +40285,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>118552309</v>
+        <v>118551447</v>
       </c>
       <c r="B348" t="n">
         <v>97853</v>
@@ -40337,10 +40337,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>478296</v>
+        <v>478341</v>
       </c>
       <c r="R348" t="n">
-        <v>6770679</v>
+        <v>6770655</v>
       </c>
       <c r="S348" t="n">
         <v>1</v>
@@ -40381,7 +40381,6 @@
       <c r="AE348" t="b">
         <v>0</v>
       </c>
-      <c r="AF348" t="inlineStr"/>
       <c r="AG348" t="b">
         <v>0</v>
       </c>
@@ -40400,7 +40399,7 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>118552162</v>
+        <v>118553035</v>
       </c>
       <c r="B349" t="n">
         <v>97853</v>
@@ -40452,10 +40451,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>478349</v>
+        <v>478473</v>
       </c>
       <c r="R349" t="n">
-        <v>6770751</v>
+        <v>6770776</v>
       </c>
       <c r="S349" t="n">
         <v>1</v>
@@ -40496,6 +40495,7 @@
       <c r="AE349" t="b">
         <v>0</v>
       </c>
+      <c r="AF349" t="inlineStr"/>
       <c r="AG349" t="b">
         <v>0</v>
       </c>
@@ -41432,7 +41432,7 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>118552328</v>
+        <v>118552948</v>
       </c>
       <c r="B358" t="n">
         <v>97853</v>
@@ -41484,10 +41484,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>478306</v>
+        <v>478448</v>
       </c>
       <c r="R358" t="n">
-        <v>6770644</v>
+        <v>6770855</v>
       </c>
       <c r="S358" t="n">
         <v>1</v>
@@ -41547,7 +41547,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>118552218</v>
+        <v>118552328</v>
       </c>
       <c r="B359" t="n">
         <v>97853</v>
@@ -41599,10 +41599,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>478284</v>
+        <v>478306</v>
       </c>
       <c r="R359" t="n">
-        <v>6770727</v>
+        <v>6770644</v>
       </c>
       <c r="S359" t="n">
         <v>1</v>
@@ -41643,6 +41643,7 @@
       <c r="AE359" t="b">
         <v>0</v>
       </c>
+      <c r="AF359" t="inlineStr"/>
       <c r="AG359" t="b">
         <v>0</v>
       </c>
@@ -41661,7 +41662,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>118551455</v>
+        <v>118552218</v>
       </c>
       <c r="B360" t="n">
         <v>97853</v>
@@ -41713,10 +41714,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>478332</v>
+        <v>478284</v>
       </c>
       <c r="R360" t="n">
-        <v>6770666</v>
+        <v>6770727</v>
       </c>
       <c r="S360" t="n">
         <v>1</v>
@@ -41775,7 +41776,7 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>118552948</v>
+        <v>118552862</v>
       </c>
       <c r="B361" t="n">
         <v>97853</v>
@@ -41810,7 +41811,7 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J361" t="inlineStr"/>
@@ -41830,7 +41831,7 @@
         <v>478448</v>
       </c>
       <c r="R361" t="n">
-        <v>6770855</v>
+        <v>6770853</v>
       </c>
       <c r="S361" t="n">
         <v>1</v>
@@ -41890,7 +41891,7 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>118552862</v>
+        <v>118551455</v>
       </c>
       <c r="B362" t="n">
         <v>97853</v>
@@ -41925,7 +41926,7 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J362" t="inlineStr"/>
@@ -41942,10 +41943,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>478448</v>
+        <v>478332</v>
       </c>
       <c r="R362" t="n">
-        <v>6770853</v>
+        <v>6770666</v>
       </c>
       <c r="S362" t="n">
         <v>1</v>
@@ -41986,7 +41987,6 @@
       <c r="AE362" t="b">
         <v>0</v>
       </c>
-      <c r="AF362" t="inlineStr"/>
       <c r="AG362" t="b">
         <v>0</v>
       </c>
@@ -42005,7 +42005,7 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>118551541</v>
+        <v>118552502</v>
       </c>
       <c r="B363" t="n">
         <v>97853</v>
@@ -42040,7 +42040,7 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J363" t="inlineStr"/>
@@ -42057,10 +42057,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>478311</v>
+        <v>478411</v>
       </c>
       <c r="R363" t="n">
-        <v>6770690</v>
+        <v>6770608</v>
       </c>
       <c r="S363" t="n">
         <v>1</v>
@@ -42101,6 +42101,7 @@
       <c r="AE363" t="b">
         <v>0</v>
       </c>
+      <c r="AF363" t="inlineStr"/>
       <c r="AG363" t="b">
         <v>0</v>
       </c>
@@ -42119,7 +42120,7 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>118551397</v>
+        <v>118551438</v>
       </c>
       <c r="B364" t="n">
         <v>97853</v>
@@ -42171,10 +42172,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>478302</v>
+        <v>478348</v>
       </c>
       <c r="R364" t="n">
-        <v>6770606</v>
+        <v>6770659</v>
       </c>
       <c r="S364" t="n">
         <v>1</v>
@@ -42233,7 +42234,7 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>118552502</v>
+        <v>118552312</v>
       </c>
       <c r="B365" t="n">
         <v>97853</v>
@@ -42285,10 +42286,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>478411</v>
+        <v>478289</v>
       </c>
       <c r="R365" t="n">
-        <v>6770608</v>
+        <v>6770655</v>
       </c>
       <c r="S365" t="n">
         <v>1</v>
@@ -42348,7 +42349,7 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>118551438</v>
+        <v>118552201</v>
       </c>
       <c r="B366" t="n">
         <v>97853</v>
@@ -42400,10 +42401,10 @@
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>478348</v>
+        <v>478354</v>
       </c>
       <c r="R366" t="n">
-        <v>6770659</v>
+        <v>6770801</v>
       </c>
       <c r="S366" t="n">
         <v>1</v>
@@ -42462,7 +42463,7 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>118552312</v>
+        <v>118553042</v>
       </c>
       <c r="B367" t="n">
         <v>97853</v>
@@ -42497,7 +42498,7 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J367" t="inlineStr"/>
@@ -42514,10 +42515,10 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>478289</v>
+        <v>478471</v>
       </c>
       <c r="R367" t="n">
-        <v>6770655</v>
+        <v>6770767</v>
       </c>
       <c r="S367" t="n">
         <v>1</v>
@@ -42577,7 +42578,7 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>118552201</v>
+        <v>118552728</v>
       </c>
       <c r="B368" t="n">
         <v>97853</v>
@@ -42612,7 +42613,7 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J368" t="inlineStr"/>
@@ -42629,10 +42630,10 @@
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>478354</v>
+        <v>478474</v>
       </c>
       <c r="R368" t="n">
-        <v>6770801</v>
+        <v>6770768</v>
       </c>
       <c r="S368" t="n">
         <v>1</v>
@@ -42673,6 +42674,7 @@
       <c r="AE368" t="b">
         <v>0</v>
       </c>
+      <c r="AF368" t="inlineStr"/>
       <c r="AG368" t="b">
         <v>0</v>
       </c>
@@ -42691,7 +42693,7 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>118553042</v>
+        <v>118552951</v>
       </c>
       <c r="B369" t="n">
         <v>97853</v>
@@ -42726,7 +42728,7 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J369" t="inlineStr"/>
@@ -42743,10 +42745,10 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>478471</v>
+        <v>478444</v>
       </c>
       <c r="R369" t="n">
-        <v>6770767</v>
+        <v>6770854</v>
       </c>
       <c r="S369" t="n">
         <v>1</v>
@@ -42806,7 +42808,7 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>118552728</v>
+        <v>118552431</v>
       </c>
       <c r="B370" t="n">
         <v>97853</v>
@@ -42841,7 +42843,7 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J370" t="inlineStr"/>
@@ -42858,10 +42860,10 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>478474</v>
+        <v>478409</v>
       </c>
       <c r="R370" t="n">
-        <v>6770768</v>
+        <v>6770592</v>
       </c>
       <c r="S370" t="n">
         <v>1</v>
@@ -42921,7 +42923,7 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>118552951</v>
+        <v>118553038</v>
       </c>
       <c r="B371" t="n">
         <v>97853</v>
@@ -42956,13 +42958,13 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L371" t="inlineStr"/>
@@ -42973,10 +42975,10 @@
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>478444</v>
+        <v>478474</v>
       </c>
       <c r="R371" t="n">
-        <v>6770854</v>
+        <v>6770776</v>
       </c>
       <c r="S371" t="n">
         <v>1</v>
@@ -43036,7 +43038,7 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>118552431</v>
+        <v>118551541</v>
       </c>
       <c r="B372" t="n">
         <v>97853</v>
@@ -43088,10 +43090,10 @@
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>478409</v>
+        <v>478311</v>
       </c>
       <c r="R372" t="n">
-        <v>6770592</v>
+        <v>6770690</v>
       </c>
       <c r="S372" t="n">
         <v>1</v>
@@ -43132,7 +43134,6 @@
       <c r="AE372" t="b">
         <v>0</v>
       </c>
-      <c r="AF372" t="inlineStr"/>
       <c r="AG372" t="b">
         <v>0</v>
       </c>
@@ -43151,7 +43152,7 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>118553038</v>
+        <v>118551397</v>
       </c>
       <c r="B373" t="n">
         <v>97853</v>
@@ -43192,7 +43193,7 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L373" t="inlineStr"/>
@@ -43203,10 +43204,10 @@
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>478474</v>
+        <v>478302</v>
       </c>
       <c r="R373" t="n">
-        <v>6770776</v>
+        <v>6770606</v>
       </c>
       <c r="S373" t="n">
         <v>1</v>
@@ -43247,7 +43248,6 @@
       <c r="AE373" t="b">
         <v>0</v>
       </c>
-      <c r="AF373" t="inlineStr"/>
       <c r="AG373" t="b">
         <v>0</v>
       </c>
@@ -46359,7 +46359,7 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>118552712</v>
+        <v>118551476</v>
       </c>
       <c r="B401" t="n">
         <v>97853</v>
@@ -46400,7 +46400,7 @@
       <c r="J401" t="inlineStr"/>
       <c r="K401" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L401" t="inlineStr"/>
@@ -46411,10 +46411,10 @@
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>478482</v>
+        <v>478332</v>
       </c>
       <c r="R401" t="n">
-        <v>6770716</v>
+        <v>6770679</v>
       </c>
       <c r="S401" t="n">
         <v>1</v>
@@ -46455,7 +46455,6 @@
       <c r="AE401" t="b">
         <v>0</v>
       </c>
-      <c r="AF401" t="inlineStr"/>
       <c r="AG401" t="b">
         <v>0</v>
       </c>
@@ -46474,7 +46473,7 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>118551953</v>
+        <v>118551819</v>
       </c>
       <c r="B402" t="n">
         <v>97853</v>
@@ -46526,10 +46525,10 @@
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>478354</v>
+        <v>478353</v>
       </c>
       <c r="R402" t="n">
-        <v>6770671</v>
+        <v>6770678</v>
       </c>
       <c r="S402" t="n">
         <v>1</v>
@@ -46570,7 +46569,6 @@
       <c r="AE402" t="b">
         <v>0</v>
       </c>
-      <c r="AF402" t="inlineStr"/>
       <c r="AG402" t="b">
         <v>0</v>
       </c>
@@ -46589,7 +46587,7 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>118551476</v>
+        <v>118552100</v>
       </c>
       <c r="B403" t="n">
         <v>97853</v>
@@ -46624,13 +46622,13 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L403" t="inlineStr"/>
@@ -46641,10 +46639,10 @@
         </is>
       </c>
       <c r="Q403" t="n">
-        <v>478332</v>
+        <v>478320</v>
       </c>
       <c r="R403" t="n">
-        <v>6770679</v>
+        <v>6770737</v>
       </c>
       <c r="S403" t="n">
         <v>1</v>
@@ -46703,7 +46701,7 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>118551819</v>
+        <v>118551900</v>
       </c>
       <c r="B404" t="n">
         <v>97853</v>
@@ -46758,7 +46756,7 @@
         <v>478353</v>
       </c>
       <c r="R404" t="n">
-        <v>6770678</v>
+        <v>6770674</v>
       </c>
       <c r="S404" t="n">
         <v>1</v>
@@ -46799,6 +46797,7 @@
       <c r="AE404" t="b">
         <v>0</v>
       </c>
+      <c r="AF404" t="inlineStr"/>
       <c r="AG404" t="b">
         <v>0</v>
       </c>
@@ -46817,7 +46816,7 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>118552100</v>
+        <v>118552712</v>
       </c>
       <c r="B405" t="n">
         <v>97853</v>
@@ -46852,7 +46851,7 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J405" t="inlineStr"/>
@@ -46869,10 +46868,10 @@
         </is>
       </c>
       <c r="Q405" t="n">
-        <v>478320</v>
+        <v>478482</v>
       </c>
       <c r="R405" t="n">
-        <v>6770737</v>
+        <v>6770716</v>
       </c>
       <c r="S405" t="n">
         <v>1</v>
@@ -46913,6 +46912,7 @@
       <c r="AE405" t="b">
         <v>0</v>
       </c>
+      <c r="AF405" t="inlineStr"/>
       <c r="AG405" t="b">
         <v>0</v>
       </c>
@@ -46931,7 +46931,7 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>118551900</v>
+        <v>118551953</v>
       </c>
       <c r="B406" t="n">
         <v>97853</v>
@@ -46983,10 +46983,10 @@
         </is>
       </c>
       <c r="Q406" t="n">
-        <v>478353</v>
+        <v>478354</v>
       </c>
       <c r="R406" t="n">
-        <v>6770674</v>
+        <v>6770671</v>
       </c>
       <c r="S406" t="n">
         <v>1</v>
@@ -49568,10 +49568,10 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>118568160</v>
+        <v>118568532</v>
       </c>
       <c r="B429" t="n">
-        <v>57290</v>
+        <v>97853</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
@@ -49580,35 +49580,39 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E429" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I429" t="inlineStr"/>
-      <c r="K429" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr"/>
-      <c r="M429" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N429" t="inlineStr"/>
       <c r="P429" t="inlineStr">
         <is>
@@ -49616,10 +49620,10 @@
         </is>
       </c>
       <c r="Q429" t="n">
-        <v>478342</v>
+        <v>478310</v>
       </c>
       <c r="R429" t="n">
-        <v>6770857</v>
+        <v>6770854</v>
       </c>
       <c r="S429" t="n">
         <v>1</v>
@@ -49660,6 +49664,7 @@
       <c r="AE429" t="b">
         <v>0</v>
       </c>
+      <c r="AF429" t="inlineStr"/>
       <c r="AG429" t="b">
         <v>0</v>
       </c>
@@ -49678,7 +49683,7 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>118568532</v>
+        <v>118568318</v>
       </c>
       <c r="B430" t="n">
         <v>97853</v>
@@ -49713,7 +49718,7 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J430" t="inlineStr"/>
@@ -49730,10 +49735,10 @@
         </is>
       </c>
       <c r="Q430" t="n">
-        <v>478310</v>
+        <v>478305</v>
       </c>
       <c r="R430" t="n">
-        <v>6770854</v>
+        <v>6770985</v>
       </c>
       <c r="S430" t="n">
         <v>1</v>
@@ -49793,10 +49798,10 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>118568318</v>
+        <v>118568160</v>
       </c>
       <c r="B431" t="n">
-        <v>97853</v>
+        <v>57290</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
@@ -49805,39 +49810,35 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E431" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I431" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J431" t="inlineStr"/>
-      <c r="K431" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr"/>
+      <c r="K431" t="inlineStr"/>
       <c r="L431" t="inlineStr"/>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N431" t="inlineStr"/>
       <c r="P431" t="inlineStr">
         <is>
@@ -49845,10 +49846,10 @@
         </is>
       </c>
       <c r="Q431" t="n">
-        <v>478305</v>
+        <v>478342</v>
       </c>
       <c r="R431" t="n">
-        <v>6770985</v>
+        <v>6770857</v>
       </c>
       <c r="S431" t="n">
         <v>1</v>
@@ -49889,7 +49890,6 @@
       <c r="AE431" t="b">
         <v>0</v>
       </c>
-      <c r="AF431" t="inlineStr"/>
       <c r="AG431" t="b">
         <v>0</v>
       </c>
@@ -49908,7 +49908,7 @@
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>118568251</v>
+        <v>118568207</v>
       </c>
       <c r="B432" t="n">
         <v>97853</v>
@@ -49960,10 +49960,10 @@
         </is>
       </c>
       <c r="Q432" t="n">
-        <v>478355</v>
+        <v>478333</v>
       </c>
       <c r="R432" t="n">
-        <v>6770890</v>
+        <v>6770886</v>
       </c>
       <c r="S432" t="n">
         <v>1</v>
@@ -50023,7 +50023,7 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>118568207</v>
+        <v>118568251</v>
       </c>
       <c r="B433" t="n">
         <v>97853</v>
@@ -50075,10 +50075,10 @@
         </is>
       </c>
       <c r="Q433" t="n">
-        <v>478333</v>
+        <v>478355</v>
       </c>
       <c r="R433" t="n">
-        <v>6770886</v>
+        <v>6770890</v>
       </c>
       <c r="S433" t="n">
         <v>1</v>
@@ -51288,7 +51288,7 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>118568540</v>
+        <v>118568716</v>
       </c>
       <c r="B444" t="n">
         <v>97853</v>
@@ -51323,13 +51323,13 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J444" t="inlineStr"/>
       <c r="K444" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L444" t="inlineStr"/>
@@ -51343,7 +51343,7 @@
         <v>478322</v>
       </c>
       <c r="R444" t="n">
-        <v>6770864</v>
+        <v>6771072</v>
       </c>
       <c r="S444" t="n">
         <v>1</v>
@@ -51403,7 +51403,7 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>118568575</v>
+        <v>118568540</v>
       </c>
       <c r="B445" t="n">
         <v>97853</v>
@@ -51455,10 +51455,10 @@
         </is>
       </c>
       <c r="Q445" t="n">
-        <v>478306</v>
+        <v>478322</v>
       </c>
       <c r="R445" t="n">
-        <v>6770902</v>
+        <v>6770864</v>
       </c>
       <c r="S445" t="n">
         <v>1</v>
@@ -51518,7 +51518,7 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>118568342</v>
+        <v>118568575</v>
       </c>
       <c r="B446" t="n">
         <v>97853</v>
@@ -51553,7 +51553,7 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J446" t="inlineStr"/>
@@ -51570,10 +51570,10 @@
         </is>
       </c>
       <c r="Q446" t="n">
-        <v>478320</v>
+        <v>478306</v>
       </c>
       <c r="R446" t="n">
-        <v>6770982</v>
+        <v>6770902</v>
       </c>
       <c r="S446" t="n">
         <v>1</v>
@@ -51633,7 +51633,7 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>118568716</v>
+        <v>118568342</v>
       </c>
       <c r="B447" t="n">
         <v>97853</v>
@@ -51674,7 +51674,7 @@
       <c r="J447" t="inlineStr"/>
       <c r="K447" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L447" t="inlineStr"/>
@@ -51685,10 +51685,10 @@
         </is>
       </c>
       <c r="Q447" t="n">
-        <v>478322</v>
+        <v>478320</v>
       </c>
       <c r="R447" t="n">
-        <v>6771072</v>
+        <v>6770982</v>
       </c>
       <c r="S447" t="n">
         <v>1</v>
@@ -52903,10 +52903,10 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>118568473</v>
+        <v>118568129</v>
       </c>
       <c r="B458" t="n">
-        <v>90795</v>
+        <v>57290</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
@@ -52919,34 +52919,31 @@
         </is>
       </c>
       <c r="E458" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I458" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J458" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr"/>
       <c r="K458" t="inlineStr"/>
+      <c r="L458" t="inlineStr"/>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N458" t="inlineStr"/>
       <c r="P458" t="inlineStr">
         <is>
@@ -52954,10 +52951,10 @@
         </is>
       </c>
       <c r="Q458" t="n">
-        <v>478270</v>
+        <v>478352</v>
       </c>
       <c r="R458" t="n">
-        <v>6770935</v>
+        <v>6770866</v>
       </c>
       <c r="S458" t="n">
         <v>1</v>
@@ -52998,7 +52995,6 @@
       <c r="AE458" t="b">
         <v>0</v>
       </c>
-      <c r="AF458" t="inlineStr"/>
       <c r="AG458" t="b">
         <v>0</v>
       </c>
@@ -53017,10 +53013,10 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>118568129</v>
+        <v>118568473</v>
       </c>
       <c r="B459" t="n">
-        <v>57290</v>
+        <v>90795</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
@@ -53033,31 +53029,34 @@
         </is>
       </c>
       <c r="E459" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I459" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K459" t="inlineStr"/>
-      <c r="L459" t="inlineStr"/>
-      <c r="M459" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N459" t="inlineStr"/>
       <c r="P459" t="inlineStr">
         <is>
@@ -53065,10 +53064,10 @@
         </is>
       </c>
       <c r="Q459" t="n">
-        <v>478352</v>
+        <v>478270</v>
       </c>
       <c r="R459" t="n">
-        <v>6770866</v>
+        <v>6770935</v>
       </c>
       <c r="S459" t="n">
         <v>1</v>
@@ -53109,6 +53108,7 @@
       <c r="AE459" t="b">
         <v>0</v>
       </c>
+      <c r="AF459" t="inlineStr"/>
       <c r="AG459" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -59879,7 +59879,7 @@
         <v>119819175</v>
       </c>
       <c r="B519" t="n">
-        <v>91005</v>
+        <v>91023</v>
       </c>
       <c r="C519" t="inlineStr">
         <is>

--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -4637,7 +4637,7 @@
         <v>118012500</v>
       </c>
       <c r="B36" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>118012252</v>
       </c>
       <c r="B37" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>118012515</v>
       </c>
       <c r="B39" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>118012327</v>
       </c>
       <c r="B40" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>118012651</v>
       </c>
       <c r="B42" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>118012563</v>
       </c>
       <c r="B43" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>118012524</v>
       </c>
       <c r="B46" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>118012590</v>
       </c>
       <c r="B47" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>118012520</v>
       </c>
       <c r="B49" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>118012262</v>
       </c>
       <c r="B50" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>118012435</v>
       </c>
       <c r="B51" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>118012310</v>
       </c>
       <c r="B52" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>118012512</v>
       </c>
       <c r="B54" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>118012197</v>
       </c>
       <c r="B55" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>118012626</v>
       </c>
       <c r="B56" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>118012371</v>
       </c>
       <c r="B57" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>118012488</v>
       </c>
       <c r="B58" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>118012580</v>
       </c>
       <c r="B60" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>118012495</v>
       </c>
       <c r="B61" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>118012541</v>
       </c>
       <c r="B63" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>118012341</v>
       </c>
       <c r="B65" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>118012615</v>
       </c>
       <c r="B70" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>118012333</v>
       </c>
       <c r="B71" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>118012347</v>
       </c>
       <c r="B72" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>118012157</v>
       </c>
       <c r="B73" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>118012532</v>
       </c>
       <c r="B75" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>118012384</v>
       </c>
       <c r="B76" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>118462730</v>
       </c>
       <c r="B83" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>118462626</v>
       </c>
       <c r="B104" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>118462737</v>
       </c>
       <c r="B125" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>118494003</v>
       </c>
       <c r="B165" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>118494019</v>
       </c>
       <c r="B182" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>118495862</v>
       </c>
       <c r="B183" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>118551916</v>
       </c>
       <c r="B230" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>118568120</v>
       </c>
       <c r="B437" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>118568160</v>
       </c>
       <c r="B446" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
@@ -52906,7 +52906,7 @@
         <v>118568129</v>
       </c>
       <c r="B458" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
@@ -57040,7 +57040,7 @@
         <v>118610619</v>
       </c>
       <c r="B494" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
@@ -57491,7 +57491,7 @@
         <v>118610692</v>
       </c>
       <c r="B498" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
@@ -58055,7 +58055,7 @@
         <v>118610631</v>
       </c>
       <c r="B503" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
@@ -58729,7 +58729,7 @@
         <v>118610669</v>
       </c>
       <c r="B509" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
@@ -59178,7 +59178,7 @@
         <v>118610640</v>
       </c>
       <c r="B513" t="n">
-        <v>57292</v>
+        <v>57478</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>

--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -4637,7 +4637,7 @@
         <v>118012500</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>118012252</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>118012515</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>118012327</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>118012651</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>118012563</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>118012524</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>118012590</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>118012520</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>118012262</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>118012435</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>118012310</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>118012512</v>
       </c>
       <c r="B54" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>118012197</v>
       </c>
       <c r="B55" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>118012626</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6952,7 +6952,7 @@
         <v>118012371</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>118012488</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>118012580</v>
       </c>
       <c r="B60" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>118012495</v>
       </c>
       <c r="B61" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>118012541</v>
       </c>
       <c r="B63" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>118012341</v>
       </c>
       <c r="B65" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>118012615</v>
       </c>
       <c r="B70" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
         <v>118012333</v>
       </c>
       <c r="B71" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>118012347</v>
       </c>
       <c r="B72" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>118012157</v>
       </c>
       <c r="B73" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>118012532</v>
       </c>
       <c r="B75" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>118012384</v>
       </c>
       <c r="B76" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>118462730</v>
       </c>
       <c r="B83" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>118462626</v>
       </c>
       <c r="B104" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>118462737</v>
       </c>
       <c r="B125" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>118494003</v>
       </c>
       <c r="B165" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>118494019</v>
       </c>
       <c r="B182" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>118495862</v>
       </c>
       <c r="B183" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -26779,7 +26779,7 @@
         <v>118551916</v>
       </c>
       <c r="B230" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -50496,7 +50496,7 @@
         <v>118568120</v>
       </c>
       <c r="B437" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
@@ -51525,7 +51525,7 @@
         <v>118568160</v>
       </c>
       <c r="B446" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
@@ -52906,7 +52906,7 @@
         <v>118568129</v>
       </c>
       <c r="B458" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
@@ -57040,7 +57040,7 @@
         <v>118610619</v>
       </c>
       <c r="B494" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
@@ -57491,7 +57491,7 @@
         <v>118610692</v>
       </c>
       <c r="B498" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
@@ -58055,7 +58055,7 @@
         <v>118610631</v>
       </c>
       <c r="B503" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
@@ -58729,7 +58729,7 @@
         <v>118610669</v>
       </c>
       <c r="B509" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
@@ -59178,7 +59178,7 @@
         <v>118610640</v>
       </c>
       <c r="B513" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>

--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>77200009</v>
       </c>
       <c r="B3" t="n">
-        <v>56604</v>
+        <v>56779</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY519"/>
+  <dimension ref="A1:AY520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59986,6 +59986,115 @@
       </c>
       <c r="AY519" t="inlineStr"/>
     </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>125833061</v>
+      </c>
+      <c r="B520" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr"/>
+      <c r="L520" t="inlineStr"/>
+      <c r="M520" t="inlineStr"/>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>Löva, Lisselheds badplats, Dlr</t>
+        </is>
+      </c>
+      <c r="Q520" t="n">
+        <v>478424</v>
+      </c>
+      <c r="R520" t="n">
+        <v>6770556</v>
+      </c>
+      <c r="S520" t="n">
+        <v>1</v>
+      </c>
+      <c r="T520" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U520" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V520" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W520" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y520" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA520" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD520" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE520" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG520" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT520" t="inlineStr"/>
+      <c r="AW520" t="inlineStr">
+        <is>
+          <t>Agnetha Ellesjö</t>
+        </is>
+      </c>
+      <c r="AX520" t="inlineStr">
+        <is>
+          <t>Agnetha Ellesjö</t>
+        </is>
+      </c>
+      <c r="AY520" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -59991,7 +59991,7 @@
         <v>125833061</v>
       </c>
       <c r="B520" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>

--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -59991,7 +59991,7 @@
         <v>125833061</v>
       </c>
       <c r="B520" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>

--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -59991,7 +59991,7 @@
         <v>125833061</v>
       </c>
       <c r="B520" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>

--- a/artfynd/A 62749-2023 artfynd.xlsx
+++ b/artfynd/A 62749-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY540"/>
+  <dimension ref="A1:AZ540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991141</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991518</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012356</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462654</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,6 +1238,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462962</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1322,6 +1352,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118495913</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118495982</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496290</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1648,6 +1693,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552054</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610755</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1873,6 +1928,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118005992</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1978,6 +2038,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012097</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2087,6 +2152,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012179</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2188,6 +2258,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012210</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2297,6 +2372,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568473</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2406,6 +2486,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568493</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2522,6 +2607,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118994247</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2623,6 +2713,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012066</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2724,6 +2819,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118493975</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2833,6 +2933,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610677</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2940,6 +3045,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819175</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3050,6 +3160,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012242</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3159,6 +3274,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118767300</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3268,6 +3388,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991161</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3384,6 +3509,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118995999</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3498,6 +3628,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991173</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3607,6 +3742,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462616</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3708,6 +3848,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462660</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3822,6 +3967,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496005</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3932,6 +4082,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118629836</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4051,6 +4206,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99398047</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4156,6 +4316,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012604</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4265,6 +4430,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125833061</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4383,6 +4553,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70729810</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4507,6 +4682,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15951787</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4633,6 +4813,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77200010</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4752,6 +4937,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132631741</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4857,6 +5047,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012157</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4962,6 +5157,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012197</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5067,6 +5267,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012252</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5172,6 +5377,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012262</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5277,6 +5487,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012310</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5382,6 +5597,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012327</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5487,6 +5707,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012333</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5592,6 +5817,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012341</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5697,6 +5927,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012347</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5802,6 +6037,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012371</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5907,6 +6147,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012384</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6012,6 +6257,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012435</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6117,6 +6367,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012488</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6222,6 +6477,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012495</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6327,6 +6587,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012500</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6432,6 +6697,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012512</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6537,6 +6807,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012515</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6642,6 +6917,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012520</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6747,6 +7027,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012524</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6852,6 +7137,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012532</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6957,6 +7247,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012541</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7062,6 +7357,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012563</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7167,6 +7467,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012580</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7272,6 +7577,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012590</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7377,6 +7687,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012615</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7482,6 +7797,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012626</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7587,6 +7907,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012651</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7692,6 +8017,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012667</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7797,6 +8127,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462626</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7902,6 +8237,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462730</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8007,6 +8347,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462737</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8112,6 +8457,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494003</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8217,6 +8567,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494019</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8322,6 +8677,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118495862</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8432,6 +8792,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551916</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8537,6 +8902,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568120</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8642,6 +9012,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568129</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8747,6 +9122,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568160</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8852,6 +9232,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610619</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8957,6 +9342,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610631</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9062,6 +9452,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610640</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9167,6 +9562,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610669</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9272,6 +9672,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610692</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9391,6 +9796,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132631781</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9498,6 +9908,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012130</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9601,6 +10016,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012224</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9708,6 +10128,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012418</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9815,6 +10240,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462371</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9922,6 +10352,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494239</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10029,6 +10464,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118495878</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10136,6 +10576,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118495968</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10243,6 +10688,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496187</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10346,6 +10796,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610627</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10453,6 +10908,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610713</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10572,6 +11032,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91800017</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10691,6 +11156,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87201116</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10815,6 +11285,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76864642</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10934,6 +11409,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108778071</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11053,6 +11533,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100071316</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11169,6 +11654,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117987499</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11288,6 +11778,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100071313</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11407,6 +11902,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124850316</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11512,6 +12012,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118553085</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11636,6 +12141,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87201133</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11762,6 +12272,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117987719</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11878,6 +12393,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118566484</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11997,6 +12517,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86792507</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12104,6 +12629,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991128</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12211,6 +12741,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610145</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12318,6 +12853,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610650</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12425,6 +12965,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610777</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12532,6 +13077,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610798</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12639,6 +13189,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610802</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12746,6 +13301,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610809</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12853,6 +13413,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610907</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12960,6 +13525,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610917</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13067,6 +13637,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610920</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13174,6 +13749,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610927</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13293,6 +13873,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117908609</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13399,6 +13984,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551318</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13509,6 +14099,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496309</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13611,6 +14206,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991939</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13725,6 +14325,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496239</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13839,6 +14444,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496262</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13953,6 +14563,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496272</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14055,6 +14670,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991967</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14165,6 +14785,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991238</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14284,6 +14909,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991309</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14394,6 +15024,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991376</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14504,6 +15139,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991390</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14614,6 +15254,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991424</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14724,6 +15369,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991442</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14834,6 +15484,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991462</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14944,6 +15599,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991486</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15054,6 +15714,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991494</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15164,6 +15829,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991506</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15266,6 +15936,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991994</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15368,6 +16043,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117992010</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15470,6 +16150,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117992031</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15572,6 +16257,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117992041</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15674,6 +16364,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117992046</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15776,6 +16471,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117992067</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15886,6 +16586,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012170</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15992,6 +16697,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012283</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16107,6 +16817,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012475</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16217,6 +16932,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012486</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16327,6 +17047,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462083</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16437,6 +17162,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462090</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16547,6 +17277,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462112</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16657,6 +17392,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462117</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16771,6 +17511,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462132</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16885,6 +17630,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462164</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16995,6 +17745,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462168</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17109,6 +17864,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462173</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17223,6 +17983,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462178</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17337,6 +18102,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462219</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17451,6 +18221,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462227</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17565,6 +18340,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462230</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17679,6 +18459,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462240</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17793,6 +18578,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462251</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17907,6 +18697,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462263</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18021,6 +18816,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462297</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18135,6 +18935,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462304</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18249,6 +19054,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462320</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18363,6 +19173,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462327</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18473,6 +19288,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462340</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18587,6 +19407,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462350</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18697,6 +19522,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462365</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18807,6 +19637,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462377</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18913,6 +19748,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462380</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19023,6 +19863,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462458</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19133,6 +19978,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462473</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19243,6 +20093,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462478</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19353,6 +20208,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462488</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19463,6 +20323,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462505</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19573,6 +20438,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462547</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19683,6 +20553,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462551</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19793,6 +20668,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462570</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19903,6 +20783,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462579</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20013,6 +20898,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462583</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20123,6 +21013,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462587</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20233,6 +21128,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462594</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20343,6 +21243,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462605</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20453,6 +21358,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462618</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20563,6 +21473,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462681</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20673,6 +21588,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462692</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20787,6 +21707,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462702</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20897,6 +21822,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462714</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21007,6 +21937,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462752</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21117,6 +22052,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462758</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21227,6 +22167,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462763</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21337,6 +22282,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462778</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21447,6 +22397,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462785</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21557,6 +22512,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462794</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21667,6 +22627,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462820</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21777,6 +22742,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462873</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21887,6 +22857,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462878</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21997,6 +22972,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462882</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22107,6 +23087,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462892</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22217,6 +23202,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462899</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22327,6 +23317,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462916</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22437,6 +23432,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462922</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22547,6 +23547,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462930</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22657,6 +23662,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462935</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22767,6 +23777,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462943</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22877,6 +23892,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462952</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22987,6 +24007,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462967</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23097,6 +24122,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462970</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23207,6 +24237,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462977</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23317,6 +24352,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462984</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23427,6 +24467,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462990</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23537,6 +24582,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463003</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23647,6 +24697,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463007</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23757,6 +24812,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463012</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23867,6 +24927,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463045</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23977,6 +25042,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463054</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24087,6 +25157,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463062</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24197,6 +25272,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463069</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24307,6 +25387,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463108</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24417,6 +25502,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463115</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24527,6 +25617,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463125</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -24637,6 +25732,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463134</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24747,6 +25847,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463141</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24857,6 +25962,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463152</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24967,6 +26077,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463183</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25077,6 +26192,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463218</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25187,6 +26307,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118493972</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25297,6 +26422,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118493978</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25403,6 +26533,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118493980</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -25513,6 +26648,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118493987</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -25623,6 +26763,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118493993</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25733,6 +26878,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494011</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25843,6 +26993,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494025</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25953,6 +27108,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494222</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26063,6 +27223,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494224</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -26173,6 +27338,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494225</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26283,6 +27453,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494227</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -26393,6 +27568,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494230</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -26503,6 +27683,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494232</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -26613,6 +27798,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494242</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -26723,6 +27913,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494244</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -26833,6 +28028,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494245</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -26943,6 +28143,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494247</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -27053,6 +28258,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494250</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27163,6 +28373,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118494251</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27273,6 +28488,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118495734</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -27383,6 +28603,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118495779</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -27493,6 +28718,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118495789</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -27603,6 +28833,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118495810</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -27713,6 +28948,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118495822</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -27823,6 +29063,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118495855</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -27933,6 +29178,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118495901</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -28043,6 +29293,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118495934</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -28153,6 +29408,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118495946</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28263,6 +29523,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496200</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -28373,6 +29638,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496212</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -28483,6 +29753,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496218</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -28593,6 +29868,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496227</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -28703,6 +29983,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551194</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -28813,6 +30098,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551224</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -28923,6 +30213,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551239</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -29033,6 +30328,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551248</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -29143,6 +30443,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551266</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -29253,6 +30558,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551276</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -29363,6 +30673,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551283</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -29473,6 +30788,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551290</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -29582,6 +30902,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551307</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -29691,6 +31016,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551333</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -29800,6 +31130,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551345</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -29909,6 +31244,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551356</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -30018,6 +31358,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551365</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -30127,6 +31472,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551379</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -30236,6 +31586,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551382</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -30345,6 +31700,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551386</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -30454,6 +31814,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551393</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -30563,6 +31928,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551397</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -30672,6 +32042,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551403</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -30781,6 +32156,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551408</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -30890,6 +32270,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551412</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -30999,6 +32384,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551416</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -31108,6 +32498,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551425</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -31217,6 +32612,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551432</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -31326,6 +32726,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551435</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -31435,6 +32840,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551438</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -31544,6 +32954,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551441</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -31653,6 +33068,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551447</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -31762,6 +33182,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551450</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -31871,6 +33296,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551455</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -31980,6 +33410,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551466</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -32089,6 +33524,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551476</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -32198,6 +33638,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551482</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -32307,6 +33752,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551489</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -32416,6 +33866,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551493</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -32525,6 +33980,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551499</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -32634,6 +34094,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551515</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -32743,6 +34208,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551523</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -32852,6 +34322,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551531</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -32961,6 +34436,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551541</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -33070,6 +34550,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551545</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -33179,6 +34664,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551762</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -33288,6 +34778,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551772</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -33397,6 +34892,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551778</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -33506,6 +35006,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551787</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -33615,6 +35120,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551794</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -33724,6 +35234,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551808</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -33833,6 +35348,11 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551811</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -33942,6 +35462,11 @@
         </is>
       </c>
       <c r="AY305" t="inlineStr"/>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551813</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -34051,6 +35576,11 @@
         </is>
       </c>
       <c r="AY306" t="inlineStr"/>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551819</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -34161,6 +35691,11 @@
         </is>
       </c>
       <c r="AY307" t="inlineStr"/>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551822</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -34271,6 +35806,11 @@
         </is>
       </c>
       <c r="AY308" t="inlineStr"/>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551829</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -34381,6 +35921,11 @@
         </is>
       </c>
       <c r="AY309" t="inlineStr"/>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551840</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -34491,6 +36036,11 @@
         </is>
       </c>
       <c r="AY310" t="inlineStr"/>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551859</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -34601,6 +36151,11 @@
         </is>
       </c>
       <c r="AY311" t="inlineStr"/>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551869</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -34711,6 +36266,11 @@
         </is>
       </c>
       <c r="AY312" t="inlineStr"/>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551875</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -34821,6 +36381,11 @@
         </is>
       </c>
       <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551884</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -34931,6 +36496,11 @@
         </is>
       </c>
       <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551887</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -35041,6 +36611,11 @@
         </is>
       </c>
       <c r="AY315" t="inlineStr"/>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551889</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -35151,6 +36726,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551892</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -35261,6 +36841,11 @@
         </is>
       </c>
       <c r="AY317" t="inlineStr"/>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551897</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -35371,6 +36956,11 @@
         </is>
       </c>
       <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551900</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -35481,6 +37071,11 @@
         </is>
       </c>
       <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551907</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -35591,6 +37186,11 @@
         </is>
       </c>
       <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551921</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -35701,6 +37301,11 @@
         </is>
       </c>
       <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551926</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -35811,6 +37416,11 @@
         </is>
       </c>
       <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551933</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -35921,6 +37531,11 @@
         </is>
       </c>
       <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551942</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -36031,6 +37646,11 @@
         </is>
       </c>
       <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551948</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -36141,6 +37761,11 @@
         </is>
       </c>
       <c r="AY325" t="inlineStr"/>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551953</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -36251,6 +37876,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551962</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -36361,6 +37991,11 @@
         </is>
       </c>
       <c r="AY327" t="inlineStr"/>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551967</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -36471,6 +38106,11 @@
         </is>
       </c>
       <c r="AY328" t="inlineStr"/>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551971</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -36581,6 +38221,11 @@
         </is>
       </c>
       <c r="AY329" t="inlineStr"/>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551977</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -36691,6 +38336,11 @@
         </is>
       </c>
       <c r="AY330" t="inlineStr"/>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551980</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -36800,6 +38450,11 @@
         </is>
       </c>
       <c r="AY331" t="inlineStr"/>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552001</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -36909,6 +38564,11 @@
         </is>
       </c>
       <c r="AY332" t="inlineStr"/>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552005</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -37018,6 +38678,11 @@
         </is>
       </c>
       <c r="AY333" t="inlineStr"/>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552006</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -37127,6 +38792,11 @@
         </is>
       </c>
       <c r="AY334" t="inlineStr"/>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552038</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -37236,6 +38906,11 @@
         </is>
       </c>
       <c r="AY335" t="inlineStr"/>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552046</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -37345,6 +39020,11 @@
         </is>
       </c>
       <c r="AY336" t="inlineStr"/>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552088</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -37454,6 +39134,11 @@
         </is>
       </c>
       <c r="AY337" t="inlineStr"/>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552091</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -37563,6 +39248,11 @@
         </is>
       </c>
       <c r="AY338" t="inlineStr"/>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552094</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -37672,6 +39362,11 @@
         </is>
       </c>
       <c r="AY339" t="inlineStr"/>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552095</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -37781,6 +39476,11 @@
         </is>
       </c>
       <c r="AY340" t="inlineStr"/>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552100</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -37890,6 +39590,11 @@
         </is>
       </c>
       <c r="AY341" t="inlineStr"/>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552105</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -37999,6 +39704,11 @@
         </is>
       </c>
       <c r="AY342" t="inlineStr"/>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552106</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -38108,6 +39818,11 @@
         </is>
       </c>
       <c r="AY343" t="inlineStr"/>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552109</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -38217,6 +39932,11 @@
         </is>
       </c>
       <c r="AY344" t="inlineStr"/>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552112</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -38326,6 +40046,11 @@
         </is>
       </c>
       <c r="AY345" t="inlineStr"/>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552116</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -38435,6 +40160,11 @@
         </is>
       </c>
       <c r="AY346" t="inlineStr"/>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552128</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -38544,6 +40274,11 @@
         </is>
       </c>
       <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552162</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -38653,6 +40388,11 @@
         </is>
       </c>
       <c r="AY348" t="inlineStr"/>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552164</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -38762,6 +40502,11 @@
         </is>
       </c>
       <c r="AY349" t="inlineStr"/>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552177</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -38871,6 +40616,11 @@
         </is>
       </c>
       <c r="AY350" t="inlineStr"/>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552188</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -38980,6 +40730,11 @@
         </is>
       </c>
       <c r="AY351" t="inlineStr"/>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552198</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -39089,6 +40844,11 @@
         </is>
       </c>
       <c r="AY352" t="inlineStr"/>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552201</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -39198,6 +40958,11 @@
         </is>
       </c>
       <c r="AY353" t="inlineStr"/>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552203</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -39307,6 +41072,11 @@
         </is>
       </c>
       <c r="AY354" t="inlineStr"/>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552205</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -39416,6 +41186,11 @@
         </is>
       </c>
       <c r="AY355" t="inlineStr"/>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552207</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -39525,6 +41300,11 @@
         </is>
       </c>
       <c r="AY356" t="inlineStr"/>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552209</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -39634,6 +41414,11 @@
         </is>
       </c>
       <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552213</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -39743,6 +41528,11 @@
         </is>
       </c>
       <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552218</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -39852,6 +41642,11 @@
         </is>
       </c>
       <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552220</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -39961,6 +41756,11 @@
         </is>
       </c>
       <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552221</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -40070,6 +41870,11 @@
         </is>
       </c>
       <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552232</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -40179,6 +41984,11 @@
         </is>
       </c>
       <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552241</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -40288,6 +42098,11 @@
         </is>
       </c>
       <c r="AY363" t="inlineStr"/>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552243</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -40397,6 +42212,11 @@
         </is>
       </c>
       <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552246</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -40506,6 +42326,11 @@
         </is>
       </c>
       <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552249</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -40615,6 +42440,11 @@
         </is>
       </c>
       <c r="AY366" t="inlineStr"/>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552250</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -40724,6 +42554,11 @@
         </is>
       </c>
       <c r="AY367" t="inlineStr"/>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552252</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -40833,6 +42668,11 @@
         </is>
       </c>
       <c r="AY368" t="inlineStr"/>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552256</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -40942,6 +42782,11 @@
         </is>
       </c>
       <c r="AY369" t="inlineStr"/>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552259</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -41052,6 +42897,11 @@
         </is>
       </c>
       <c r="AY370" t="inlineStr"/>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552260</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -41162,6 +43012,11 @@
         </is>
       </c>
       <c r="AY371" t="inlineStr"/>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552265</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -41272,6 +43127,11 @@
         </is>
       </c>
       <c r="AY372" t="inlineStr"/>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552269</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -41382,6 +43242,11 @@
         </is>
       </c>
       <c r="AY373" t="inlineStr"/>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552275</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -41492,6 +43357,11 @@
         </is>
       </c>
       <c r="AY374" t="inlineStr"/>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552281</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -41602,6 +43472,11 @@
         </is>
       </c>
       <c r="AY375" t="inlineStr"/>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552291</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -41712,6 +43587,11 @@
         </is>
       </c>
       <c r="AY376" t="inlineStr"/>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552301</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -41822,6 +43702,11 @@
         </is>
       </c>
       <c r="AY377" t="inlineStr"/>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552304</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -41932,6 +43817,11 @@
         </is>
       </c>
       <c r="AY378" t="inlineStr"/>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552307</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -42042,6 +43932,11 @@
         </is>
       </c>
       <c r="AY379" t="inlineStr"/>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552308</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -42152,6 +44047,11 @@
         </is>
       </c>
       <c r="AY380" t="inlineStr"/>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552309</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -42262,6 +44162,11 @@
         </is>
       </c>
       <c r="AY381" t="inlineStr"/>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552312</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -42372,6 +44277,11 @@
         </is>
       </c>
       <c r="AY382" t="inlineStr"/>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552315</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -42482,6 +44392,11 @@
         </is>
       </c>
       <c r="AY383" t="inlineStr"/>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552320</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -42592,6 +44507,11 @@
         </is>
       </c>
       <c r="AY384" t="inlineStr"/>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552328</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -42702,6 +44622,11 @@
         </is>
       </c>
       <c r="AY385" t="inlineStr"/>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552352</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -42812,6 +44737,11 @@
         </is>
       </c>
       <c r="AY386" t="inlineStr"/>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552356</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -42922,6 +44852,11 @@
         </is>
       </c>
       <c r="AY387" t="inlineStr"/>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552370</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -43032,6 +44967,11 @@
         </is>
       </c>
       <c r="AY388" t="inlineStr"/>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552375</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -43142,6 +45082,11 @@
         </is>
       </c>
       <c r="AY389" t="inlineStr"/>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552381</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -43252,6 +45197,11 @@
         </is>
       </c>
       <c r="AY390" t="inlineStr"/>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552384</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -43362,6 +45312,11 @@
         </is>
       </c>
       <c r="AY391" t="inlineStr"/>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552393</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -43472,6 +45427,11 @@
         </is>
       </c>
       <c r="AY392" t="inlineStr"/>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552411</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -43582,6 +45542,11 @@
         </is>
       </c>
       <c r="AY393" t="inlineStr"/>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552416</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -43692,6 +45657,11 @@
         </is>
       </c>
       <c r="AY394" t="inlineStr"/>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552419</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -43802,6 +45772,11 @@
         </is>
       </c>
       <c r="AY395" t="inlineStr"/>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552426</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -43912,6 +45887,11 @@
         </is>
       </c>
       <c r="AY396" t="inlineStr"/>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552431</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -44022,6 +46002,11 @@
         </is>
       </c>
       <c r="AY397" t="inlineStr"/>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552473</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -44132,6 +46117,11 @@
         </is>
       </c>
       <c r="AY398" t="inlineStr"/>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552494</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -44242,6 +46232,11 @@
         </is>
       </c>
       <c r="AY399" t="inlineStr"/>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552502</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -44352,6 +46347,11 @@
         </is>
       </c>
       <c r="AY400" t="inlineStr"/>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552506</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -44462,6 +46462,11 @@
         </is>
       </c>
       <c r="AY401" t="inlineStr"/>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552511</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -44572,6 +46577,11 @@
         </is>
       </c>
       <c r="AY402" t="inlineStr"/>
+      <c r="AZ402" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552517</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -44682,6 +46692,11 @@
         </is>
       </c>
       <c r="AY403" t="inlineStr"/>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552524</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -44792,6 +46807,11 @@
         </is>
       </c>
       <c r="AY404" t="inlineStr"/>
+      <c r="AZ404" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552620</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -44902,6 +46922,11 @@
         </is>
       </c>
       <c r="AY405" t="inlineStr"/>
+      <c r="AZ405" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552630</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -45012,6 +47037,11 @@
         </is>
       </c>
       <c r="AY406" t="inlineStr"/>
+      <c r="AZ406" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552647</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -45122,6 +47152,11 @@
         </is>
       </c>
       <c r="AY407" t="inlineStr"/>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552648</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -45232,6 +47267,11 @@
         </is>
       </c>
       <c r="AY408" t="inlineStr"/>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552651</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -45342,6 +47382,11 @@
         </is>
       </c>
       <c r="AY409" t="inlineStr"/>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552655</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -45452,6 +47497,11 @@
         </is>
       </c>
       <c r="AY410" t="inlineStr"/>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552662</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -45562,6 +47612,11 @@
         </is>
       </c>
       <c r="AY411" t="inlineStr"/>
+      <c r="AZ411" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552666</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -45672,6 +47727,11 @@
         </is>
       </c>
       <c r="AY412" t="inlineStr"/>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552671</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -45782,6 +47842,11 @@
         </is>
       </c>
       <c r="AY413" t="inlineStr"/>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552678</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -45892,6 +47957,11 @@
         </is>
       </c>
       <c r="AY414" t="inlineStr"/>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552680</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -46002,6 +48072,11 @@
         </is>
       </c>
       <c r="AY415" t="inlineStr"/>
+      <c r="AZ415" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552684</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -46112,6 +48187,11 @@
         </is>
       </c>
       <c r="AY416" t="inlineStr"/>
+      <c r="AZ416" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552695</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -46222,6 +48302,11 @@
         </is>
       </c>
       <c r="AY417" t="inlineStr"/>
+      <c r="AZ417" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552700</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -46332,6 +48417,11 @@
         </is>
       </c>
       <c r="AY418" t="inlineStr"/>
+      <c r="AZ418" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552703</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -46442,6 +48532,11 @@
         </is>
       </c>
       <c r="AY419" t="inlineStr"/>
+      <c r="AZ419" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552707</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -46552,6 +48647,11 @@
         </is>
       </c>
       <c r="AY420" t="inlineStr"/>
+      <c r="AZ420" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552712</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -46662,6 +48762,11 @@
         </is>
       </c>
       <c r="AY421" t="inlineStr"/>
+      <c r="AZ421" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552716</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -46772,6 +48877,11 @@
         </is>
       </c>
       <c r="AY422" t="inlineStr"/>
+      <c r="AZ422" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552720</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -46882,6 +48992,11 @@
         </is>
       </c>
       <c r="AY423" t="inlineStr"/>
+      <c r="AZ423" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552724</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -46992,6 +49107,11 @@
         </is>
       </c>
       <c r="AY424" t="inlineStr"/>
+      <c r="AZ424" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552728</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -47102,6 +49222,11 @@
         </is>
       </c>
       <c r="AY425" t="inlineStr"/>
+      <c r="AZ425" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552732</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -47212,6 +49337,11 @@
         </is>
       </c>
       <c r="AY426" t="inlineStr"/>
+      <c r="AZ426" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552739</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -47322,6 +49452,11 @@
         </is>
       </c>
       <c r="AY427" t="inlineStr"/>
+      <c r="AZ427" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552741</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -47432,6 +49567,11 @@
         </is>
       </c>
       <c r="AY428" t="inlineStr"/>
+      <c r="AZ428" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552745</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -47542,6 +49682,11 @@
         </is>
       </c>
       <c r="AY429" t="inlineStr"/>
+      <c r="AZ429" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552749</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -47652,6 +49797,11 @@
         </is>
       </c>
       <c r="AY430" t="inlineStr"/>
+      <c r="AZ430" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552757</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -47762,6 +49912,11 @@
         </is>
       </c>
       <c r="AY431" t="inlineStr"/>
+      <c r="AZ431" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552767</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -47872,6 +50027,11 @@
         </is>
       </c>
       <c r="AY432" t="inlineStr"/>
+      <c r="AZ432" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552773</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -47982,6 +50142,11 @@
         </is>
       </c>
       <c r="AY433" t="inlineStr"/>
+      <c r="AZ433" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552782</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -48092,6 +50257,11 @@
         </is>
       </c>
       <c r="AY434" t="inlineStr"/>
+      <c r="AZ434" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552791</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -48202,6 +50372,11 @@
         </is>
       </c>
       <c r="AY435" t="inlineStr"/>
+      <c r="AZ435" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552823</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -48312,6 +50487,11 @@
         </is>
       </c>
       <c r="AY436" t="inlineStr"/>
+      <c r="AZ436" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552835</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -48422,6 +50602,11 @@
         </is>
       </c>
       <c r="AY437" t="inlineStr"/>
+      <c r="AZ437" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552855</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -48532,6 +50717,11 @@
         </is>
       </c>
       <c r="AY438" t="inlineStr"/>
+      <c r="AZ438" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552862</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -48642,6 +50832,11 @@
         </is>
       </c>
       <c r="AY439" t="inlineStr"/>
+      <c r="AZ439" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552944</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -48752,6 +50947,11 @@
         </is>
       </c>
       <c r="AY440" t="inlineStr"/>
+      <c r="AZ440" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552948</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -48862,6 +51062,11 @@
         </is>
       </c>
       <c r="AY441" t="inlineStr"/>
+      <c r="AZ441" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552951</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -48972,6 +51177,11 @@
         </is>
       </c>
       <c r="AY442" t="inlineStr"/>
+      <c r="AZ442" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552953</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -49082,6 +51292,11 @@
         </is>
       </c>
       <c r="AY443" t="inlineStr"/>
+      <c r="AZ443" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552971</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -49192,6 +51407,11 @@
         </is>
       </c>
       <c r="AY444" t="inlineStr"/>
+      <c r="AZ444" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552976</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -49302,6 +51522,11 @@
         </is>
       </c>
       <c r="AY445" t="inlineStr"/>
+      <c r="AZ445" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552986</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -49412,6 +51637,11 @@
         </is>
       </c>
       <c r="AY446" t="inlineStr"/>
+      <c r="AZ446" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552991</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -49522,6 +51752,11 @@
         </is>
       </c>
       <c r="AY447" t="inlineStr"/>
+      <c r="AZ447" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552999</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -49632,6 +51867,11 @@
         </is>
       </c>
       <c r="AY448" t="inlineStr"/>
+      <c r="AZ448" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118553009</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -49742,6 +51982,11 @@
         </is>
       </c>
       <c r="AY449" t="inlineStr"/>
+      <c r="AZ449" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118553013</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -49852,6 +52097,11 @@
         </is>
       </c>
       <c r="AY450" t="inlineStr"/>
+      <c r="AZ450" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118553019</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -49962,6 +52212,11 @@
         </is>
       </c>
       <c r="AY451" t="inlineStr"/>
+      <c r="AZ451" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118553022</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -50072,6 +52327,11 @@
         </is>
       </c>
       <c r="AY452" t="inlineStr"/>
+      <c r="AZ452" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118553030</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -50182,6 +52442,11 @@
         </is>
       </c>
       <c r="AY453" t="inlineStr"/>
+      <c r="AZ453" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118553035</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -50292,6 +52557,11 @@
         </is>
       </c>
       <c r="AY454" t="inlineStr"/>
+      <c r="AZ454" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118553038</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -50402,6 +52672,11 @@
         </is>
       </c>
       <c r="AY455" t="inlineStr"/>
+      <c r="AZ455" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118553042</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -50512,6 +52787,11 @@
         </is>
       </c>
       <c r="AY456" t="inlineStr"/>
+      <c r="AZ456" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118553050</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -50622,6 +52902,11 @@
         </is>
       </c>
       <c r="AY457" t="inlineStr"/>
+      <c r="AZ457" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118553069</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -50732,6 +53017,11 @@
         </is>
       </c>
       <c r="AY458" t="inlineStr"/>
+      <c r="AZ458" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568170</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -50842,6 +53132,11 @@
         </is>
       </c>
       <c r="AY459" t="inlineStr"/>
+      <c r="AZ459" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568173</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -50952,6 +53247,11 @@
         </is>
       </c>
       <c r="AY460" t="inlineStr"/>
+      <c r="AZ460" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568176</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -51062,6 +53362,11 @@
         </is>
       </c>
       <c r="AY461" t="inlineStr"/>
+      <c r="AZ461" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568180</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -51172,6 +53477,11 @@
         </is>
       </c>
       <c r="AY462" t="inlineStr"/>
+      <c r="AZ462" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568186</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -51282,6 +53592,11 @@
         </is>
       </c>
       <c r="AY463" t="inlineStr"/>
+      <c r="AZ463" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568188</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -51392,6 +53707,11 @@
         </is>
       </c>
       <c r="AY464" t="inlineStr"/>
+      <c r="AZ464" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568192</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -51502,6 +53822,11 @@
         </is>
       </c>
       <c r="AY465" t="inlineStr"/>
+      <c r="AZ465" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568201</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -51612,6 +53937,11 @@
         </is>
       </c>
       <c r="AY466" t="inlineStr"/>
+      <c r="AZ466" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568207</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -51722,6 +54052,11 @@
         </is>
       </c>
       <c r="AY467" t="inlineStr"/>
+      <c r="AZ467" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568211</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -51832,6 +54167,11 @@
         </is>
       </c>
       <c r="AY468" t="inlineStr"/>
+      <c r="AZ468" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568220</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -51942,6 +54282,11 @@
         </is>
       </c>
       <c r="AY469" t="inlineStr"/>
+      <c r="AZ469" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568224</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -52052,6 +54397,11 @@
         </is>
       </c>
       <c r="AY470" t="inlineStr"/>
+      <c r="AZ470" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568251</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -52162,6 +54512,11 @@
         </is>
       </c>
       <c r="AY471" t="inlineStr"/>
+      <c r="AZ471" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568263</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -52272,6 +54627,11 @@
         </is>
       </c>
       <c r="AY472" t="inlineStr"/>
+      <c r="AZ472" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568271</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -52382,6 +54742,11 @@
         </is>
       </c>
       <c r="AY473" t="inlineStr"/>
+      <c r="AZ473" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568275</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -52492,6 +54857,11 @@
         </is>
       </c>
       <c r="AY474" t="inlineStr"/>
+      <c r="AZ474" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568300</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -52602,6 +54972,11 @@
         </is>
       </c>
       <c r="AY475" t="inlineStr"/>
+      <c r="AZ475" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568308</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -52712,6 +55087,11 @@
         </is>
       </c>
       <c r="AY476" t="inlineStr"/>
+      <c r="AZ476" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568314</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -52822,6 +55202,11 @@
         </is>
       </c>
       <c r="AY477" t="inlineStr"/>
+      <c r="AZ477" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568318</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -52932,6 +55317,11 @@
         </is>
       </c>
       <c r="AY478" t="inlineStr"/>
+      <c r="AZ478" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568324</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -53042,6 +55432,11 @@
         </is>
       </c>
       <c r="AY479" t="inlineStr"/>
+      <c r="AZ479" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568332</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -53152,6 +55547,11 @@
         </is>
       </c>
       <c r="AY480" t="inlineStr"/>
+      <c r="AZ480" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568335</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -53262,6 +55662,11 @@
         </is>
       </c>
       <c r="AY481" t="inlineStr"/>
+      <c r="AZ481" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568340</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -53372,6 +55777,11 @@
         </is>
       </c>
       <c r="AY482" t="inlineStr"/>
+      <c r="AZ482" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568342</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -53482,6 +55892,11 @@
         </is>
       </c>
       <c r="AY483" t="inlineStr"/>
+      <c r="AZ483" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568344</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -53592,6 +56007,11 @@
         </is>
       </c>
       <c r="AY484" t="inlineStr"/>
+      <c r="AZ484" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568347</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -53702,6 +56122,11 @@
         </is>
       </c>
       <c r="AY485" t="inlineStr"/>
+      <c r="AZ485" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568356</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -53812,6 +56237,11 @@
         </is>
       </c>
       <c r="AY486" t="inlineStr"/>
+      <c r="AZ486" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568359</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -53922,6 +56352,11 @@
         </is>
       </c>
       <c r="AY487" t="inlineStr"/>
+      <c r="AZ487" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568364</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -54032,6 +56467,11 @@
         </is>
       </c>
       <c r="AY488" t="inlineStr"/>
+      <c r="AZ488" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568373</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -54142,6 +56582,11 @@
         </is>
       </c>
       <c r="AY489" t="inlineStr"/>
+      <c r="AZ489" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568377</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -54252,6 +56697,11 @@
         </is>
       </c>
       <c r="AY490" t="inlineStr"/>
+      <c r="AZ490" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568386</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -54362,6 +56812,11 @@
         </is>
       </c>
       <c r="AY491" t="inlineStr"/>
+      <c r="AZ491" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568392</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -54472,6 +56927,11 @@
         </is>
       </c>
       <c r="AY492" t="inlineStr"/>
+      <c r="AZ492" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568400</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -54582,6 +57042,11 @@
         </is>
       </c>
       <c r="AY493" t="inlineStr"/>
+      <c r="AZ493" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568441</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -54692,6 +57157,11 @@
         </is>
       </c>
       <c r="AY494" t="inlineStr"/>
+      <c r="AZ494" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568447</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -54802,6 +57272,11 @@
         </is>
       </c>
       <c r="AY495" t="inlineStr"/>
+      <c r="AZ495" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568454</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -54912,6 +57387,11 @@
         </is>
       </c>
       <c r="AY496" t="inlineStr"/>
+      <c r="AZ496" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568516</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -55022,6 +57502,11 @@
         </is>
       </c>
       <c r="AY497" t="inlineStr"/>
+      <c r="AZ497" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568525</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -55132,6 +57617,11 @@
         </is>
       </c>
       <c r="AY498" t="inlineStr"/>
+      <c r="AZ498" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568532</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -55242,6 +57732,11 @@
         </is>
       </c>
       <c r="AY499" t="inlineStr"/>
+      <c r="AZ499" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568536</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -55352,6 +57847,11 @@
         </is>
       </c>
       <c r="AY500" t="inlineStr"/>
+      <c r="AZ500" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568540</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -55462,6 +57962,11 @@
         </is>
       </c>
       <c r="AY501" t="inlineStr"/>
+      <c r="AZ501" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568546</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -55572,6 +58077,11 @@
         </is>
       </c>
       <c r="AY502" t="inlineStr"/>
+      <c r="AZ502" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568552</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -55682,6 +58192,11 @@
         </is>
       </c>
       <c r="AY503" t="inlineStr"/>
+      <c r="AZ503" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568558</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -55792,6 +58307,11 @@
         </is>
       </c>
       <c r="AY504" t="inlineStr"/>
+      <c r="AZ504" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568561</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -55902,6 +58422,11 @@
         </is>
       </c>
       <c r="AY505" t="inlineStr"/>
+      <c r="AZ505" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568575</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -56012,6 +58537,11 @@
         </is>
       </c>
       <c r="AY506" t="inlineStr"/>
+      <c r="AZ506" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568581</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -56122,6 +58652,11 @@
         </is>
       </c>
       <c r="AY507" t="inlineStr"/>
+      <c r="AZ507" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568589</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -56232,6 +58767,11 @@
         </is>
       </c>
       <c r="AY508" t="inlineStr"/>
+      <c r="AZ508" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568592</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -56342,6 +58882,11 @@
         </is>
       </c>
       <c r="AY509" t="inlineStr"/>
+      <c r="AZ509" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568610</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -56452,6 +58997,11 @@
         </is>
       </c>
       <c r="AY510" t="inlineStr"/>
+      <c r="AZ510" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568615</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -56562,6 +59112,11 @@
         </is>
       </c>
       <c r="AY511" t="inlineStr"/>
+      <c r="AZ511" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568624</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -56672,6 +59227,11 @@
         </is>
       </c>
       <c r="AY512" t="inlineStr"/>
+      <c r="AZ512" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568634</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -56782,6 +59342,11 @@
         </is>
       </c>
       <c r="AY513" t="inlineStr"/>
+      <c r="AZ513" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568639</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -56892,6 +59457,11 @@
         </is>
       </c>
       <c r="AY514" t="inlineStr"/>
+      <c r="AZ514" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568647</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -57002,6 +59572,11 @@
         </is>
       </c>
       <c r="AY515" t="inlineStr"/>
+      <c r="AZ515" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568655</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -57112,6 +59687,11 @@
         </is>
       </c>
       <c r="AY516" t="inlineStr"/>
+      <c r="AZ516" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568657</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -57222,6 +59802,11 @@
         </is>
       </c>
       <c r="AY517" t="inlineStr"/>
+      <c r="AZ517" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568667</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -57332,6 +59917,11 @@
         </is>
       </c>
       <c r="AY518" t="inlineStr"/>
+      <c r="AZ518" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568676</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -57442,6 +60032,11 @@
         </is>
       </c>
       <c r="AY519" t="inlineStr"/>
+      <c r="AZ519" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568679</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -57552,6 +60147,11 @@
         </is>
       </c>
       <c r="AY520" t="inlineStr"/>
+      <c r="AZ520" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568683</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -57662,6 +60262,11 @@
         </is>
       </c>
       <c r="AY521" t="inlineStr"/>
+      <c r="AZ521" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568687</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -57772,6 +60377,11 @@
         </is>
       </c>
       <c r="AY522" t="inlineStr"/>
+      <c r="AZ522" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568690</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -57882,6 +60492,11 @@
         </is>
       </c>
       <c r="AY523" t="inlineStr"/>
+      <c r="AZ523" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568696</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -57992,6 +60607,11 @@
         </is>
       </c>
       <c r="AY524" t="inlineStr"/>
+      <c r="AZ524" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568716</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -58102,6 +60722,11 @@
         </is>
       </c>
       <c r="AY525" t="inlineStr"/>
+      <c r="AZ525" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568728</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -58212,6 +60837,11 @@
         </is>
       </c>
       <c r="AY526" t="inlineStr"/>
+      <c r="AZ526" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568737</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -58322,6 +60952,11 @@
         </is>
       </c>
       <c r="AY527" t="inlineStr"/>
+      <c r="AZ527" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568743</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -58432,6 +61067,11 @@
         </is>
       </c>
       <c r="AY528" t="inlineStr"/>
+      <c r="AZ528" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568748</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -58542,6 +61182,11 @@
         </is>
       </c>
       <c r="AY529" t="inlineStr"/>
+      <c r="AZ529" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568756</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -58652,6 +61297,11 @@
         </is>
       </c>
       <c r="AY530" t="inlineStr"/>
+      <c r="AZ530" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568765</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -58762,6 +61412,11 @@
         </is>
       </c>
       <c r="AY531" t="inlineStr"/>
+      <c r="AZ531" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568780</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -58872,6 +61527,11 @@
         </is>
       </c>
       <c r="AY532" t="inlineStr"/>
+      <c r="AZ532" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610721</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -58982,6 +61642,11 @@
         </is>
       </c>
       <c r="AY533" t="inlineStr"/>
+      <c r="AZ533" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610726</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -59092,6 +61757,11 @@
         </is>
       </c>
       <c r="AY534" t="inlineStr"/>
+      <c r="AZ534" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610732</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -59202,6 +61872,11 @@
         </is>
       </c>
       <c r="AY535" t="inlineStr"/>
+      <c r="AZ535" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610739</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -59312,6 +61987,11 @@
         </is>
       </c>
       <c r="AY536" t="inlineStr"/>
+      <c r="AZ536" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610746</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -59422,6 +62102,11 @@
         </is>
       </c>
       <c r="AY537" t="inlineStr"/>
+      <c r="AZ537" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610767</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -59536,6 +62221,11 @@
         </is>
       </c>
       <c r="AY538" t="inlineStr"/>
+      <c r="AZ538" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496176</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -59654,6 +62344,11 @@
         </is>
       </c>
       <c r="AY539" t="inlineStr"/>
+      <c r="AZ539" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117908567</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -59769,8 +62464,554 @@
         </is>
       </c>
       <c r="AY540" t="inlineStr"/>
+      <c r="AZ540" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118993330</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ445" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ446" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ447" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ448" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ449" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ451" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ452" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ453" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ454" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ455" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ456" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ457" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ458" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ459" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ460" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ461" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ462" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ463" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ464" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ465" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ466" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ467" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ468" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ469" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ470" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ471" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ472" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ473" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ474" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ475" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ476" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ477" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ478" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ479" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ480" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ481" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ482" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ483" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ484" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ485" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ486" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ487" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ488" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ489" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ490" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ491" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ492" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ493" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ494" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ495" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ496" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ497" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ498" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ499" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ500" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ501" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ502" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ503" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ504" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ505" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ506" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ507" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ508" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ509" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ510" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ511" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ512" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ513" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ514" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ515" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ516" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ517" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ518" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ519" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ520" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ521" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ522" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ523" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ524" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ525" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ526" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ527" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ528" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ529" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ530" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ531" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ532" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ533" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ534" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ535" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ536" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ537" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ538" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ539" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ540" r:id="rId539"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>